--- a/data/shifts_fixes.xlsx
+++ b/data/shifts_fixes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,103 +424,27 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>Prénom</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>Jour</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Tâche</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Début</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Fin</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Personne 01</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Lundi</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Technique</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>24:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Personne 02</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Mardi</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Sécurité</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Personne 02</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Vendredi</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Sécurité</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>24:00</t>
         </is>
       </c>
     </row>

--- a/data/shifts_fixes.xlsx
+++ b/data/shifts_fixes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sschies1\_code\1.09_VScode\06_VoeuxConcerts\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADED30D4-D9EC-468B-B880-4EF39E136E32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0133B593-55BC-4A02-BC40-98F755DE6FC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-69" yWindow="-69" windowWidth="22080" windowHeight="13132" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25490" yWindow="1480" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mardi" sheetId="1" r:id="rId1"/>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="12">
   <si>
     <t>Nom</t>
   </si>
@@ -106,6 +106,12 @@
   </si>
   <si>
     <t>Bourdon.ne</t>
+  </si>
+  <si>
+    <t>Stageman</t>
+  </si>
+  <si>
+    <t>Tech Jacquard</t>
   </si>
 </sst>
 </file>
@@ -178,130 +184,6 @@
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="Mardi"/>
-      <sheetName val="Mercredi"/>
-      <sheetName val="Jeudi"/>
-      <sheetName val="Vendredi"/>
-      <sheetName val="Samedi"/>
-      <sheetName val="Dimanche"/>
-      <sheetName val="Tâches"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6">
-        <row r="1">
-          <cell r="A1" t="str">
-            <v>Tâches</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="A2" t="str">
-            <v>Accueil</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="A3" t="str">
-            <v>Abeilles Ruche</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="A4" t="str">
-            <v>Ailes</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="A5" t="str">
-            <v>Bar loges</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="A6" t="str">
-            <v>Bar public</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="A7" t="str">
-            <v>Bourdon.ne</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="A8" t="str">
-            <v>Entrée backstage</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="A9" t="str">
-            <v>Horaires</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="A10" t="str">
-            <v>Déambule Gerry</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="A11" t="str">
-            <v>Déambule Colbok</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="A12" t="str">
-            <v>Déambule Goulus</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="A13" t="str">
-            <v>Déambule Ko-compagnie</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="A14" t="str">
-            <v>Déambule Spoutnik</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="A15" t="str">
-            <v>Déambule FBI</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="A16" t="str">
-            <v>Tech PCGB</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="A17" t="str">
-            <v>Tech Jacquard</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="A18" t="str">
-            <v>Tech Muchmuche</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="A19" t="str">
-            <v>Tech T'es rien…</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
       <sheetName val="Bénévoles 2026 V2"/>
       <sheetName val="Drop-downs"/>
       <sheetName val="Bénévoles_2026"/>
@@ -330,6 +212,16 @@
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
+        <row r="1">
+          <cell r="B1"/>
+          <cell r="E1"/>
+          <cell r="F1"/>
+        </row>
+        <row r="2">
+          <cell r="B2"/>
+          <cell r="E2"/>
+          <cell r="F2"/>
+        </row>
         <row r="3">
           <cell r="B3" t="str">
             <v>In</v>
@@ -1014,13 +906,13 @@
         </row>
         <row r="65">
           <cell r="B65" t="b">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="E65" t="str">
-            <v>Delassus</v>
+            <v>Ménard</v>
           </cell>
           <cell r="F65" t="str">
-            <v>Frank</v>
+            <v>Mireille</v>
           </cell>
         </row>
         <row r="66">
@@ -1028,10 +920,10 @@
             <v>0</v>
           </cell>
           <cell r="E66" t="str">
-            <v>Rieger</v>
+            <v>Delassus</v>
           </cell>
           <cell r="F66" t="str">
-            <v>Maya</v>
+            <v>Frank</v>
           </cell>
         </row>
         <row r="67">
@@ -1039,10 +931,10 @@
             <v>0</v>
           </cell>
           <cell r="E67" t="str">
-            <v>Michel</v>
+            <v>Rieger</v>
           </cell>
           <cell r="F67" t="str">
-            <v>Mehdi</v>
+            <v>Maya</v>
           </cell>
         </row>
         <row r="68">
@@ -1050,10 +942,10 @@
             <v>0</v>
           </cell>
           <cell r="E68" t="str">
-            <v>Ménard</v>
+            <v>Michel</v>
           </cell>
           <cell r="F68" t="str">
-            <v>Mireille</v>
+            <v>Mehdi</v>
           </cell>
         </row>
         <row r="69">
@@ -1061,10 +953,10 @@
             <v>0</v>
           </cell>
           <cell r="E69" t="str">
-            <v>Goumaz</v>
+            <v>Pieper</v>
           </cell>
           <cell r="F69" t="str">
-            <v>Alexandre</v>
+            <v>Giulia</v>
           </cell>
         </row>
         <row r="70">
@@ -1072,10 +964,10 @@
             <v>0</v>
           </cell>
           <cell r="E70" t="str">
-            <v>Pieper</v>
+            <v>Durand</v>
           </cell>
           <cell r="F70" t="str">
-            <v>Giulia</v>
+            <v>Isidore</v>
           </cell>
         </row>
         <row r="71">
@@ -1083,29 +975,30 @@
             <v>0</v>
           </cell>
           <cell r="E71" t="str">
-            <v>Durand</v>
+            <v>Lemay</v>
           </cell>
           <cell r="F71" t="str">
-            <v>Isidore</v>
+            <v>Mae</v>
           </cell>
         </row>
         <row r="72">
           <cell r="B72" t="b">
             <v>0</v>
           </cell>
-          <cell r="E72" t="str">
-            <v>Lemay</v>
-          </cell>
+          <cell r="E72"/>
           <cell r="F72" t="str">
-            <v>Mae</v>
+            <v>Michelle-Evy</v>
           </cell>
         </row>
         <row r="73">
           <cell r="B73" t="b">
             <v>0</v>
           </cell>
+          <cell r="E73" t="str">
+            <v>Bonay</v>
+          </cell>
           <cell r="F73" t="str">
-            <v>Michelle-Evy</v>
+            <v>Paul</v>
           </cell>
         </row>
         <row r="74">
@@ -1113,10 +1006,10 @@
             <v>0</v>
           </cell>
           <cell r="E74" t="str">
-            <v>Bonay</v>
+            <v>Lagier</v>
           </cell>
           <cell r="F74" t="str">
-            <v>Paul</v>
+            <v>Tician</v>
           </cell>
         </row>
         <row r="75">
@@ -1124,10 +1017,10 @@
             <v>0</v>
           </cell>
           <cell r="E75" t="str">
-            <v>Lagier</v>
+            <v>Carrière</v>
           </cell>
           <cell r="F75" t="str">
-            <v>Tician</v>
+            <v>Zellie</v>
           </cell>
         </row>
         <row r="76">
@@ -1135,10 +1028,10 @@
             <v>0</v>
           </cell>
           <cell r="E76" t="str">
-            <v>Carrière</v>
+            <v>Goumaz</v>
           </cell>
           <cell r="F76" t="str">
-            <v>Zellie</v>
+            <v>Alexandre</v>
           </cell>
         </row>
         <row r="77">
@@ -1321,6 +1214,7 @@
           <cell r="B93" t="b">
             <v>0</v>
           </cell>
+          <cell r="E93"/>
           <cell r="F93" t="str">
             <v>Ramón</v>
           </cell>
@@ -1335,6 +1229,11 @@
           <cell r="F94" t="str">
             <v>Robert</v>
           </cell>
+        </row>
+        <row r="95">
+          <cell r="B95"/>
+          <cell r="E95"/>
+          <cell r="F95"/>
         </row>
       </sheetData>
       <sheetData sheetId="1"/>
@@ -1361,6 +1260,130 @@
       <sheetData sheetId="22"/>
       <sheetData sheetId="23"/>
       <sheetData sheetId="24"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Mardi"/>
+      <sheetName val="Mercredi"/>
+      <sheetName val="Jeudi"/>
+      <sheetName val="Vendredi"/>
+      <sheetName val="Samedi"/>
+      <sheetName val="Dimanche"/>
+      <sheetName val="Tâches"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6">
+        <row r="1">
+          <cell r="A1" t="str">
+            <v>Tâches</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="A2" t="str">
+            <v>Accueil</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="A3" t="str">
+            <v>Abeilles Ruche</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4" t="str">
+            <v>Ailes</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5" t="str">
+            <v>Bar loges</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6" t="str">
+            <v>Bar public</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7" t="str">
+            <v>Bourdon.ne</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8" t="str">
+            <v>Entrée backstage</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9" t="str">
+            <v>Horaires</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10" t="str">
+            <v>Déambule Gerry</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11" t="str">
+            <v>Déambule Colbok</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="A12" t="str">
+            <v>Déambule Goulus</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="A13" t="str">
+            <v>Déambule Ko-compagnie</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="A14" t="str">
+            <v>Déambule Spoutnik</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="A15" t="str">
+            <v>Déambule FBI</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="A16" t="str">
+            <v>Tech PCGB</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="A17" t="str">
+            <v>Tech Jacquard</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="A18" t="str">
+            <v>Tech Muchmuche</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="A19" t="str">
+            <v>Tech T'es rien…</v>
+          </cell>
+        </row>
+      </sheetData>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1651,7 +1674,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E62"/>
+  <dimension ref="A1:E63"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="2" width="14.921875" customWidth="1"/>
@@ -1678,7 +1701,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A2" t="str" cm="1">
-        <f t="array" ref="A2:B62">_xlfn._xlws.FILTER('[2]Bénévoles 2026 V2'!$E:$F,'[2]Bénévoles 2026 V2'!$B:$B=TRUE)</f>
+        <f t="array" ref="A2:B63">_xlfn._xlws.FILTER('[1]Bénévoles 2026 V2'!$E:$F,'[1]Bénévoles 2026 V2'!$B:$B=TRUE)</f>
         <v>Bouvet</v>
       </c>
       <c r="B2" t="str">
@@ -1791,12 +1814,6 @@
       <c r="C15" t="s">
         <v>9</v>
       </c>
-      <c r="D15" s="2">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="E15" s="2">
-        <v>0.79166666666666663</v>
-      </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A16" t="str">
@@ -1806,7 +1823,7 @@
         <v>Corentin</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A17" t="str">
         <v>De Filippo</v>
       </c>
@@ -1814,7 +1831,7 @@
         <v>Emma</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A18" t="str">
         <v>Maître</v>
       </c>
@@ -1822,7 +1839,7 @@
         <v>Enzo</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A19" t="str">
         <v>Prouvost</v>
       </c>
@@ -1830,7 +1847,7 @@
         <v>Eugénie</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A20" t="str">
         <v xml:space="preserve">Rakotonandrasana </v>
       </c>
@@ -1838,7 +1855,7 @@
         <v>Iris</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A21" t="str">
         <v>Bürgisser</v>
       </c>
@@ -1846,7 +1863,7 @@
         <v>Jamilah</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A22" t="str">
         <v>Ruscio</v>
       </c>
@@ -1854,7 +1871,7 @@
         <v>Jolan</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A23" t="str">
         <v>Wuilloud</v>
       </c>
@@ -1864,14 +1881,8 @@
       <c r="C23" t="s">
         <v>8</v>
       </c>
-      <c r="D23" s="2">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="E23" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.4">
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A24" t="str">
         <v>Pirolley</v>
       </c>
@@ -1879,7 +1890,7 @@
         <v>Jules</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A25" t="str">
         <v>Chavaillaz</v>
       </c>
@@ -1887,7 +1898,7 @@
         <v>Julie</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A26" t="str">
         <v>Oeschger</v>
       </c>
@@ -1897,14 +1908,8 @@
       <c r="C26" t="s">
         <v>8</v>
       </c>
-      <c r="D26" s="2">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="E26" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.4">
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A27" t="str">
         <v>Baltzinger</v>
       </c>
@@ -1912,7 +1917,7 @@
         <v>Léa</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A28" t="str">
         <v>Chambaz</v>
       </c>
@@ -1920,7 +1925,7 @@
         <v>Léa</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A29" t="str">
         <v>Ledru</v>
       </c>
@@ -1928,7 +1933,7 @@
         <v>Lina-Rosa</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A30" t="str">
         <v>Jaquet</v>
       </c>
@@ -1936,7 +1941,7 @@
         <v>Lisa</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A31" t="str">
         <v>Magnin</v>
       </c>
@@ -1944,7 +1949,7 @@
         <v>Lisa</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A32" t="str">
         <v>Cardis</v>
       </c>
@@ -1970,12 +1975,6 @@
       <c r="C34" t="s">
         <v>9</v>
       </c>
-      <c r="D34" s="2">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="E34" s="2">
-        <v>0.91666666666666663</v>
-      </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A35" t="str">
@@ -1995,12 +1994,6 @@
       <c r="C36" t="s">
         <v>9</v>
       </c>
-      <c r="D36" s="2">
-        <v>0.91666666666666663</v>
-      </c>
-      <c r="E36" s="2">
-        <v>1.0208333333333333</v>
-      </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A37" t="str">
@@ -2026,13 +2019,7 @@
         <v>Marius</v>
       </c>
       <c r="C39" t="s">
-        <v>5</v>
-      </c>
-      <c r="D39" s="2">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="E39" s="2">
-        <v>0.875</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.4">
@@ -2050,6 +2037,15 @@
       <c r="B41" t="str">
         <v>Mathis</v>
       </c>
+      <c r="C41" t="s">
+        <v>11</v>
+      </c>
+      <c r="D41" s="2">
+        <v>0.875</v>
+      </c>
+      <c r="E41" s="2">
+        <v>0.95833333333333337</v>
+      </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A42" t="str">
@@ -2067,13 +2063,7 @@
         <v>Maxime</v>
       </c>
       <c r="C43" t="s">
-        <v>6</v>
-      </c>
-      <c r="D43" s="2">
-        <v>0.75</v>
-      </c>
-      <c r="E43" s="2">
-        <v>0.83333333333333337</v>
+        <v>10</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.4">
@@ -2099,6 +2089,15 @@
       <c r="B46" t="str">
         <v>Morgana</v>
       </c>
+      <c r="C46" t="s">
+        <v>5</v>
+      </c>
+      <c r="D46" s="2">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="E46" s="2">
+        <v>0.75</v>
+      </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A47" t="str">
@@ -2235,6 +2234,23 @@
       </c>
       <c r="B62" t="str">
         <v>Ysatis</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A63" t="str">
+        <v>Ménard</v>
+      </c>
+      <c r="B63" t="str">
+        <v>Mireille</v>
+      </c>
+      <c r="C63" t="s">
+        <v>6</v>
+      </c>
+      <c r="D63" s="2">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="E63" s="2">
+        <v>0.875</v>
       </c>
     </row>
   </sheetData>
@@ -2244,9 +2260,9 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{084F9546-D096-4E4D-8C52-00F41E3AF85B}">
           <x14:formula1>
-            <xm:f>Taches!$A$2:$A$19</xm:f>
+            <xm:f>Taches!$A$2:$A$20</xm:f>
           </x14:formula1>
-          <xm:sqref>C2:C62</xm:sqref>
+          <xm:sqref>C2:C63</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2256,7 +2272,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{423EC40D-93CA-4FCD-A6F8-28F80DC6C0B8}">
-  <dimension ref="A1:E62"/>
+  <dimension ref="A1:E63"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="2" width="14.921875" customWidth="1"/>
@@ -2282,7 +2298,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A2" t="str" cm="1">
-        <f t="array" ref="A2:B62">_xlfn._xlws.FILTER('[2]Bénévoles 2026 V2'!$E:$F,'[2]Bénévoles 2026 V2'!$B:$B=TRUE)</f>
+        <f t="array" ref="A2:B63">_xlfn._xlws.FILTER('[1]Bénévoles 2026 V2'!$E:$F,'[1]Bénévoles 2026 V2'!$B:$B=TRUE)</f>
         <v>Bouvet</v>
       </c>
       <c r="B2" t="str">
@@ -2794,6 +2810,14 @@
       </c>
       <c r="B62" t="str">
         <v>Ysatis</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A63" t="str">
+        <v>Ménard</v>
+      </c>
+      <c r="B63" t="str">
+        <v>Mireille</v>
       </c>
     </row>
   </sheetData>
@@ -2803,7 +2827,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4D8DA555-F325-4E41-88C8-C31CF97FEC4E}">
           <x14:formula1>
-            <xm:f>Taches!$A$2:$A$15</xm:f>
+            <xm:f>Taches!$A$2:$A$16</xm:f>
           </x14:formula1>
           <xm:sqref>C2:C62</xm:sqref>
         </x14:dataValidation>
@@ -2815,7 +2839,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3D62804-1233-4D8D-A119-6FEA62BCFE42}">
-  <dimension ref="A1:E62"/>
+  <dimension ref="A1:E63"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="2" width="14.921875" customWidth="1"/>
@@ -2841,7 +2865,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A2" t="str" cm="1">
-        <f t="array" ref="A2:B62">_xlfn._xlws.FILTER('[2]Bénévoles 2026 V2'!$E:$F,'[2]Bénévoles 2026 V2'!$B:$B=TRUE)</f>
+        <f t="array" ref="A2:B63">_xlfn._xlws.FILTER('[1]Bénévoles 2026 V2'!$E:$F,'[1]Bénévoles 2026 V2'!$B:$B=TRUE)</f>
         <v>Bouvet</v>
       </c>
       <c r="B2" t="str">
@@ -3353,6 +3377,14 @@
       </c>
       <c r="B62" t="str">
         <v>Ysatis</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A63" t="str">
+        <v>Ménard</v>
+      </c>
+      <c r="B63" t="str">
+        <v>Mireille</v>
       </c>
     </row>
   </sheetData>
@@ -3362,7 +3394,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8152DAFD-18A2-4A13-8446-2A68C51C1123}">
           <x14:formula1>
-            <xm:f>Taches!$A$2:$A$15</xm:f>
+            <xm:f>Taches!$A$2:$A$16</xm:f>
           </x14:formula1>
           <xm:sqref>C2:C62</xm:sqref>
         </x14:dataValidation>
@@ -3374,7 +3406,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9848EB70-D8FB-4222-91C3-0659002AC443}">
-  <dimension ref="A1:E62"/>
+  <dimension ref="A1:E63"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="2" width="14.921875" customWidth="1"/>
@@ -3400,7 +3432,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A2" t="str" cm="1">
-        <f t="array" ref="A2:B62">_xlfn._xlws.FILTER('[2]Bénévoles 2026 V2'!$E:$F,'[2]Bénévoles 2026 V2'!$B:$B=TRUE)</f>
+        <f t="array" ref="A2:B63">_xlfn._xlws.FILTER('[1]Bénévoles 2026 V2'!$E:$F,'[1]Bénévoles 2026 V2'!$B:$B=TRUE)</f>
         <v>Bouvet</v>
       </c>
       <c r="B2" t="str">
@@ -3912,6 +3944,14 @@
       </c>
       <c r="B62" t="str">
         <v>Ysatis</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A63" t="str">
+        <v>Ménard</v>
+      </c>
+      <c r="B63" t="str">
+        <v>Mireille</v>
       </c>
     </row>
   </sheetData>
@@ -3921,7 +3961,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{32982F90-5317-4051-945D-FC1716C4ACE1}">
           <x14:formula1>
-            <xm:f>Taches!$A$2:$A$15</xm:f>
+            <xm:f>Taches!$A$2:$A$16</xm:f>
           </x14:formula1>
           <xm:sqref>C2:C62</xm:sqref>
         </x14:dataValidation>
@@ -3933,7 +3973,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7E4AE93-50CA-4EB1-98E3-757ADDFDDBBD}">
-  <dimension ref="A1:E62"/>
+  <dimension ref="A1:E63"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="2" width="14.921875" customWidth="1"/>
@@ -3959,7 +3999,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A2" t="str" cm="1">
-        <f t="array" ref="A2:B62">_xlfn._xlws.FILTER('[2]Bénévoles 2026 V2'!$E:$F,'[2]Bénévoles 2026 V2'!$B:$B=TRUE)</f>
+        <f t="array" ref="A2:B63">_xlfn._xlws.FILTER('[1]Bénévoles 2026 V2'!$E:$F,'[1]Bénévoles 2026 V2'!$B:$B=TRUE)</f>
         <v>Bouvet</v>
       </c>
       <c r="B2" t="str">
@@ -4471,6 +4511,14 @@
       </c>
       <c r="B62" t="str">
         <v>Ysatis</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A63" t="str">
+        <v>Ménard</v>
+      </c>
+      <c r="B63" t="str">
+        <v>Mireille</v>
       </c>
     </row>
   </sheetData>
@@ -4480,7 +4528,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B0D27922-CCA9-4DA0-AEDA-6FDF09745AD2}">
           <x14:formula1>
-            <xm:f>Taches!$A$2:$A$15</xm:f>
+            <xm:f>Taches!$A$2:$A$16</xm:f>
           </x14:formula1>
           <xm:sqref>C2:C62</xm:sqref>
         </x14:dataValidation>
@@ -4492,7 +4540,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B965F37E-7321-434E-8400-31D7FE0BF594}">
-  <dimension ref="A1:E62"/>
+  <dimension ref="A1:E63"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="2" width="14.921875" customWidth="1"/>
@@ -4518,7 +4566,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A2" t="str" cm="1">
-        <f t="array" ref="A2:B62">_xlfn._xlws.FILTER('[2]Bénévoles 2026 V2'!$E:$F,'[2]Bénévoles 2026 V2'!$B:$B=TRUE)</f>
+        <f t="array" ref="A2:B63">_xlfn._xlws.FILTER('[1]Bénévoles 2026 V2'!$E:$F,'[1]Bénévoles 2026 V2'!$B:$B=TRUE)</f>
         <v>Bouvet</v>
       </c>
       <c r="B2" t="str">
@@ -5030,6 +5078,14 @@
       </c>
       <c r="B62" t="str">
         <v>Ysatis</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A63" t="str">
+        <v>Ménard</v>
+      </c>
+      <c r="B63" t="str">
+        <v>Mireille</v>
       </c>
     </row>
   </sheetData>
@@ -5039,7 +5095,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{7D7030CC-FCBC-4B51-8F31-91C3DF89EAA0}">
           <x14:formula1>
-            <xm:f>Taches!$A$2:$A$15</xm:f>
+            <xm:f>Taches!$A$2:$A$16</xm:f>
           </x14:formula1>
           <xm:sqref>C2:C62</xm:sqref>
         </x14:dataValidation>
@@ -5051,123 +5107,128 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C8EFFCD-CA70-46B8-8E6B-FC87ED018E1A}">
-  <dimension ref="A1:A19"/>
+  <dimension ref="A1:A20"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="17.07421875" customWidth="1"/>
+    <col min="1" max="1" width="22.3828125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="str">
-        <f>[1]Tâches!$A1</f>
+        <f>[2]Tâches!$A1</f>
         <v>Tâches</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="str">
-        <f>[1]Tâches!$A2</f>
+        <f>[2]Tâches!$A2</f>
         <v>Accueil</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="str">
-        <f>[1]Tâches!$A3</f>
+        <f>[2]Tâches!$A3</f>
         <v>Abeilles Ruche</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="str">
-        <f>[1]Tâches!$A4</f>
+        <f>[2]Tâches!$A4</f>
         <v>Ailes</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="str">
-        <f>[1]Tâches!$A5</f>
+        <f>[2]Tâches!$A5</f>
         <v>Bar loges</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="str">
-        <f>[1]Tâches!$A6</f>
+        <f>[2]Tâches!$A6</f>
         <v>Bar public</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="str">
-        <f>[1]Tâches!$A7</f>
+        <f>[2]Tâches!$A7</f>
         <v>Bourdon.ne</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="str">
-        <f>[1]Tâches!$A8</f>
+        <f>[2]Tâches!$A8</f>
         <v>Entrée backstage</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="str">
-        <f>[1]Tâches!$A9</f>
+        <f>[2]Tâches!$A9</f>
         <v>Horaires</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A10" t="str">
-        <f>[1]Tâches!$A10</f>
-        <v>Déambule Gerry</v>
+      <c r="A10" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="str">
-        <f>[1]Tâches!$A11</f>
-        <v>Déambule Colbok</v>
+        <f>[2]Tâches!$A10</f>
+        <v>Déambule Gerry</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="str">
-        <f>[1]Tâches!$A12</f>
-        <v>Déambule Goulus</v>
+        <f>[2]Tâches!$A11</f>
+        <v>Déambule Colbok</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="str">
-        <f>[1]Tâches!$A13</f>
-        <v>Déambule Ko-compagnie</v>
+        <f>[2]Tâches!$A12</f>
+        <v>Déambule Goulus</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="str">
-        <f>[1]Tâches!$A14</f>
-        <v>Déambule Spoutnik</v>
+        <f>[2]Tâches!$A13</f>
+        <v>Déambule Ko-compagnie</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A15" t="str">
-        <f>[1]Tâches!$A15</f>
-        <v>Déambule FBI</v>
+        <f>[2]Tâches!$A14</f>
+        <v>Déambule Spoutnik</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" t="str">
-        <f>[1]Tâches!$A16</f>
-        <v>Tech PCGB</v>
+        <f>[2]Tâches!$A15</f>
+        <v>Déambule FBI</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17" t="str">
-        <f>[1]Tâches!$A17</f>
-        <v>Tech Jacquard</v>
+        <f>[2]Tâches!$A16</f>
+        <v>Tech PCGB</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A18" t="str">
-        <f>[1]Tâches!$A18</f>
-        <v>Tech Muchmuche</v>
+        <f>[2]Tâches!$A17</f>
+        <v>Tech Jacquard</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19" t="str">
-        <f>[1]Tâches!$A19</f>
+        <f>[2]Tâches!$A18</f>
+        <v>Tech Muchmuche</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A20" t="str">
+        <f>[2]Tâches!$A19</f>
         <v>Tech T'es rien…</v>
       </c>
     </row>

--- a/data/shifts_fixes.xlsx
+++ b/data/shifts_fixes.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sschies1\_code\1.09_VScode\06_VoeuxConcerts\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0133B593-55BC-4A02-BC40-98F755DE6FC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EB75E46-24F0-4FDA-BBCA-7337DB391D55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25490" yWindow="1480" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <sheet name="Vendredi" sheetId="5" r:id="rId4"/>
     <sheet name="Samedi" sheetId="6" r:id="rId5"/>
     <sheet name="Dimanche" sheetId="7" r:id="rId6"/>
-    <sheet name="Taches" sheetId="2" r:id="rId7"/>
+    <sheet name="Taches" sheetId="2" state="hidden" r:id="rId7"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId8"/>
@@ -28,7 +28,7 @@
   <definedNames>
     <definedName name="FromArray_1">_xlfn.ANCHORARRAY(Mardi!$A$2)</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterate="1" iterateCount="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -53,30 +53,8 @@
 </connections>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="10">
   <si>
     <t>Nom</t>
   </si>
@@ -100,12 +78,6 @@
   </si>
   <si>
     <t>Tech T'es rien…</t>
-  </si>
-  <si>
-    <t>Bar public</t>
-  </si>
-  <si>
-    <t>Bourdon.ne</t>
   </si>
   <si>
     <t>Stageman</t>
@@ -135,12 +107,48 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -155,16 +163,65 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="20" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="6">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -177,1095 +234,1069 @@
 </styleSheet>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Bénévoles 2026 V2"/>
-      <sheetName val="Drop-downs"/>
-      <sheetName val="Bénévoles_2026"/>
-      <sheetName val="Bénévoles_2025"/>
-      <sheetName val="Appel"/>
-      <sheetName val="Bénévoles_2024"/>
-      <sheetName val="Téléphones_2023"/>
-      <sheetName val="Bénévoles_2022"/>
-      <sheetName val="Bénévoles_2020"/>
-      <sheetName val="Bénévoles_2019NEW (2)"/>
-      <sheetName val="Liste attente 2019"/>
-      <sheetName val="Bénévoles_2019"/>
-      <sheetName val="Bénévoles_2018"/>
-      <sheetName val="Bénévoles_17"/>
-      <sheetName val="Bénévoles_16"/>
-      <sheetName val="Bénévoles_15"/>
-      <sheetName val="Bénévoles_14"/>
-      <sheetName val="Bénévoles_13"/>
-      <sheetName val="Présence_16"/>
-      <sheetName val="Téléphones"/>
-      <sheetName val="Tél__grande_liste"/>
-      <sheetName val="Concerts_p1"/>
-      <sheetName val="Concerts_p2"/>
-      <sheetName val="Liste__prénom"/>
-      <sheetName val="Bénévoles_12"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="1">
-          <cell r="B1"/>
-          <cell r="E1"/>
-          <cell r="F1"/>
-        </row>
-        <row r="2">
-          <cell r="B2"/>
-          <cell r="E2"/>
-          <cell r="F2"/>
-        </row>
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>In</v>
-          </cell>
-          <cell r="E3" t="str">
-            <v>NOM</v>
-          </cell>
-          <cell r="F3" t="str">
-            <v>PRÉNOM</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="B4" t="b">
-            <v>1</v>
-          </cell>
-          <cell r="E4" t="str">
-            <v>Bouvet</v>
-          </cell>
-          <cell r="F4" t="str">
-            <v>Agathe</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="B5" t="b">
-            <v>1</v>
-          </cell>
-          <cell r="E5" t="str">
-            <v>Bulka</v>
-          </cell>
-          <cell r="F5" t="str">
-            <v>Alegria Lily</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="B6" t="b">
-            <v>1</v>
-          </cell>
-          <cell r="E6" t="str">
-            <v>Bastian</v>
-          </cell>
-          <cell r="F6" t="str">
-            <v>Alexandra</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="B7" t="b">
-            <v>1</v>
-          </cell>
-          <cell r="E7" t="str">
-            <v>L'Horset</v>
-          </cell>
-          <cell r="F7" t="str">
-            <v>Alice</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="B8" t="b">
-            <v>1</v>
-          </cell>
-          <cell r="E8" t="str">
-            <v>Ledru</v>
-          </cell>
-          <cell r="F8" t="str">
-            <v>Analou</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="B9" t="b">
-            <v>1</v>
-          </cell>
-          <cell r="E9" t="str">
-            <v>Mallet</v>
-          </cell>
-          <cell r="F9" t="str">
-            <v>Anna</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="B10" t="b">
-            <v>1</v>
-          </cell>
-          <cell r="E10" t="str">
-            <v>Malric</v>
-          </cell>
-          <cell r="F10" t="str">
-            <v>Annouk</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="B11" t="b">
-            <v>1</v>
-          </cell>
-          <cell r="E11" t="str">
-            <v>Noël</v>
-          </cell>
-          <cell r="F11" t="str">
-            <v>Antonin</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="B12" t="b">
-            <v>1</v>
-          </cell>
-          <cell r="E12" t="str">
-            <v>Tessier</v>
-          </cell>
-          <cell r="F12" t="str">
-            <v>Arsène</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="B13" t="b">
-            <v>1</v>
-          </cell>
-          <cell r="E13" t="str">
-            <v>Uldry</v>
-          </cell>
-          <cell r="F13" t="str">
-            <v>Arthur</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="B14" t="b">
-            <v>1</v>
-          </cell>
-          <cell r="E14" t="str">
-            <v>Marchand</v>
-          </cell>
-          <cell r="F14" t="str">
-            <v>Athénaé</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="B15" t="b">
-            <v>1</v>
-          </cell>
-          <cell r="E15" t="str">
-            <v>Magerand</v>
-          </cell>
-          <cell r="F15" t="str">
-            <v>Auxence</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="B16" t="b">
-            <v>1</v>
-          </cell>
-          <cell r="E16" t="str">
-            <v>Baruch</v>
-          </cell>
-          <cell r="F16" t="str">
-            <v>Ava</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="B17" t="b">
-            <v>1</v>
-          </cell>
-          <cell r="E17" t="str">
-            <v>Detrain</v>
-          </cell>
-          <cell r="F17" t="str">
-            <v>Benoît</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="B18" t="b">
-            <v>1</v>
-          </cell>
-          <cell r="E18" t="str">
-            <v>Meige</v>
-          </cell>
-          <cell r="F18" t="str">
-            <v>Corentin</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="B19" t="b">
-            <v>1</v>
-          </cell>
-          <cell r="E19" t="str">
-            <v>De Filippo</v>
-          </cell>
-          <cell r="F19" t="str">
-            <v>Emma</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="B20" t="b">
-            <v>1</v>
-          </cell>
-          <cell r="E20" t="str">
-            <v>Maître</v>
-          </cell>
-          <cell r="F20" t="str">
-            <v>Enzo</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="B21" t="b">
-            <v>1</v>
-          </cell>
-          <cell r="E21" t="str">
-            <v>Prouvost</v>
-          </cell>
-          <cell r="F21" t="str">
-            <v>Eugénie</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="B22" t="b">
-            <v>1</v>
-          </cell>
-          <cell r="E22" t="str">
-            <v xml:space="preserve">Rakotonandrasana </v>
-          </cell>
-          <cell r="F22" t="str">
-            <v>Iris</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="B23" t="b">
-            <v>1</v>
-          </cell>
-          <cell r="E23" t="str">
-            <v>Bürgisser</v>
-          </cell>
-          <cell r="F23" t="str">
-            <v>Jamilah</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="B24" t="b">
-            <v>1</v>
-          </cell>
-          <cell r="E24" t="str">
-            <v>Ruscio</v>
-          </cell>
-          <cell r="F24" t="str">
-            <v>Jolan</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="B25" t="b">
-            <v>1</v>
-          </cell>
-          <cell r="E25" t="str">
-            <v>Wuilloud</v>
-          </cell>
-          <cell r="F25" t="str">
-            <v xml:space="preserve">Jonas </v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="B26" t="b">
-            <v>1</v>
-          </cell>
-          <cell r="E26" t="str">
-            <v>Pirolley</v>
-          </cell>
-          <cell r="F26" t="str">
-            <v>Jules</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="B27" t="b">
-            <v>1</v>
-          </cell>
-          <cell r="E27" t="str">
-            <v>Chavaillaz</v>
-          </cell>
-          <cell r="F27" t="str">
-            <v>Julie</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="B28" t="b">
-            <v>1</v>
-          </cell>
-          <cell r="E28" t="str">
-            <v>Oeschger</v>
-          </cell>
-          <cell r="F28" t="str">
-            <v>Kristel</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="B29" t="b">
-            <v>1</v>
-          </cell>
-          <cell r="E29" t="str">
-            <v>Baltzinger</v>
-          </cell>
-          <cell r="F29" t="str">
-            <v>Léa</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="B30" t="b">
-            <v>1</v>
-          </cell>
-          <cell r="E30" t="str">
-            <v>Chambaz</v>
-          </cell>
-          <cell r="F30" t="str">
-            <v>Léa</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="B31" t="b">
-            <v>1</v>
-          </cell>
-          <cell r="E31" t="str">
-            <v>Ledru</v>
-          </cell>
-          <cell r="F31" t="str">
-            <v>Lina-Rosa</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="B32" t="b">
-            <v>1</v>
-          </cell>
-          <cell r="E32" t="str">
-            <v>Jaquet</v>
-          </cell>
-          <cell r="F32" t="str">
-            <v>Lisa</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="B33" t="b">
-            <v>1</v>
-          </cell>
-          <cell r="E33" t="str">
-            <v>Magnin</v>
-          </cell>
-          <cell r="F33" t="str">
-            <v>Lisa</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="B34" t="b">
-            <v>1</v>
-          </cell>
-          <cell r="E34" t="str">
-            <v>Cardis</v>
-          </cell>
-          <cell r="F34" t="str">
-            <v>Louis</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="B35" t="b">
-            <v>1</v>
-          </cell>
-          <cell r="E35" t="str">
-            <v>Post</v>
-          </cell>
-          <cell r="F35" t="str">
-            <v>Louis</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="B36" t="b">
-            <v>1</v>
-          </cell>
-          <cell r="E36" t="str">
-            <v>Blanchard</v>
-          </cell>
-          <cell r="F36" t="str">
-            <v>Louise</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="B37" t="b">
-            <v>1</v>
-          </cell>
-          <cell r="E37" t="str">
-            <v>Chastroux</v>
-          </cell>
-          <cell r="F37" t="str">
-            <v>Lucas</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="B38" t="b">
-            <v>1</v>
-          </cell>
-          <cell r="E38" t="str">
-            <v>Meyer</v>
-          </cell>
-          <cell r="F38" t="str">
-            <v>Lucie</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="B39" t="b">
-            <v>1</v>
-          </cell>
-          <cell r="E39" t="str">
-            <v>Ménétrey</v>
-          </cell>
-          <cell r="F39" t="str">
-            <v>Maëlan</v>
-          </cell>
-        </row>
-        <row r="40">
-          <cell r="B40" t="b">
-            <v>1</v>
-          </cell>
-          <cell r="E40" t="str">
-            <v>Chambaz</v>
-          </cell>
-          <cell r="F40" t="str">
-            <v>Maëlle</v>
-          </cell>
-        </row>
-        <row r="41">
-          <cell r="B41" t="b">
-            <v>1</v>
-          </cell>
-          <cell r="E41" t="str">
-            <v>Felix</v>
-          </cell>
-          <cell r="F41" t="str">
-            <v>Marius</v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="B42" t="b">
-            <v>1</v>
-          </cell>
-          <cell r="E42" t="str">
-            <v>Ledru</v>
-          </cell>
-          <cell r="F42" t="str">
-            <v>Marot</v>
-          </cell>
-        </row>
-        <row r="43">
-          <cell r="B43" t="b">
-            <v>1</v>
-          </cell>
-          <cell r="E43" t="str">
-            <v>Cuinet</v>
-          </cell>
-          <cell r="F43" t="str">
-            <v>Mathis</v>
-          </cell>
-        </row>
-        <row r="44">
-          <cell r="B44" t="b">
-            <v>1</v>
-          </cell>
-          <cell r="E44" t="str">
-            <v>Gavin</v>
-          </cell>
-          <cell r="F44" t="str">
-            <v>Matteo</v>
-          </cell>
-        </row>
-        <row r="45">
-          <cell r="B45" t="b">
-            <v>1</v>
-          </cell>
-          <cell r="E45" t="str">
-            <v>Debray</v>
-          </cell>
-          <cell r="F45" t="str">
-            <v>Maxime</v>
-          </cell>
-        </row>
-        <row r="46">
-          <cell r="B46" t="b">
-            <v>1</v>
-          </cell>
-          <cell r="E46" t="str">
-            <v>Corbelli</v>
-          </cell>
-          <cell r="F46" t="str">
-            <v>Maya</v>
-          </cell>
-        </row>
-        <row r="47">
-          <cell r="B47" t="b">
-            <v>1</v>
-          </cell>
-          <cell r="E47" t="str">
-            <v>Pasche</v>
-          </cell>
-          <cell r="F47" t="str">
-            <v>Mickaël</v>
-          </cell>
-        </row>
-        <row r="48">
-          <cell r="B48" t="b">
-            <v>1</v>
-          </cell>
-          <cell r="E48" t="str">
-            <v>Fargues</v>
-          </cell>
-          <cell r="F48" t="str">
-            <v>Morgana</v>
-          </cell>
-        </row>
-        <row r="49">
-          <cell r="B49" t="b">
-            <v>1</v>
-          </cell>
-          <cell r="E49" t="str">
-            <v>Scyboz (Lambelet)</v>
-          </cell>
-          <cell r="F49" t="str">
-            <v>Morgane</v>
-          </cell>
-        </row>
-        <row r="50">
-          <cell r="B50" t="b">
-            <v>1</v>
-          </cell>
-          <cell r="E50" t="str">
-            <v>Koux</v>
-          </cell>
-          <cell r="F50" t="str">
-            <v>Nathalia</v>
-          </cell>
-        </row>
-        <row r="51">
-          <cell r="B51" t="b">
-            <v>1</v>
-          </cell>
-          <cell r="E51" t="str">
-            <v>Cherpillod</v>
-          </cell>
-          <cell r="F51" t="str">
-            <v>Noah</v>
-          </cell>
-        </row>
-        <row r="52">
-          <cell r="B52" t="b">
-            <v>1</v>
-          </cell>
-          <cell r="E52" t="str">
-            <v>Chambaz</v>
-          </cell>
-          <cell r="F52" t="str">
-            <v>Patrick</v>
-          </cell>
-        </row>
-        <row r="53">
-          <cell r="B53" t="b">
-            <v>1</v>
-          </cell>
-          <cell r="E53" t="str">
-            <v>Assaoui</v>
-          </cell>
-          <cell r="F53" t="str">
-            <v>Rama</v>
-          </cell>
-        </row>
-        <row r="54">
-          <cell r="B54" t="b">
-            <v>1</v>
-          </cell>
-          <cell r="E54" t="str">
-            <v>Lacroze</v>
-          </cell>
-          <cell r="F54" t="str">
-            <v>Raphaël</v>
-          </cell>
-        </row>
-        <row r="55">
-          <cell r="B55" t="b">
-            <v>1</v>
-          </cell>
-          <cell r="E55" t="str">
-            <v>Neidhart</v>
-          </cell>
-          <cell r="F55" t="str">
-            <v>Raphaëlle</v>
-          </cell>
-        </row>
-        <row r="56">
-          <cell r="B56" t="b">
-            <v>1</v>
-          </cell>
-          <cell r="E56" t="str">
-            <v xml:space="preserve">Lanni </v>
-          </cell>
-          <cell r="F56" t="str">
-            <v>Roxanne</v>
-          </cell>
-        </row>
-        <row r="57">
-          <cell r="B57" t="b">
-            <v>1</v>
-          </cell>
-          <cell r="E57" t="str">
-            <v>Schiesser</v>
-          </cell>
-          <cell r="F57" t="str">
-            <v>Sébastien</v>
-          </cell>
-        </row>
-        <row r="58">
-          <cell r="B58" t="b">
-            <v>1</v>
-          </cell>
-          <cell r="E58" t="str">
-            <v>Lambelet</v>
-          </cell>
-          <cell r="F58" t="str">
-            <v>Simon</v>
-          </cell>
-        </row>
-        <row r="59">
-          <cell r="B59" t="b">
-            <v>1</v>
-          </cell>
-          <cell r="E59" t="str">
-            <v>Cyprien</v>
-          </cell>
-          <cell r="F59" t="str">
-            <v>Theo</v>
-          </cell>
-        </row>
-        <row r="60">
-          <cell r="B60" t="b">
-            <v>1</v>
-          </cell>
-          <cell r="E60" t="str">
-            <v>Clerici</v>
-          </cell>
-          <cell r="F60" t="str">
-            <v>Thibault</v>
-          </cell>
-        </row>
-        <row r="61">
-          <cell r="B61" t="b">
-            <v>1</v>
-          </cell>
-          <cell r="E61" t="str">
-            <v>Ménétrey</v>
-          </cell>
-          <cell r="F61" t="str">
-            <v>Titouan</v>
-          </cell>
-        </row>
-        <row r="62">
-          <cell r="B62" t="b">
-            <v>1</v>
-          </cell>
-          <cell r="E62" t="str">
-            <v>Clerici</v>
-          </cell>
-          <cell r="F62" t="str">
-            <v>Tristan</v>
-          </cell>
-        </row>
-        <row r="63">
-          <cell r="B63" t="b">
-            <v>1</v>
-          </cell>
-          <cell r="E63" t="str">
-            <v>Bally</v>
-          </cell>
-          <cell r="F63" t="str">
-            <v>Yann</v>
-          </cell>
-        </row>
-        <row r="64">
-          <cell r="B64" t="b">
-            <v>1</v>
-          </cell>
-          <cell r="E64" t="str">
-            <v>Ménétrey</v>
-          </cell>
-          <cell r="F64" t="str">
-            <v>Ysatis</v>
-          </cell>
-        </row>
-        <row r="65">
-          <cell r="B65" t="b">
-            <v>1</v>
-          </cell>
-          <cell r="E65" t="str">
-            <v>Ménard</v>
-          </cell>
-          <cell r="F65" t="str">
-            <v>Mireille</v>
-          </cell>
-        </row>
-        <row r="66">
-          <cell r="B66" t="b">
-            <v>0</v>
-          </cell>
-          <cell r="E66" t="str">
-            <v>Delassus</v>
-          </cell>
-          <cell r="F66" t="str">
-            <v>Frank</v>
-          </cell>
-        </row>
-        <row r="67">
-          <cell r="B67" t="b">
-            <v>0</v>
-          </cell>
-          <cell r="E67" t="str">
-            <v>Rieger</v>
-          </cell>
-          <cell r="F67" t="str">
-            <v>Maya</v>
-          </cell>
-        </row>
-        <row r="68">
-          <cell r="B68" t="b">
-            <v>0</v>
-          </cell>
-          <cell r="E68" t="str">
-            <v>Michel</v>
-          </cell>
-          <cell r="F68" t="str">
-            <v>Mehdi</v>
-          </cell>
-        </row>
-        <row r="69">
-          <cell r="B69" t="b">
-            <v>0</v>
-          </cell>
-          <cell r="E69" t="str">
-            <v>Pieper</v>
-          </cell>
-          <cell r="F69" t="str">
-            <v>Giulia</v>
-          </cell>
-        </row>
-        <row r="70">
-          <cell r="B70" t="b">
-            <v>0</v>
-          </cell>
-          <cell r="E70" t="str">
-            <v>Durand</v>
-          </cell>
-          <cell r="F70" t="str">
-            <v>Isidore</v>
-          </cell>
-        </row>
-        <row r="71">
-          <cell r="B71" t="b">
-            <v>0</v>
-          </cell>
-          <cell r="E71" t="str">
-            <v>Lemay</v>
-          </cell>
-          <cell r="F71" t="str">
-            <v>Mae</v>
-          </cell>
-        </row>
-        <row r="72">
-          <cell r="B72" t="b">
-            <v>0</v>
-          </cell>
-          <cell r="E72"/>
-          <cell r="F72" t="str">
-            <v>Michelle-Evy</v>
-          </cell>
-        </row>
-        <row r="73">
-          <cell r="B73" t="b">
-            <v>0</v>
-          </cell>
-          <cell r="E73" t="str">
-            <v>Bonay</v>
-          </cell>
-          <cell r="F73" t="str">
-            <v>Paul</v>
-          </cell>
-        </row>
-        <row r="74">
-          <cell r="B74" t="b">
-            <v>0</v>
-          </cell>
-          <cell r="E74" t="str">
-            <v>Lagier</v>
-          </cell>
-          <cell r="F74" t="str">
-            <v>Tician</v>
-          </cell>
-        </row>
-        <row r="75">
-          <cell r="B75" t="b">
-            <v>0</v>
-          </cell>
-          <cell r="E75" t="str">
-            <v>Carrière</v>
-          </cell>
-          <cell r="F75" t="str">
-            <v>Zellie</v>
-          </cell>
-        </row>
-        <row r="76">
-          <cell r="B76" t="b">
-            <v>0</v>
-          </cell>
-          <cell r="E76" t="str">
-            <v>Goumaz</v>
-          </cell>
-          <cell r="F76" t="str">
-            <v>Alexandre</v>
-          </cell>
-        </row>
-        <row r="77">
-          <cell r="B77" t="b">
-            <v>0</v>
-          </cell>
-          <cell r="E77" t="str">
-            <v xml:space="preserve">Lanni </v>
-          </cell>
-          <cell r="F77" t="str">
-            <v>Brian</v>
-          </cell>
-        </row>
-        <row r="78">
-          <cell r="B78" t="b">
-            <v>0</v>
-          </cell>
-          <cell r="E78" t="str">
-            <v>Pernet</v>
-          </cell>
-          <cell r="F78" t="str">
-            <v>Célia</v>
-          </cell>
-        </row>
-        <row r="79">
-          <cell r="B79" t="b">
-            <v>0</v>
-          </cell>
-          <cell r="E79" t="str">
-            <v>Cardinaux</v>
-          </cell>
-          <cell r="F79" t="str">
-            <v>Christian</v>
-          </cell>
-        </row>
-        <row r="80">
-          <cell r="B80" t="b">
-            <v>0</v>
-          </cell>
-          <cell r="E80" t="str">
-            <v>Gebhardt</v>
-          </cell>
-          <cell r="F80" t="str">
-            <v>David</v>
-          </cell>
-        </row>
-        <row r="81">
-          <cell r="B81" t="b">
-            <v>0</v>
-          </cell>
-          <cell r="E81" t="str">
-            <v>Aigner</v>
-          </cell>
-          <cell r="F81" t="str">
-            <v>David</v>
-          </cell>
-        </row>
-        <row r="82">
-          <cell r="B82" t="b">
-            <v>0</v>
-          </cell>
-          <cell r="E82" t="str">
-            <v>Requena</v>
-          </cell>
-          <cell r="F82" t="str">
-            <v>Elisa</v>
-          </cell>
-        </row>
-        <row r="83">
-          <cell r="B83" t="b">
-            <v>0</v>
-          </cell>
-          <cell r="E83" t="str">
-            <v>Déchanez</v>
-          </cell>
-          <cell r="F83" t="str">
-            <v>Léa</v>
-          </cell>
-        </row>
-        <row r="84">
-          <cell r="B84" t="b">
-            <v>0</v>
-          </cell>
-          <cell r="E84" t="str">
-            <v>Bonduel</v>
-          </cell>
-          <cell r="F84" t="str">
-            <v>Lola</v>
-          </cell>
-        </row>
-        <row r="85">
-          <cell r="B85" t="b">
-            <v>0</v>
-          </cell>
-          <cell r="E85" t="str">
-            <v>Ledru</v>
-          </cell>
-          <cell r="F85" t="str">
-            <v>Loucas</v>
-          </cell>
-        </row>
-        <row r="86">
-          <cell r="B86" t="b">
-            <v>0</v>
-          </cell>
-          <cell r="E86" t="str">
-            <v>Deschoux</v>
-          </cell>
-          <cell r="F86" t="str">
-            <v>Louise</v>
-          </cell>
-        </row>
-        <row r="87">
-          <cell r="B87" t="b">
-            <v>0</v>
-          </cell>
-          <cell r="E87" t="str">
-            <v>Schlapbach</v>
-          </cell>
-          <cell r="F87" t="str">
-            <v>Naomé</v>
-          </cell>
-        </row>
-        <row r="88">
-          <cell r="B88" t="b">
-            <v>0</v>
-          </cell>
-          <cell r="E88" t="str">
-            <v>Lugeon</v>
-          </cell>
-          <cell r="F88" t="str">
-            <v>Nicolas</v>
-          </cell>
-        </row>
-        <row r="89">
-          <cell r="B89" t="b">
-            <v>0</v>
-          </cell>
-          <cell r="E89" t="str">
-            <v>Fogo</v>
-          </cell>
-          <cell r="F89" t="str">
-            <v>Noé</v>
-          </cell>
-        </row>
-        <row r="90">
-          <cell r="B90" t="b">
-            <v>0</v>
-          </cell>
-          <cell r="E90" t="str">
-            <v>de Schoulepnikoff</v>
-          </cell>
-          <cell r="F90" t="str">
-            <v>Noémie</v>
-          </cell>
-        </row>
-        <row r="91">
-          <cell r="B91" t="b">
-            <v>0</v>
-          </cell>
-          <cell r="E91" t="str">
-            <v>Bouduban</v>
-          </cell>
-          <cell r="F91" t="str">
-            <v>Pénélope</v>
-          </cell>
-        </row>
-        <row r="92">
-          <cell r="B92" t="b">
-            <v>0</v>
-          </cell>
-          <cell r="E92" t="str">
-            <v>Trieu</v>
-          </cell>
-          <cell r="F92" t="str">
-            <v>Raimond</v>
-          </cell>
-        </row>
-        <row r="93">
-          <cell r="B93" t="b">
-            <v>0</v>
-          </cell>
-          <cell r="E93"/>
-          <cell r="F93" t="str">
-            <v>Ramón</v>
-          </cell>
-        </row>
-        <row r="94">
-          <cell r="B94" t="b">
-            <v>0</v>
-          </cell>
-          <cell r="E94" t="str">
-            <v>Aigner</v>
-          </cell>
-          <cell r="F94" t="str">
-            <v>Robert</v>
-          </cell>
-        </row>
-        <row r="95">
-          <cell r="B95"/>
-          <cell r="E95"/>
-          <cell r="F95"/>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
-      <sheetData sheetId="19"/>
-      <sheetData sheetId="20"/>
-      <sheetData sheetId="21"/>
-      <sheetData sheetId="22"/>
-      <sheetData sheetId="23"/>
-      <sheetData sheetId="24"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>182216</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>17868</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>176695</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E68F3CA9-5645-4975-92BB-EEE62CE76311}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4897783" y="182216"/>
+          <a:ext cx="3275694" cy="2909957"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-GB" sz="2400" b="1" u="sng"/>
+            <a:t>Shifts fixes</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="2400" b="1" u="sng" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" indent="-171450">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:endParaRPr lang="en-GB" sz="1100" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" indent="-171450">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0"/>
+            <a:t>Cette liste est faite pour les personnes qui sont assignées à une compagnie (accueil technique ou déambulation), indépendamment des autres shifts du jour.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" indent="-171450">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0"/>
+            <a:t>Les responsables de secteur qui s'auto-gèrent se trouvent dans le fichier "personnes.xlsx"</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" indent="-171450">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0"/>
+            <a:t>Cette liste est donc sensée rester en grande partie vide!</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" indent="-171450">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:endParaRPr lang="en-GB" sz="1100" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="1" baseline="0"/>
+            <a:t>Utilisation :</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" indent="-171450">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0"/>
+            <a:t>Sélectionner une tâche dans la liste</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" indent="-171450">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0"/>
+            <a:t>Entrer les heures de début et de fin</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>17868</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>43503</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{03FA8ABF-1F62-4F59-AE1E-A6C578C77DEB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4897783" y="182217"/>
+          <a:ext cx="3275694" cy="2776764"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-GB" sz="2400" b="1" u="sng"/>
+            <a:t>Shifts fixes</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="2400" b="1" u="sng" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" indent="-171450">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:endParaRPr lang="en-GB" sz="1100" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" indent="-171450">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0"/>
+            <a:t>Cette liste est faite pour les personnes qui sont assignées à une compagnie (accueil technique ou déambulation), indépendamment des autres shifts du jour.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" indent="-171450">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0"/>
+            <a:t>Les responsables de secteur qui s'auto-gèrent se trouvent dans le fichier "personnes.xlsx"</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" indent="-171450">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0"/>
+            <a:t>Cette liste est donc sensée rester en grande partie vide!</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" indent="-171450">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:endParaRPr lang="en-GB" sz="1100" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="1" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Utilisation :</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" indent="-171450">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Sélectionner une tâche dans la liste</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" indent="-171450">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Entrer les heures de début et de fin</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>17868</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>43503</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F3C4576-005E-477F-9FB0-561A61179896}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4897783" y="182217"/>
+          <a:ext cx="3275694" cy="2776764"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent3">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-GB" sz="2400" b="1" u="sng"/>
+            <a:t>Shifts fixes</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="2400" b="1" u="sng" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" indent="-171450">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:endParaRPr lang="en-GB" sz="1100" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" indent="-171450">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0"/>
+            <a:t>Cette liste est faite pour les personnes qui sont assignées à une compagnie (accueil technique ou déambulation), indépendamment des autres shifts du jour.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" indent="-171450">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0"/>
+            <a:t>Les responsables de secteur qui s'auto-gèrent se trouvent dans le fichier "personnes.xlsx"</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" indent="-171450">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0"/>
+            <a:t>Cette liste est donc sensée rester en grande partie vide!</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" indent="-171450">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:endParaRPr lang="en-GB" sz="1100" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="1" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Utilisation :</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" indent="-171450">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Sélectionner une tâche dans la liste</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" indent="-171450">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Entrer les heures de début et de fin</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>17868</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>43503</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{98ED8FF9-16FC-4183-B494-7134C84FFE7C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4897783" y="182217"/>
+          <a:ext cx="3275694" cy="2776764"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent4">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-GB" sz="2400" b="1" u="sng"/>
+            <a:t>Shifts fixes</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="2400" b="1" u="sng" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" indent="-171450">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:endParaRPr lang="en-GB" sz="1100" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" indent="-171450">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0"/>
+            <a:t>Cette liste est faite pour les personnes qui sont assignées à une compagnie (accueil technique ou déambulation), indépendamment des autres shifts du jour.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" indent="-171450">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0"/>
+            <a:t>Les responsables de secteur qui s'auto-gèrent se trouvent dans le fichier "personnes.xlsx"</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" indent="-171450">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0"/>
+            <a:t>Cette liste est donc sensée rester en grande partie vide!</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" indent="-171450">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:endParaRPr lang="en-GB" sz="1100" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="1" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Utilisation :</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" indent="-171450">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Sélectionner une tâche dans la liste</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" indent="-171450">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Entrer les heures de début et de fin</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>17868</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>43503</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B66BD9EE-FE00-4EF5-B494-A062B5E6728B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4897783" y="182217"/>
+          <a:ext cx="3275694" cy="2776764"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent6">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-GB" sz="2400" b="1" u="sng"/>
+            <a:t>Shifts fixes</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="2400" b="1" u="sng" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" indent="-171450">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:endParaRPr lang="en-GB" sz="1100" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" indent="-171450">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0"/>
+            <a:t>Cette liste est faite pour les personnes qui sont assignées à une compagnie (accueil technique ou déambulation), indépendamment des autres shifts du jour.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" indent="-171450">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0"/>
+            <a:t>Les responsables de secteur qui s'auto-gèrent se trouvent dans le fichier "personnes.xlsx"</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" indent="-171450">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0"/>
+            <a:t>Cette liste est donc sensée rester en grande partie vide!</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" indent="-171450">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:endParaRPr lang="en-GB" sz="1100" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="1" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Utilisation :</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" indent="-171450">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Sélectionner une tâche dans la liste</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" indent="-171450">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Entrer les heures de début et de fin</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>17868</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>43503</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5BE0E683-1DD5-4497-98A8-54476C3CE834}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4897783" y="182217"/>
+          <a:ext cx="3275694" cy="2776764"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-GB" sz="2400" b="1" u="sng"/>
+            <a:t>Shifts fixes</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="2400" b="1" u="sng" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" indent="-171450">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:endParaRPr lang="en-GB" sz="1100" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" indent="-171450">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0"/>
+            <a:t>Cette liste est faite pour les personnes qui sont assignées à une compagnie (accueil technique ou déambulation), indépendamment des autres shifts du jour.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" indent="-171450">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0"/>
+            <a:t>Les responsables de secteur qui s'auto-gèrent se trouvent dans le fichier "personnes.xlsx"</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" indent="-171450">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0"/>
+            <a:t>Cette liste est donc sensée rester en grande partie vide!</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" indent="-171450">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:endParaRPr lang="en-GB" sz="1100" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="1" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Utilisation :</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" indent="-171450">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Sélectionner une tâche dans la liste</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="171450" indent="-171450">
+            <a:buFont typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Entrer les heures de début et de fin</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1281,12 +1312,12 @@
       <sheetName val="Tâches"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
       <sheetData sheetId="6">
         <row r="1">
           <cell r="A1" t="str">
@@ -1384,6 +1415,529 @@
           </cell>
         </row>
       </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Personnes"/>
+      <sheetName val="LOOKUP"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="A2" t="str">
+            <v>Bouvet</v>
+          </cell>
+          <cell r="B2" t="str">
+            <v>Agathe</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="A3" t="str">
+            <v>Bulka</v>
+          </cell>
+          <cell r="B3" t="str">
+            <v>Alegria Lily</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4" t="str">
+            <v>Bastian</v>
+          </cell>
+          <cell r="B4" t="str">
+            <v>Alexandra</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5" t="str">
+            <v>L'Horset</v>
+          </cell>
+          <cell r="B5" t="str">
+            <v>Alice</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6" t="str">
+            <v>Ledru</v>
+          </cell>
+          <cell r="B6" t="str">
+            <v>Analou</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7" t="str">
+            <v>Mallet</v>
+          </cell>
+          <cell r="B7" t="str">
+            <v>Anna</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8" t="str">
+            <v>Malric</v>
+          </cell>
+          <cell r="B8" t="str">
+            <v>Annouk</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9" t="str">
+            <v>Noël</v>
+          </cell>
+          <cell r="B9" t="str">
+            <v>Antonin</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10" t="str">
+            <v>Tessier</v>
+          </cell>
+          <cell r="B10" t="str">
+            <v>Arsène</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11" t="str">
+            <v>Uldry</v>
+          </cell>
+          <cell r="B11" t="str">
+            <v>Arthur</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="A12" t="str">
+            <v>Marchand</v>
+          </cell>
+          <cell r="B12" t="str">
+            <v>Athénaé</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="A13" t="str">
+            <v>Magerand</v>
+          </cell>
+          <cell r="B13" t="str">
+            <v>Auxence</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="A14" t="str">
+            <v>Baruch</v>
+          </cell>
+          <cell r="B14" t="str">
+            <v>Ava</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="A15" t="str">
+            <v>Detrain</v>
+          </cell>
+          <cell r="B15" t="str">
+            <v>Benoît</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="A16" t="str">
+            <v>Meige</v>
+          </cell>
+          <cell r="B16" t="str">
+            <v>Corentin</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="A17" t="str">
+            <v>De Filippo</v>
+          </cell>
+          <cell r="B17" t="str">
+            <v>Emma</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="A18" t="str">
+            <v>Maître</v>
+          </cell>
+          <cell r="B18" t="str">
+            <v>Enzo</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="A19" t="str">
+            <v>Prouvost</v>
+          </cell>
+          <cell r="B19" t="str">
+            <v>Eugénie</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="A20" t="str">
+            <v xml:space="preserve">Rakotonandrasana </v>
+          </cell>
+          <cell r="B20" t="str">
+            <v>Iris</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="A21" t="str">
+            <v>Bürgisser</v>
+          </cell>
+          <cell r="B21" t="str">
+            <v>Jamilah</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="A22" t="str">
+            <v>Ruscio</v>
+          </cell>
+          <cell r="B22" t="str">
+            <v>Jolan</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="A23" t="str">
+            <v>Wuilloud</v>
+          </cell>
+          <cell r="B23" t="str">
+            <v xml:space="preserve">Jonas </v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="A24" t="str">
+            <v>Pirolley</v>
+          </cell>
+          <cell r="B24" t="str">
+            <v>Jules</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="A25" t="str">
+            <v>Chavaillaz</v>
+          </cell>
+          <cell r="B25" t="str">
+            <v>Julie</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="A26" t="str">
+            <v>Oeschger</v>
+          </cell>
+          <cell r="B26" t="str">
+            <v>Kristel</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="A27" t="str">
+            <v>Baltzinger</v>
+          </cell>
+          <cell r="B27" t="str">
+            <v>Léa</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="A28" t="str">
+            <v>Chambaz</v>
+          </cell>
+          <cell r="B28" t="str">
+            <v>Léa</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="A29" t="str">
+            <v>Ledru</v>
+          </cell>
+          <cell r="B29" t="str">
+            <v>Lina-Rosa</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="A30" t="str">
+            <v>Jaquet</v>
+          </cell>
+          <cell r="B30" t="str">
+            <v>Lisa</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="A31" t="str">
+            <v>Magnin</v>
+          </cell>
+          <cell r="B31" t="str">
+            <v>Lisa</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="A32" t="str">
+            <v>Cardis</v>
+          </cell>
+          <cell r="B32" t="str">
+            <v>Louis</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="A33" t="str">
+            <v>Post</v>
+          </cell>
+          <cell r="B33" t="str">
+            <v>Louis</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="A34" t="str">
+            <v>Blanchard</v>
+          </cell>
+          <cell r="B34" t="str">
+            <v>Louise</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="A35" t="str">
+            <v>Chastroux</v>
+          </cell>
+          <cell r="B35" t="str">
+            <v>Lucas</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="A36" t="str">
+            <v>Meyer</v>
+          </cell>
+          <cell r="B36" t="str">
+            <v>Lucie</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="A37" t="str">
+            <v>Ménétrey</v>
+          </cell>
+          <cell r="B37" t="str">
+            <v>Maëlan</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="A38" t="str">
+            <v>Chambaz</v>
+          </cell>
+          <cell r="B38" t="str">
+            <v>Maëlle</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="A39" t="str">
+            <v>Felix</v>
+          </cell>
+          <cell r="B39" t="str">
+            <v>Marius</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="A40" t="str">
+            <v>Ledru</v>
+          </cell>
+          <cell r="B40" t="str">
+            <v>Marot</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="A41" t="str">
+            <v>Cuinet</v>
+          </cell>
+          <cell r="B41" t="str">
+            <v>Mathis</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="A42" t="str">
+            <v>Gavin</v>
+          </cell>
+          <cell r="B42" t="str">
+            <v>Matteo</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="A43" t="str">
+            <v>Debray</v>
+          </cell>
+          <cell r="B43" t="str">
+            <v>Maxime</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="A44" t="str">
+            <v>Corbelli</v>
+          </cell>
+          <cell r="B44" t="str">
+            <v>Maya</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="A45" t="str">
+            <v>Pasche</v>
+          </cell>
+          <cell r="B45" t="str">
+            <v>Mickaël</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="A46" t="str">
+            <v>Fargues</v>
+          </cell>
+          <cell r="B46" t="str">
+            <v>Morgana</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="A47" t="str">
+            <v>Scyboz (Lambelet)</v>
+          </cell>
+          <cell r="B47" t="str">
+            <v>Morgane</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="A48" t="str">
+            <v>Koux</v>
+          </cell>
+          <cell r="B48" t="str">
+            <v>Nathalia</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="A49" t="str">
+            <v>Cherpillod</v>
+          </cell>
+          <cell r="B49" t="str">
+            <v>Noah</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="A50" t="str">
+            <v>Chambaz</v>
+          </cell>
+          <cell r="B50" t="str">
+            <v>Patrick</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="A51" t="str">
+            <v>Assaoui</v>
+          </cell>
+          <cell r="B51" t="str">
+            <v>Rama</v>
+          </cell>
+        </row>
+        <row r="52">
+          <cell r="A52" t="str">
+            <v>Lacroze</v>
+          </cell>
+          <cell r="B52" t="str">
+            <v>Raphaël</v>
+          </cell>
+        </row>
+        <row r="53">
+          <cell r="A53" t="str">
+            <v>Neidhart</v>
+          </cell>
+          <cell r="B53" t="str">
+            <v>Raphaëlle</v>
+          </cell>
+        </row>
+        <row r="54">
+          <cell r="A54" t="str">
+            <v xml:space="preserve">Lanni </v>
+          </cell>
+          <cell r="B54" t="str">
+            <v>Roxanne</v>
+          </cell>
+        </row>
+        <row r="55">
+          <cell r="A55" t="str">
+            <v>Schiesser</v>
+          </cell>
+          <cell r="B55" t="str">
+            <v>Sébastien</v>
+          </cell>
+        </row>
+        <row r="56">
+          <cell r="A56" t="str">
+            <v>Lambelet</v>
+          </cell>
+          <cell r="B56" t="str">
+            <v>Simon</v>
+          </cell>
+        </row>
+        <row r="57">
+          <cell r="A57" t="str">
+            <v>Cyprien</v>
+          </cell>
+          <cell r="B57" t="str">
+            <v>Theo</v>
+          </cell>
+        </row>
+        <row r="58">
+          <cell r="A58" t="str">
+            <v>Clerici</v>
+          </cell>
+          <cell r="B58" t="str">
+            <v>Thibault</v>
+          </cell>
+        </row>
+        <row r="59">
+          <cell r="A59" t="str">
+            <v>Ménétrey</v>
+          </cell>
+          <cell r="B59" t="str">
+            <v>Titouan</v>
+          </cell>
+        </row>
+        <row r="60">
+          <cell r="A60" t="str">
+            <v>Clerici</v>
+          </cell>
+          <cell r="B60" t="str">
+            <v>Tristan</v>
+          </cell>
+        </row>
+        <row r="61">
+          <cell r="A61" t="str">
+            <v>Bally</v>
+          </cell>
+          <cell r="B61" t="str">
+            <v>Yann</v>
+          </cell>
+        </row>
+        <row r="62">
+          <cell r="A62" t="str">
+            <v>Ménétrey</v>
+          </cell>
+          <cell r="B62" t="str">
+            <v>Ysatis</v>
+          </cell>
+        </row>
+        <row r="63">
+          <cell r="A63" t="str">
+            <v>Ménard</v>
+          </cell>
+          <cell r="B63" t="str">
+            <v>Mireille</v>
+          </cell>
+        </row>
+        <row r="64">
+          <cell r="A64" t="str">
+            <v>Rieger</v>
+          </cell>
+          <cell r="B64" t="str">
+            <v>Maya</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1674,7 +2228,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E63"/>
+  <sheetPr codeName="Sheet1">
+    <tabColor theme="4" tint="0.59999389629810485"/>
+  </sheetPr>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="2" width="14.921875" customWidth="1"/>
@@ -1682,363 +2239,424 @@
     <col min="4" max="5" width="9.23046875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A2" t="str" cm="1">
-        <f t="array" ref="A2:B63">_xlfn._xlws.FILTER('[1]Bénévoles 2026 V2'!$E:$F,'[1]Bénévoles 2026 V2'!$B:$B=TRUE)</f>
+      <c r="A2" t="str">
+        <f>[2]Personnes!A2</f>
         <v>Bouvet</v>
       </c>
       <c r="B2" t="str">
+        <f>[2]Personnes!B2</f>
         <v>Agathe</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A3" t="str">
+        <f>[2]Personnes!A3</f>
         <v>Bulka</v>
       </c>
       <c r="B3" t="str">
+        <f>[2]Personnes!B3</f>
         <v>Alegria Lily</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A4" t="str">
+        <f>[2]Personnes!A4</f>
         <v>Bastian</v>
       </c>
       <c r="B4" t="str">
+        <f>[2]Personnes!B4</f>
         <v>Alexandra</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A5" t="str">
+        <f>[2]Personnes!A5</f>
         <v>L'Horset</v>
       </c>
       <c r="B5" t="str">
+        <f>[2]Personnes!B5</f>
         <v>Alice</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A6" t="str">
+        <f>[2]Personnes!A6</f>
         <v>Ledru</v>
       </c>
       <c r="B6" t="str">
+        <f>[2]Personnes!B6</f>
         <v>Analou</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A7" t="str">
+        <f>[2]Personnes!A7</f>
         <v>Mallet</v>
       </c>
       <c r="B7" t="str">
+        <f>[2]Personnes!B7</f>
         <v>Anna</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A8" t="str">
+        <f>[2]Personnes!A8</f>
         <v>Malric</v>
       </c>
       <c r="B8" t="str">
+        <f>[2]Personnes!B8</f>
         <v>Annouk</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A9" t="str">
+        <f>[2]Personnes!A9</f>
         <v>Noël</v>
       </c>
       <c r="B9" t="str">
+        <f>[2]Personnes!B9</f>
         <v>Antonin</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A10" t="str">
+        <f>[2]Personnes!A10</f>
         <v>Tessier</v>
       </c>
       <c r="B10" t="str">
+        <f>[2]Personnes!B10</f>
         <v>Arsène</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A11" t="str">
+        <f>[2]Personnes!A11</f>
         <v>Uldry</v>
       </c>
       <c r="B11" t="str">
+        <f>[2]Personnes!B11</f>
         <v>Arthur</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A12" t="str">
+        <f>[2]Personnes!A12</f>
         <v>Marchand</v>
       </c>
       <c r="B12" t="str">
+        <f>[2]Personnes!B12</f>
         <v>Athénaé</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A13" t="str">
+        <f>[2]Personnes!A13</f>
         <v>Magerand</v>
       </c>
       <c r="B13" t="str">
+        <f>[2]Personnes!B13</f>
         <v>Auxence</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A14" t="str">
+        <f>[2]Personnes!A14</f>
         <v>Baruch</v>
       </c>
       <c r="B14" t="str">
+        <f>[2]Personnes!B14</f>
         <v>Ava</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A15" t="str">
+        <f>[2]Personnes!A15</f>
         <v>Detrain</v>
       </c>
       <c r="B15" t="str">
+        <f>[2]Personnes!B15</f>
         <v>Benoît</v>
-      </c>
-      <c r="C15" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A16" t="str">
+        <f>[2]Personnes!A16</f>
         <v>Meige</v>
       </c>
       <c r="B16" t="str">
+        <f>[2]Personnes!B16</f>
         <v>Corentin</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17" t="str">
+        <f>[2]Personnes!A17</f>
         <v>De Filippo</v>
       </c>
       <c r="B17" t="str">
+        <f>[2]Personnes!B17</f>
         <v>Emma</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18" t="str">
+        <f>[2]Personnes!A18</f>
         <v>Maître</v>
       </c>
       <c r="B18" t="str">
+        <f>[2]Personnes!B18</f>
         <v>Enzo</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19" t="str">
+        <f>[2]Personnes!A19</f>
         <v>Prouvost</v>
       </c>
       <c r="B19" t="str">
+        <f>[2]Personnes!B19</f>
         <v>Eugénie</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20" t="str">
+        <f>[2]Personnes!A20</f>
         <v xml:space="preserve">Rakotonandrasana </v>
       </c>
       <c r="B20" t="str">
+        <f>[2]Personnes!B20</f>
         <v>Iris</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21" t="str">
+        <f>[2]Personnes!A21</f>
         <v>Bürgisser</v>
       </c>
       <c r="B21" t="str">
+        <f>[2]Personnes!B21</f>
         <v>Jamilah</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A22" t="str">
+        <f>[2]Personnes!A22</f>
         <v>Ruscio</v>
       </c>
       <c r="B22" t="str">
+        <f>[2]Personnes!B22</f>
         <v>Jolan</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A23" t="str">
+        <f>[2]Personnes!A23</f>
         <v>Wuilloud</v>
       </c>
       <c r="B23" t="str">
+        <f>[2]Personnes!B23</f>
         <v xml:space="preserve">Jonas </v>
       </c>
-      <c r="C23" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A24" t="str">
+        <f>[2]Personnes!A24</f>
         <v>Pirolley</v>
       </c>
       <c r="B24" t="str">
+        <f>[2]Personnes!B24</f>
         <v>Jules</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25" t="str">
+        <f>[2]Personnes!A25</f>
         <v>Chavaillaz</v>
       </c>
       <c r="B25" t="str">
+        <f>[2]Personnes!B25</f>
         <v>Julie</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A26" t="str">
+        <f>[2]Personnes!A26</f>
         <v>Oeschger</v>
       </c>
       <c r="B26" t="str">
+        <f>[2]Personnes!B26</f>
         <v>Kristel</v>
       </c>
-      <c r="C26" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A27" t="str">
+        <f>[2]Personnes!A27</f>
         <v>Baltzinger</v>
       </c>
       <c r="B27" t="str">
+        <f>[2]Personnes!B27</f>
         <v>Léa</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A28" t="str">
+        <f>[2]Personnes!A28</f>
         <v>Chambaz</v>
       </c>
       <c r="B28" t="str">
+        <f>[2]Personnes!B28</f>
         <v>Léa</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A29" t="str">
+        <f>[2]Personnes!A29</f>
         <v>Ledru</v>
       </c>
       <c r="B29" t="str">
+        <f>[2]Personnes!B29</f>
         <v>Lina-Rosa</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A30" t="str">
+        <f>[2]Personnes!A30</f>
         <v>Jaquet</v>
       </c>
       <c r="B30" t="str">
+        <f>[2]Personnes!B30</f>
         <v>Lisa</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A31" t="str">
+        <f>[2]Personnes!A31</f>
         <v>Magnin</v>
       </c>
       <c r="B31" t="str">
+        <f>[2]Personnes!B31</f>
         <v>Lisa</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A32" t="str">
+        <f>[2]Personnes!A32</f>
         <v>Cardis</v>
       </c>
       <c r="B32" t="str">
+        <f>[2]Personnes!B32</f>
         <v>Louis</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A33" t="str">
+        <f>[2]Personnes!A33</f>
         <v>Post</v>
       </c>
       <c r="B33" t="str">
+        <f>[2]Personnes!B33</f>
         <v>Louis</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A34" t="str">
+        <f>[2]Personnes!A34</f>
         <v>Blanchard</v>
       </c>
       <c r="B34" t="str">
+        <f>[2]Personnes!B34</f>
         <v>Louise</v>
-      </c>
-      <c r="C34" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A35" t="str">
+        <f>[2]Personnes!A35</f>
         <v>Chastroux</v>
       </c>
       <c r="B35" t="str">
+        <f>[2]Personnes!B35</f>
         <v>Lucas</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A36" t="str">
+        <f>[2]Personnes!A36</f>
         <v>Meyer</v>
       </c>
       <c r="B36" t="str">
+        <f>[2]Personnes!B36</f>
         <v>Lucie</v>
-      </c>
-      <c r="C36" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A37" t="str">
+        <f>[2]Personnes!A37</f>
         <v>Ménétrey</v>
       </c>
       <c r="B37" t="str">
+        <f>[2]Personnes!B37</f>
         <v>Maëlan</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A38" t="str">
+        <f>[2]Personnes!A38</f>
         <v>Chambaz</v>
       </c>
       <c r="B38" t="str">
+        <f>[2]Personnes!B38</f>
         <v>Maëlle</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A39" t="str">
+        <f>[2]Personnes!A39</f>
         <v>Felix</v>
       </c>
       <c r="B39" t="str">
+        <f>[2]Personnes!B39</f>
         <v>Marius</v>
-      </c>
-      <c r="C39" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A40" t="str">
+        <f>[2]Personnes!A40</f>
         <v>Ledru</v>
       </c>
       <c r="B40" t="str">
+        <f>[2]Personnes!B40</f>
         <v>Marot</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A41" t="str">
+        <f>[2]Personnes!A41</f>
         <v>Cuinet</v>
       </c>
       <c r="B41" t="str">
+        <f>[2]Personnes!B41</f>
         <v>Mathis</v>
       </c>
       <c r="C41" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D41" s="2">
         <v>0.875</v>
@@ -2049,44 +2667,51 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A42" t="str">
+        <f>[2]Personnes!A42</f>
         <v>Gavin</v>
       </c>
       <c r="B42" t="str">
+        <f>[2]Personnes!B42</f>
         <v>Matteo</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A43" t="str">
+        <f>[2]Personnes!A43</f>
         <v>Debray</v>
       </c>
       <c r="B43" t="str">
+        <f>[2]Personnes!B43</f>
         <v>Maxime</v>
-      </c>
-      <c r="C43" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A44" t="str">
+        <f>[2]Personnes!A44</f>
         <v>Corbelli</v>
       </c>
       <c r="B44" t="str">
+        <f>[2]Personnes!B44</f>
         <v>Maya</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A45" t="str">
+        <f>[2]Personnes!A45</f>
         <v>Pasche</v>
       </c>
       <c r="B45" t="str">
+        <f>[2]Personnes!B45</f>
         <v>Mickaël</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A46" t="str">
+        <f>[2]Personnes!A46</f>
         <v>Fargues</v>
       </c>
       <c r="B46" t="str">
+        <f>[2]Personnes!B46</f>
         <v>Morgana</v>
       </c>
       <c r="C46" t="s">
@@ -2101,49 +2726,61 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A47" t="str">
+        <f>[2]Personnes!A47</f>
         <v>Scyboz (Lambelet)</v>
       </c>
       <c r="B47" t="str">
+        <f>[2]Personnes!B47</f>
         <v>Morgane</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A48" t="str">
+        <f>[2]Personnes!A48</f>
         <v>Koux</v>
       </c>
       <c r="B48" t="str">
+        <f>[2]Personnes!B48</f>
         <v>Nathalia</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A49" t="str">
+        <f>[2]Personnes!A49</f>
         <v>Cherpillod</v>
       </c>
       <c r="B49" t="str">
+        <f>[2]Personnes!B49</f>
         <v>Noah</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A50" t="str">
+        <f>[2]Personnes!A50</f>
         <v>Chambaz</v>
       </c>
       <c r="B50" t="str">
+        <f>[2]Personnes!B50</f>
         <v>Patrick</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A51" t="str">
+        <f>[2]Personnes!A51</f>
         <v>Assaoui</v>
       </c>
       <c r="B51" t="str">
+        <f>[2]Personnes!B51</f>
         <v>Rama</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A52" t="str">
+        <f>[2]Personnes!A52</f>
         <v>Lacroze</v>
       </c>
       <c r="B52" t="str">
+        <f>[2]Personnes!B52</f>
         <v>Raphaël</v>
       </c>
       <c r="C52" t="s">
@@ -2158,89 +2795,111 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A53" t="str">
+        <f>[2]Personnes!A53</f>
         <v>Neidhart</v>
       </c>
       <c r="B53" t="str">
+        <f>[2]Personnes!B53</f>
         <v>Raphaëlle</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A54" t="str">
+        <f>[2]Personnes!A54</f>
         <v xml:space="preserve">Lanni </v>
       </c>
       <c r="B54" t="str">
+        <f>[2]Personnes!B54</f>
         <v>Roxanne</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A55" t="str">
+        <f>[2]Personnes!A55</f>
         <v>Schiesser</v>
       </c>
       <c r="B55" t="str">
+        <f>[2]Personnes!B55</f>
         <v>Sébastien</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A56" t="str">
+        <f>[2]Personnes!A56</f>
         <v>Lambelet</v>
       </c>
       <c r="B56" t="str">
+        <f>[2]Personnes!B56</f>
         <v>Simon</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A57" t="str">
+        <f>[2]Personnes!A57</f>
         <v>Cyprien</v>
       </c>
       <c r="B57" t="str">
+        <f>[2]Personnes!B57</f>
         <v>Theo</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A58" t="str">
+        <f>[2]Personnes!A58</f>
         <v>Clerici</v>
       </c>
       <c r="B58" t="str">
+        <f>[2]Personnes!B58</f>
         <v>Thibault</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A59" t="str">
+        <f>[2]Personnes!A59</f>
         <v>Ménétrey</v>
       </c>
       <c r="B59" t="str">
+        <f>[2]Personnes!B59</f>
         <v>Titouan</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A60" t="str">
+        <f>[2]Personnes!A60</f>
         <v>Clerici</v>
       </c>
       <c r="B60" t="str">
+        <f>[2]Personnes!B60</f>
         <v>Tristan</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A61" t="str">
+        <f>[2]Personnes!A61</f>
         <v>Bally</v>
       </c>
       <c r="B61" t="str">
+        <f>[2]Personnes!B61</f>
         <v>Yann</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A62" t="str">
+        <f>[2]Personnes!A62</f>
         <v>Ménétrey</v>
       </c>
       <c r="B62" t="str">
+        <f>[2]Personnes!B62</f>
         <v>Ysatis</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A63" t="str">
+        <f>[2]Personnes!A63</f>
         <v>Ménard</v>
       </c>
       <c r="B63" t="str">
+        <f>[2]Personnes!B63</f>
         <v>Mireille</v>
       </c>
       <c r="C63" t="s">
@@ -2253,8 +2912,28 @@
         <v>0.875</v>
       </c>
     </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A64" t="str">
+        <f>[2]Personnes!A64</f>
+        <v>Rieger</v>
+      </c>
+      <c r="B64" t="str">
+        <f>[2]Personnes!B64</f>
+        <v>Maya</v>
+      </c>
+    </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
+  <protectedRanges>
+    <protectedRange sqref="C1:E1048576" name="Shifts"/>
+  </protectedRanges>
+  <conditionalFormatting sqref="A2:XFD65">
+    <cfRule type="expression" dxfId="5" priority="1">
+      <formula>MOD(ROW(),2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -2272,332 +2951,410 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{423EC40D-93CA-4FCD-A6F8-28F80DC6C0B8}">
-  <dimension ref="A1:E63"/>
+  <sheetPr codeName="Sheet2">
+    <tabColor theme="5" tint="0.59999389629810485"/>
+  </sheetPr>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="2" width="14.921875" customWidth="1"/>
     <col min="3" max="3" width="11.765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A2" t="str" cm="1">
-        <f t="array" ref="A2:B63">_xlfn._xlws.FILTER('[1]Bénévoles 2026 V2'!$E:$F,'[1]Bénévoles 2026 V2'!$B:$B=TRUE)</f>
+      <c r="A2" t="str">
+        <f>[2]Personnes!A2</f>
         <v>Bouvet</v>
       </c>
       <c r="B2" t="str">
+        <f>[2]Personnes!B2</f>
         <v>Agathe</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A3" t="str">
+        <f>[2]Personnes!A3</f>
         <v>Bulka</v>
       </c>
       <c r="B3" t="str">
+        <f>[2]Personnes!B3</f>
         <v>Alegria Lily</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A4" t="str">
+        <f>[2]Personnes!A4</f>
         <v>Bastian</v>
       </c>
       <c r="B4" t="str">
+        <f>[2]Personnes!B4</f>
         <v>Alexandra</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A5" t="str">
+        <f>[2]Personnes!A5</f>
         <v>L'Horset</v>
       </c>
       <c r="B5" t="str">
+        <f>[2]Personnes!B5</f>
         <v>Alice</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A6" t="str">
+        <f>[2]Personnes!A6</f>
         <v>Ledru</v>
       </c>
       <c r="B6" t="str">
+        <f>[2]Personnes!B6</f>
         <v>Analou</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A7" t="str">
+        <f>[2]Personnes!A7</f>
         <v>Mallet</v>
       </c>
       <c r="B7" t="str">
+        <f>[2]Personnes!B7</f>
         <v>Anna</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A8" t="str">
+        <f>[2]Personnes!A8</f>
         <v>Malric</v>
       </c>
       <c r="B8" t="str">
+        <f>[2]Personnes!B8</f>
         <v>Annouk</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A9" t="str">
+        <f>[2]Personnes!A9</f>
         <v>Noël</v>
       </c>
       <c r="B9" t="str">
+        <f>[2]Personnes!B9</f>
         <v>Antonin</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A10" t="str">
+        <f>[2]Personnes!A10</f>
         <v>Tessier</v>
       </c>
       <c r="B10" t="str">
+        <f>[2]Personnes!B10</f>
         <v>Arsène</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A11" t="str">
+        <f>[2]Personnes!A11</f>
         <v>Uldry</v>
       </c>
       <c r="B11" t="str">
+        <f>[2]Personnes!B11</f>
         <v>Arthur</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A12" t="str">
+        <f>[2]Personnes!A12</f>
         <v>Marchand</v>
       </c>
       <c r="B12" t="str">
+        <f>[2]Personnes!B12</f>
         <v>Athénaé</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A13" t="str">
+        <f>[2]Personnes!A13</f>
         <v>Magerand</v>
       </c>
       <c r="B13" t="str">
+        <f>[2]Personnes!B13</f>
         <v>Auxence</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A14" t="str">
+        <f>[2]Personnes!A14</f>
         <v>Baruch</v>
       </c>
       <c r="B14" t="str">
+        <f>[2]Personnes!B14</f>
         <v>Ava</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A15" t="str">
+        <f>[2]Personnes!A15</f>
         <v>Detrain</v>
       </c>
       <c r="B15" t="str">
+        <f>[2]Personnes!B15</f>
         <v>Benoît</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A16" t="str">
+        <f>[2]Personnes!A16</f>
         <v>Meige</v>
       </c>
       <c r="B16" t="str">
+        <f>[2]Personnes!B16</f>
         <v>Corentin</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17" t="str">
+        <f>[2]Personnes!A17</f>
         <v>De Filippo</v>
       </c>
       <c r="B17" t="str">
+        <f>[2]Personnes!B17</f>
         <v>Emma</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18" t="str">
+        <f>[2]Personnes!A18</f>
         <v>Maître</v>
       </c>
       <c r="B18" t="str">
+        <f>[2]Personnes!B18</f>
         <v>Enzo</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19" t="str">
+        <f>[2]Personnes!A19</f>
         <v>Prouvost</v>
       </c>
       <c r="B19" t="str">
+        <f>[2]Personnes!B19</f>
         <v>Eugénie</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20" t="str">
+        <f>[2]Personnes!A20</f>
         <v xml:space="preserve">Rakotonandrasana </v>
       </c>
       <c r="B20" t="str">
+        <f>[2]Personnes!B20</f>
         <v>Iris</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21" t="str">
+        <f>[2]Personnes!A21</f>
         <v>Bürgisser</v>
       </c>
       <c r="B21" t="str">
+        <f>[2]Personnes!B21</f>
         <v>Jamilah</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A22" t="str">
+        <f>[2]Personnes!A22</f>
         <v>Ruscio</v>
       </c>
       <c r="B22" t="str">
+        <f>[2]Personnes!B22</f>
         <v>Jolan</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A23" t="str">
+        <f>[2]Personnes!A23</f>
         <v>Wuilloud</v>
       </c>
       <c r="B23" t="str">
+        <f>[2]Personnes!B23</f>
         <v xml:space="preserve">Jonas </v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A24" t="str">
+        <f>[2]Personnes!A24</f>
         <v>Pirolley</v>
       </c>
       <c r="B24" t="str">
+        <f>[2]Personnes!B24</f>
         <v>Jules</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25" t="str">
+        <f>[2]Personnes!A25</f>
         <v>Chavaillaz</v>
       </c>
       <c r="B25" t="str">
+        <f>[2]Personnes!B25</f>
         <v>Julie</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A26" t="str">
+        <f>[2]Personnes!A26</f>
         <v>Oeschger</v>
       </c>
       <c r="B26" t="str">
+        <f>[2]Personnes!B26</f>
         <v>Kristel</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A27" t="str">
+        <f>[2]Personnes!A27</f>
         <v>Baltzinger</v>
       </c>
       <c r="B27" t="str">
+        <f>[2]Personnes!B27</f>
         <v>Léa</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A28" t="str">
+        <f>[2]Personnes!A28</f>
         <v>Chambaz</v>
       </c>
       <c r="B28" t="str">
+        <f>[2]Personnes!B28</f>
         <v>Léa</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A29" t="str">
+        <f>[2]Personnes!A29</f>
         <v>Ledru</v>
       </c>
       <c r="B29" t="str">
+        <f>[2]Personnes!B29</f>
         <v>Lina-Rosa</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A30" t="str">
+        <f>[2]Personnes!A30</f>
         <v>Jaquet</v>
       </c>
       <c r="B30" t="str">
+        <f>[2]Personnes!B30</f>
         <v>Lisa</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A31" t="str">
+        <f>[2]Personnes!A31</f>
         <v>Magnin</v>
       </c>
       <c r="B31" t="str">
+        <f>[2]Personnes!B31</f>
         <v>Lisa</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A32" t="str">
+        <f>[2]Personnes!A32</f>
         <v>Cardis</v>
       </c>
       <c r="B32" t="str">
+        <f>[2]Personnes!B32</f>
         <v>Louis</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A33" t="str">
+        <f>[2]Personnes!A33</f>
         <v>Post</v>
       </c>
       <c r="B33" t="str">
+        <f>[2]Personnes!B33</f>
         <v>Louis</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A34" t="str">
+        <f>[2]Personnes!A34</f>
         <v>Blanchard</v>
       </c>
       <c r="B34" t="str">
+        <f>[2]Personnes!B34</f>
         <v>Louise</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A35" t="str">
+        <f>[2]Personnes!A35</f>
         <v>Chastroux</v>
       </c>
       <c r="B35" t="str">
+        <f>[2]Personnes!B35</f>
         <v>Lucas</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A36" t="str">
+        <f>[2]Personnes!A36</f>
         <v>Meyer</v>
       </c>
       <c r="B36" t="str">
+        <f>[2]Personnes!B36</f>
         <v>Lucie</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A37" t="str">
+        <f>[2]Personnes!A37</f>
         <v>Ménétrey</v>
       </c>
       <c r="B37" t="str">
+        <f>[2]Personnes!B37</f>
         <v>Maëlan</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A38" t="str">
+        <f>[2]Personnes!A38</f>
         <v>Chambaz</v>
       </c>
       <c r="B38" t="str">
+        <f>[2]Personnes!B38</f>
         <v>Maëlle</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A39" t="str">
+        <f>[2]Personnes!A39</f>
         <v>Felix</v>
       </c>
       <c r="B39" t="str">
+        <f>[2]Personnes!B39</f>
         <v>Marius</v>
       </c>
       <c r="C39" t="s">
@@ -2612,33 +3369,41 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A40" t="str">
+        <f>[2]Personnes!A40</f>
         <v>Ledru</v>
       </c>
       <c r="B40" t="str">
+        <f>[2]Personnes!B40</f>
         <v>Marot</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A41" t="str">
+        <f>[2]Personnes!A41</f>
         <v>Cuinet</v>
       </c>
       <c r="B41" t="str">
+        <f>[2]Personnes!B41</f>
         <v>Mathis</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A42" t="str">
+        <f>[2]Personnes!A42</f>
         <v>Gavin</v>
       </c>
       <c r="B42" t="str">
+        <f>[2]Personnes!B42</f>
         <v>Matteo</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A43" t="str">
+        <f>[2]Personnes!A43</f>
         <v>Debray</v>
       </c>
       <c r="B43" t="str">
+        <f>[2]Personnes!B43</f>
         <v>Maxime</v>
       </c>
       <c r="C43" t="s">
@@ -2653,73 +3418,91 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A44" t="str">
+        <f>[2]Personnes!A44</f>
         <v>Corbelli</v>
       </c>
       <c r="B44" t="str">
+        <f>[2]Personnes!B44</f>
         <v>Maya</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A45" t="str">
+        <f>[2]Personnes!A45</f>
         <v>Pasche</v>
       </c>
       <c r="B45" t="str">
+        <f>[2]Personnes!B45</f>
         <v>Mickaël</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A46" t="str">
+        <f>[2]Personnes!A46</f>
         <v>Fargues</v>
       </c>
       <c r="B46" t="str">
+        <f>[2]Personnes!B46</f>
         <v>Morgana</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A47" t="str">
+        <f>[2]Personnes!A47</f>
         <v>Scyboz (Lambelet)</v>
       </c>
       <c r="B47" t="str">
+        <f>[2]Personnes!B47</f>
         <v>Morgane</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A48" t="str">
+        <f>[2]Personnes!A48</f>
         <v>Koux</v>
       </c>
       <c r="B48" t="str">
+        <f>[2]Personnes!B48</f>
         <v>Nathalia</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A49" t="str">
+        <f>[2]Personnes!A49</f>
         <v>Cherpillod</v>
       </c>
       <c r="B49" t="str">
+        <f>[2]Personnes!B49</f>
         <v>Noah</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A50" t="str">
+        <f>[2]Personnes!A50</f>
         <v>Chambaz</v>
       </c>
       <c r="B50" t="str">
+        <f>[2]Personnes!B50</f>
         <v>Patrick</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A51" t="str">
+        <f>[2]Personnes!A51</f>
         <v>Assaoui</v>
       </c>
       <c r="B51" t="str">
+        <f>[2]Personnes!B51</f>
         <v>Rama</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A52" t="str">
+        <f>[2]Personnes!A52</f>
         <v>Lacroze</v>
       </c>
       <c r="B52" t="str">
+        <f>[2]Personnes!B52</f>
         <v>Raphaël</v>
       </c>
       <c r="C52" t="s">
@@ -2734,94 +3517,142 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A53" t="str">
+        <f>[2]Personnes!A53</f>
         <v>Neidhart</v>
       </c>
       <c r="B53" t="str">
+        <f>[2]Personnes!B53</f>
         <v>Raphaëlle</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A54" t="str">
+        <f>[2]Personnes!A54</f>
         <v xml:space="preserve">Lanni </v>
       </c>
       <c r="B54" t="str">
+        <f>[2]Personnes!B54</f>
         <v>Roxanne</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A55" t="str">
+        <f>[2]Personnes!A55</f>
         <v>Schiesser</v>
       </c>
       <c r="B55" t="str">
+        <f>[2]Personnes!B55</f>
         <v>Sébastien</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A56" t="str">
+        <f>[2]Personnes!A56</f>
         <v>Lambelet</v>
       </c>
       <c r="B56" t="str">
+        <f>[2]Personnes!B56</f>
         <v>Simon</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A57" t="str">
+        <f>[2]Personnes!A57</f>
         <v>Cyprien</v>
       </c>
       <c r="B57" t="str">
+        <f>[2]Personnes!B57</f>
         <v>Theo</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A58" t="str">
+        <f>[2]Personnes!A58</f>
         <v>Clerici</v>
       </c>
       <c r="B58" t="str">
+        <f>[2]Personnes!B58</f>
         <v>Thibault</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A59" t="str">
+        <f>[2]Personnes!A59</f>
         <v>Ménétrey</v>
       </c>
       <c r="B59" t="str">
+        <f>[2]Personnes!B59</f>
         <v>Titouan</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A60" t="str">
+        <f>[2]Personnes!A60</f>
         <v>Clerici</v>
       </c>
       <c r="B60" t="str">
+        <f>[2]Personnes!B60</f>
         <v>Tristan</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A61" t="str">
+        <f>[2]Personnes!A61</f>
         <v>Bally</v>
       </c>
       <c r="B61" t="str">
+        <f>[2]Personnes!B61</f>
         <v>Yann</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A62" t="str">
+        <f>[2]Personnes!A62</f>
         <v>Ménétrey</v>
       </c>
       <c r="B62" t="str">
+        <f>[2]Personnes!B62</f>
         <v>Ysatis</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A63" t="str">
+        <f>[2]Personnes!A63</f>
         <v>Ménard</v>
       </c>
       <c r="B63" t="str">
+        <f>[2]Personnes!B63</f>
         <v>Mireille</v>
       </c>
     </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A64" t="str">
+        <f>[2]Personnes!A64</f>
+        <v>Rieger</v>
+      </c>
+      <c r="B64" t="str">
+        <f>[2]Personnes!B64</f>
+        <v>Maya</v>
+      </c>
+    </row>
+    <row r="65" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B65">
+        <f>[2]Personnes!B65</f>
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
+  <protectedRanges>
+    <protectedRange sqref="C1:E1048576" name="Shifts"/>
+  </protectedRanges>
+  <conditionalFormatting sqref="A2:XFD65">
+    <cfRule type="expression" dxfId="4" priority="1">
+      <formula>MOD(ROW(),2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -2839,332 +3670,410 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3D62804-1233-4D8D-A119-6FEA62BCFE42}">
-  <dimension ref="A1:E63"/>
+  <sheetPr codeName="Sheet3">
+    <tabColor theme="6" tint="0.59999389629810485"/>
+  </sheetPr>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="2" width="14.921875" customWidth="1"/>
     <col min="3" max="3" width="11.765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A2" t="str" cm="1">
-        <f t="array" ref="A2:B63">_xlfn._xlws.FILTER('[1]Bénévoles 2026 V2'!$E:$F,'[1]Bénévoles 2026 V2'!$B:$B=TRUE)</f>
+      <c r="A2" t="str">
+        <f>[2]Personnes!A2</f>
         <v>Bouvet</v>
       </c>
       <c r="B2" t="str">
+        <f>[2]Personnes!B2</f>
         <v>Agathe</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A3" t="str">
+        <f>[2]Personnes!A3</f>
         <v>Bulka</v>
       </c>
       <c r="B3" t="str">
+        <f>[2]Personnes!B3</f>
         <v>Alegria Lily</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A4" t="str">
+        <f>[2]Personnes!A4</f>
         <v>Bastian</v>
       </c>
       <c r="B4" t="str">
+        <f>[2]Personnes!B4</f>
         <v>Alexandra</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A5" t="str">
+        <f>[2]Personnes!A5</f>
         <v>L'Horset</v>
       </c>
       <c r="B5" t="str">
+        <f>[2]Personnes!B5</f>
         <v>Alice</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A6" t="str">
+        <f>[2]Personnes!A6</f>
         <v>Ledru</v>
       </c>
       <c r="B6" t="str">
+        <f>[2]Personnes!B6</f>
         <v>Analou</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A7" t="str">
+        <f>[2]Personnes!A7</f>
         <v>Mallet</v>
       </c>
       <c r="B7" t="str">
+        <f>[2]Personnes!B7</f>
         <v>Anna</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A8" t="str">
+        <f>[2]Personnes!A8</f>
         <v>Malric</v>
       </c>
       <c r="B8" t="str">
+        <f>[2]Personnes!B8</f>
         <v>Annouk</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A9" t="str">
+        <f>[2]Personnes!A9</f>
         <v>Noël</v>
       </c>
       <c r="B9" t="str">
+        <f>[2]Personnes!B9</f>
         <v>Antonin</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A10" t="str">
+        <f>[2]Personnes!A10</f>
         <v>Tessier</v>
       </c>
       <c r="B10" t="str">
+        <f>[2]Personnes!B10</f>
         <v>Arsène</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A11" t="str">
+        <f>[2]Personnes!A11</f>
         <v>Uldry</v>
       </c>
       <c r="B11" t="str">
+        <f>[2]Personnes!B11</f>
         <v>Arthur</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A12" t="str">
+        <f>[2]Personnes!A12</f>
         <v>Marchand</v>
       </c>
       <c r="B12" t="str">
+        <f>[2]Personnes!B12</f>
         <v>Athénaé</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A13" t="str">
+        <f>[2]Personnes!A13</f>
         <v>Magerand</v>
       </c>
       <c r="B13" t="str">
+        <f>[2]Personnes!B13</f>
         <v>Auxence</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A14" t="str">
+        <f>[2]Personnes!A14</f>
         <v>Baruch</v>
       </c>
       <c r="B14" t="str">
+        <f>[2]Personnes!B14</f>
         <v>Ava</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A15" t="str">
+        <f>[2]Personnes!A15</f>
         <v>Detrain</v>
       </c>
       <c r="B15" t="str">
+        <f>[2]Personnes!B15</f>
         <v>Benoît</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A16" t="str">
+        <f>[2]Personnes!A16</f>
         <v>Meige</v>
       </c>
       <c r="B16" t="str">
+        <f>[2]Personnes!B16</f>
         <v>Corentin</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17" t="str">
+        <f>[2]Personnes!A17</f>
         <v>De Filippo</v>
       </c>
       <c r="B17" t="str">
+        <f>[2]Personnes!B17</f>
         <v>Emma</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18" t="str">
+        <f>[2]Personnes!A18</f>
         <v>Maître</v>
       </c>
       <c r="B18" t="str">
+        <f>[2]Personnes!B18</f>
         <v>Enzo</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19" t="str">
+        <f>[2]Personnes!A19</f>
         <v>Prouvost</v>
       </c>
       <c r="B19" t="str">
+        <f>[2]Personnes!B19</f>
         <v>Eugénie</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20" t="str">
+        <f>[2]Personnes!A20</f>
         <v xml:space="preserve">Rakotonandrasana </v>
       </c>
       <c r="B20" t="str">
+        <f>[2]Personnes!B20</f>
         <v>Iris</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21" t="str">
+        <f>[2]Personnes!A21</f>
         <v>Bürgisser</v>
       </c>
       <c r="B21" t="str">
+        <f>[2]Personnes!B21</f>
         <v>Jamilah</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A22" t="str">
+        <f>[2]Personnes!A22</f>
         <v>Ruscio</v>
       </c>
       <c r="B22" t="str">
+        <f>[2]Personnes!B22</f>
         <v>Jolan</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A23" t="str">
+        <f>[2]Personnes!A23</f>
         <v>Wuilloud</v>
       </c>
       <c r="B23" t="str">
+        <f>[2]Personnes!B23</f>
         <v xml:space="preserve">Jonas </v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A24" t="str">
+        <f>[2]Personnes!A24</f>
         <v>Pirolley</v>
       </c>
       <c r="B24" t="str">
+        <f>[2]Personnes!B24</f>
         <v>Jules</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25" t="str">
+        <f>[2]Personnes!A25</f>
         <v>Chavaillaz</v>
       </c>
       <c r="B25" t="str">
+        <f>[2]Personnes!B25</f>
         <v>Julie</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A26" t="str">
+        <f>[2]Personnes!A26</f>
         <v>Oeschger</v>
       </c>
       <c r="B26" t="str">
+        <f>[2]Personnes!B26</f>
         <v>Kristel</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A27" t="str">
+        <f>[2]Personnes!A27</f>
         <v>Baltzinger</v>
       </c>
       <c r="B27" t="str">
+        <f>[2]Personnes!B27</f>
         <v>Léa</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A28" t="str">
+        <f>[2]Personnes!A28</f>
         <v>Chambaz</v>
       </c>
       <c r="B28" t="str">
+        <f>[2]Personnes!B28</f>
         <v>Léa</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A29" t="str">
+        <f>[2]Personnes!A29</f>
         <v>Ledru</v>
       </c>
       <c r="B29" t="str">
+        <f>[2]Personnes!B29</f>
         <v>Lina-Rosa</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A30" t="str">
+        <f>[2]Personnes!A30</f>
         <v>Jaquet</v>
       </c>
       <c r="B30" t="str">
+        <f>[2]Personnes!B30</f>
         <v>Lisa</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A31" t="str">
+        <f>[2]Personnes!A31</f>
         <v>Magnin</v>
       </c>
       <c r="B31" t="str">
+        <f>[2]Personnes!B31</f>
         <v>Lisa</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A32" t="str">
+        <f>[2]Personnes!A32</f>
         <v>Cardis</v>
       </c>
       <c r="B32" t="str">
+        <f>[2]Personnes!B32</f>
         <v>Louis</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A33" t="str">
+        <f>[2]Personnes!A33</f>
         <v>Post</v>
       </c>
       <c r="B33" t="str">
+        <f>[2]Personnes!B33</f>
         <v>Louis</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A34" t="str">
+        <f>[2]Personnes!A34</f>
         <v>Blanchard</v>
       </c>
       <c r="B34" t="str">
+        <f>[2]Personnes!B34</f>
         <v>Louise</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A35" t="str">
+        <f>[2]Personnes!A35</f>
         <v>Chastroux</v>
       </c>
       <c r="B35" t="str">
+        <f>[2]Personnes!B35</f>
         <v>Lucas</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A36" t="str">
+        <f>[2]Personnes!A36</f>
         <v>Meyer</v>
       </c>
       <c r="B36" t="str">
+        <f>[2]Personnes!B36</f>
         <v>Lucie</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A37" t="str">
+        <f>[2]Personnes!A37</f>
         <v>Ménétrey</v>
       </c>
       <c r="B37" t="str">
+        <f>[2]Personnes!B37</f>
         <v>Maëlan</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A38" t="str">
+        <f>[2]Personnes!A38</f>
         <v>Chambaz</v>
       </c>
       <c r="B38" t="str">
+        <f>[2]Personnes!B38</f>
         <v>Maëlle</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A39" t="str">
+        <f>[2]Personnes!A39</f>
         <v>Felix</v>
       </c>
       <c r="B39" t="str">
+        <f>[2]Personnes!B39</f>
         <v>Marius</v>
       </c>
       <c r="C39" t="s">
@@ -3179,33 +4088,41 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A40" t="str">
+        <f>[2]Personnes!A40</f>
         <v>Ledru</v>
       </c>
       <c r="B40" t="str">
+        <f>[2]Personnes!B40</f>
         <v>Marot</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A41" t="str">
+        <f>[2]Personnes!A41</f>
         <v>Cuinet</v>
       </c>
       <c r="B41" t="str">
+        <f>[2]Personnes!B41</f>
         <v>Mathis</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A42" t="str">
+        <f>[2]Personnes!A42</f>
         <v>Gavin</v>
       </c>
       <c r="B42" t="str">
+        <f>[2]Personnes!B42</f>
         <v>Matteo</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A43" t="str">
+        <f>[2]Personnes!A43</f>
         <v>Debray</v>
       </c>
       <c r="B43" t="str">
+        <f>[2]Personnes!B43</f>
         <v>Maxime</v>
       </c>
       <c r="C43" t="s">
@@ -3220,73 +4137,91 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A44" t="str">
+        <f>[2]Personnes!A44</f>
         <v>Corbelli</v>
       </c>
       <c r="B44" t="str">
+        <f>[2]Personnes!B44</f>
         <v>Maya</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A45" t="str">
+        <f>[2]Personnes!A45</f>
         <v>Pasche</v>
       </c>
       <c r="B45" t="str">
+        <f>[2]Personnes!B45</f>
         <v>Mickaël</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A46" t="str">
+        <f>[2]Personnes!A46</f>
         <v>Fargues</v>
       </c>
       <c r="B46" t="str">
+        <f>[2]Personnes!B46</f>
         <v>Morgana</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A47" t="str">
+        <f>[2]Personnes!A47</f>
         <v>Scyboz (Lambelet)</v>
       </c>
       <c r="B47" t="str">
+        <f>[2]Personnes!B47</f>
         <v>Morgane</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A48" t="str">
+        <f>[2]Personnes!A48</f>
         <v>Koux</v>
       </c>
       <c r="B48" t="str">
+        <f>[2]Personnes!B48</f>
         <v>Nathalia</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A49" t="str">
+        <f>[2]Personnes!A49</f>
         <v>Cherpillod</v>
       </c>
       <c r="B49" t="str">
+        <f>[2]Personnes!B49</f>
         <v>Noah</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A50" t="str">
+        <f>[2]Personnes!A50</f>
         <v>Chambaz</v>
       </c>
       <c r="B50" t="str">
+        <f>[2]Personnes!B50</f>
         <v>Patrick</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A51" t="str">
+        <f>[2]Personnes!A51</f>
         <v>Assaoui</v>
       </c>
       <c r="B51" t="str">
+        <f>[2]Personnes!B51</f>
         <v>Rama</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A52" t="str">
+        <f>[2]Personnes!A52</f>
         <v>Lacroze</v>
       </c>
       <c r="B52" t="str">
+        <f>[2]Personnes!B52</f>
         <v>Raphaël</v>
       </c>
       <c r="C52" t="s">
@@ -3301,94 +4236,136 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A53" t="str">
+        <f>[2]Personnes!A53</f>
         <v>Neidhart</v>
       </c>
       <c r="B53" t="str">
+        <f>[2]Personnes!B53</f>
         <v>Raphaëlle</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A54" t="str">
+        <f>[2]Personnes!A54</f>
         <v xml:space="preserve">Lanni </v>
       </c>
       <c r="B54" t="str">
+        <f>[2]Personnes!B54</f>
         <v>Roxanne</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A55" t="str">
+        <f>[2]Personnes!A55</f>
         <v>Schiesser</v>
       </c>
       <c r="B55" t="str">
+        <f>[2]Personnes!B55</f>
         <v>Sébastien</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A56" t="str">
+        <f>[2]Personnes!A56</f>
         <v>Lambelet</v>
       </c>
       <c r="B56" t="str">
+        <f>[2]Personnes!B56</f>
         <v>Simon</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A57" t="str">
+        <f>[2]Personnes!A57</f>
         <v>Cyprien</v>
       </c>
       <c r="B57" t="str">
+        <f>[2]Personnes!B57</f>
         <v>Theo</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A58" t="str">
+        <f>[2]Personnes!A58</f>
         <v>Clerici</v>
       </c>
       <c r="B58" t="str">
+        <f>[2]Personnes!B58</f>
         <v>Thibault</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A59" t="str">
+        <f>[2]Personnes!A59</f>
         <v>Ménétrey</v>
       </c>
       <c r="B59" t="str">
+        <f>[2]Personnes!B59</f>
         <v>Titouan</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A60" t="str">
+        <f>[2]Personnes!A60</f>
         <v>Clerici</v>
       </c>
       <c r="B60" t="str">
+        <f>[2]Personnes!B60</f>
         <v>Tristan</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A61" t="str">
+        <f>[2]Personnes!A61</f>
         <v>Bally</v>
       </c>
       <c r="B61" t="str">
+        <f>[2]Personnes!B61</f>
         <v>Yann</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A62" t="str">
+        <f>[2]Personnes!A62</f>
         <v>Ménétrey</v>
       </c>
       <c r="B62" t="str">
+        <f>[2]Personnes!B62</f>
         <v>Ysatis</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A63" t="str">
+        <f>[2]Personnes!A63</f>
         <v>Ménard</v>
       </c>
       <c r="B63" t="str">
+        <f>[2]Personnes!B63</f>
         <v>Mireille</v>
       </c>
     </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A64" t="str">
+        <f>[2]Personnes!A64</f>
+        <v>Rieger</v>
+      </c>
+      <c r="B64" t="str">
+        <f>[2]Personnes!B64</f>
+        <v>Maya</v>
+      </c>
+    </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
+  <protectedRanges>
+    <protectedRange sqref="C1:E1048576" name="Shifts"/>
+  </protectedRanges>
+  <conditionalFormatting sqref="A2:XFD65">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>MOD(ROW(),2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -3406,332 +4383,410 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9848EB70-D8FB-4222-91C3-0659002AC443}">
-  <dimension ref="A1:E63"/>
+  <sheetPr codeName="Sheet4">
+    <tabColor theme="7" tint="0.59999389629810485"/>
+  </sheetPr>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="2" width="14.921875" customWidth="1"/>
     <col min="3" max="3" width="11.765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A2" t="str" cm="1">
-        <f t="array" ref="A2:B63">_xlfn._xlws.FILTER('[1]Bénévoles 2026 V2'!$E:$F,'[1]Bénévoles 2026 V2'!$B:$B=TRUE)</f>
+      <c r="A2" t="str">
+        <f>[2]Personnes!A2</f>
         <v>Bouvet</v>
       </c>
       <c r="B2" t="str">
+        <f>[2]Personnes!B2</f>
         <v>Agathe</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A3" t="str">
+        <f>[2]Personnes!A3</f>
         <v>Bulka</v>
       </c>
       <c r="B3" t="str">
+        <f>[2]Personnes!B3</f>
         <v>Alegria Lily</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A4" t="str">
+        <f>[2]Personnes!A4</f>
         <v>Bastian</v>
       </c>
       <c r="B4" t="str">
+        <f>[2]Personnes!B4</f>
         <v>Alexandra</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A5" t="str">
+        <f>[2]Personnes!A5</f>
         <v>L'Horset</v>
       </c>
       <c r="B5" t="str">
+        <f>[2]Personnes!B5</f>
         <v>Alice</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A6" t="str">
+        <f>[2]Personnes!A6</f>
         <v>Ledru</v>
       </c>
       <c r="B6" t="str">
+        <f>[2]Personnes!B6</f>
         <v>Analou</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A7" t="str">
+        <f>[2]Personnes!A7</f>
         <v>Mallet</v>
       </c>
       <c r="B7" t="str">
+        <f>[2]Personnes!B7</f>
         <v>Anna</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A8" t="str">
+        <f>[2]Personnes!A8</f>
         <v>Malric</v>
       </c>
       <c r="B8" t="str">
+        <f>[2]Personnes!B8</f>
         <v>Annouk</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A9" t="str">
+        <f>[2]Personnes!A9</f>
         <v>Noël</v>
       </c>
       <c r="B9" t="str">
+        <f>[2]Personnes!B9</f>
         <v>Antonin</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A10" t="str">
+        <f>[2]Personnes!A10</f>
         <v>Tessier</v>
       </c>
       <c r="B10" t="str">
+        <f>[2]Personnes!B10</f>
         <v>Arsène</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A11" t="str">
+        <f>[2]Personnes!A11</f>
         <v>Uldry</v>
       </c>
       <c r="B11" t="str">
+        <f>[2]Personnes!B11</f>
         <v>Arthur</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A12" t="str">
+        <f>[2]Personnes!A12</f>
         <v>Marchand</v>
       </c>
       <c r="B12" t="str">
+        <f>[2]Personnes!B12</f>
         <v>Athénaé</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A13" t="str">
+        <f>[2]Personnes!A13</f>
         <v>Magerand</v>
       </c>
       <c r="B13" t="str">
+        <f>[2]Personnes!B13</f>
         <v>Auxence</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A14" t="str">
+        <f>[2]Personnes!A14</f>
         <v>Baruch</v>
       </c>
       <c r="B14" t="str">
+        <f>[2]Personnes!B14</f>
         <v>Ava</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A15" t="str">
+        <f>[2]Personnes!A15</f>
         <v>Detrain</v>
       </c>
       <c r="B15" t="str">
+        <f>[2]Personnes!B15</f>
         <v>Benoît</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A16" t="str">
+        <f>[2]Personnes!A16</f>
         <v>Meige</v>
       </c>
       <c r="B16" t="str">
+        <f>[2]Personnes!B16</f>
         <v>Corentin</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17" t="str">
+        <f>[2]Personnes!A17</f>
         <v>De Filippo</v>
       </c>
       <c r="B17" t="str">
+        <f>[2]Personnes!B17</f>
         <v>Emma</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18" t="str">
+        <f>[2]Personnes!A18</f>
         <v>Maître</v>
       </c>
       <c r="B18" t="str">
+        <f>[2]Personnes!B18</f>
         <v>Enzo</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19" t="str">
+        <f>[2]Personnes!A19</f>
         <v>Prouvost</v>
       </c>
       <c r="B19" t="str">
+        <f>[2]Personnes!B19</f>
         <v>Eugénie</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20" t="str">
+        <f>[2]Personnes!A20</f>
         <v xml:space="preserve">Rakotonandrasana </v>
       </c>
       <c r="B20" t="str">
+        <f>[2]Personnes!B20</f>
         <v>Iris</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21" t="str">
+        <f>[2]Personnes!A21</f>
         <v>Bürgisser</v>
       </c>
       <c r="B21" t="str">
+        <f>[2]Personnes!B21</f>
         <v>Jamilah</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A22" t="str">
+        <f>[2]Personnes!A22</f>
         <v>Ruscio</v>
       </c>
       <c r="B22" t="str">
+        <f>[2]Personnes!B22</f>
         <v>Jolan</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A23" t="str">
+        <f>[2]Personnes!A23</f>
         <v>Wuilloud</v>
       </c>
       <c r="B23" t="str">
+        <f>[2]Personnes!B23</f>
         <v xml:space="preserve">Jonas </v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A24" t="str">
+        <f>[2]Personnes!A24</f>
         <v>Pirolley</v>
       </c>
       <c r="B24" t="str">
+        <f>[2]Personnes!B24</f>
         <v>Jules</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25" t="str">
+        <f>[2]Personnes!A25</f>
         <v>Chavaillaz</v>
       </c>
       <c r="B25" t="str">
+        <f>[2]Personnes!B25</f>
         <v>Julie</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A26" t="str">
+        <f>[2]Personnes!A26</f>
         <v>Oeschger</v>
       </c>
       <c r="B26" t="str">
+        <f>[2]Personnes!B26</f>
         <v>Kristel</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A27" t="str">
+        <f>[2]Personnes!A27</f>
         <v>Baltzinger</v>
       </c>
       <c r="B27" t="str">
+        <f>[2]Personnes!B27</f>
         <v>Léa</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A28" t="str">
+        <f>[2]Personnes!A28</f>
         <v>Chambaz</v>
       </c>
       <c r="B28" t="str">
+        <f>[2]Personnes!B28</f>
         <v>Léa</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A29" t="str">
+        <f>[2]Personnes!A29</f>
         <v>Ledru</v>
       </c>
       <c r="B29" t="str">
+        <f>[2]Personnes!B29</f>
         <v>Lina-Rosa</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A30" t="str">
+        <f>[2]Personnes!A30</f>
         <v>Jaquet</v>
       </c>
       <c r="B30" t="str">
+        <f>[2]Personnes!B30</f>
         <v>Lisa</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A31" t="str">
+        <f>[2]Personnes!A31</f>
         <v>Magnin</v>
       </c>
       <c r="B31" t="str">
+        <f>[2]Personnes!B31</f>
         <v>Lisa</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A32" t="str">
+        <f>[2]Personnes!A32</f>
         <v>Cardis</v>
       </c>
       <c r="B32" t="str">
+        <f>[2]Personnes!B32</f>
         <v>Louis</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A33" t="str">
+        <f>[2]Personnes!A33</f>
         <v>Post</v>
       </c>
       <c r="B33" t="str">
+        <f>[2]Personnes!B33</f>
         <v>Louis</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A34" t="str">
+        <f>[2]Personnes!A34</f>
         <v>Blanchard</v>
       </c>
       <c r="B34" t="str">
+        <f>[2]Personnes!B34</f>
         <v>Louise</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A35" t="str">
+        <f>[2]Personnes!A35</f>
         <v>Chastroux</v>
       </c>
       <c r="B35" t="str">
+        <f>[2]Personnes!B35</f>
         <v>Lucas</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A36" t="str">
+        <f>[2]Personnes!A36</f>
         <v>Meyer</v>
       </c>
       <c r="B36" t="str">
+        <f>[2]Personnes!B36</f>
         <v>Lucie</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A37" t="str">
+        <f>[2]Personnes!A37</f>
         <v>Ménétrey</v>
       </c>
       <c r="B37" t="str">
+        <f>[2]Personnes!B37</f>
         <v>Maëlan</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A38" t="str">
+        <f>[2]Personnes!A38</f>
         <v>Chambaz</v>
       </c>
       <c r="B38" t="str">
+        <f>[2]Personnes!B38</f>
         <v>Maëlle</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A39" t="str">
+        <f>[2]Personnes!A39</f>
         <v>Felix</v>
       </c>
       <c r="B39" t="str">
+        <f>[2]Personnes!B39</f>
         <v>Marius</v>
       </c>
       <c r="C39" t="s">
@@ -3746,33 +4801,41 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A40" t="str">
+        <f>[2]Personnes!A40</f>
         <v>Ledru</v>
       </c>
       <c r="B40" t="str">
+        <f>[2]Personnes!B40</f>
         <v>Marot</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A41" t="str">
+        <f>[2]Personnes!A41</f>
         <v>Cuinet</v>
       </c>
       <c r="B41" t="str">
+        <f>[2]Personnes!B41</f>
         <v>Mathis</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A42" t="str">
+        <f>[2]Personnes!A42</f>
         <v>Gavin</v>
       </c>
       <c r="B42" t="str">
+        <f>[2]Personnes!B42</f>
         <v>Matteo</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A43" t="str">
+        <f>[2]Personnes!A43</f>
         <v>Debray</v>
       </c>
       <c r="B43" t="str">
+        <f>[2]Personnes!B43</f>
         <v>Maxime</v>
       </c>
       <c r="C43" t="s">
@@ -3787,73 +4850,91 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A44" t="str">
+        <f>[2]Personnes!A44</f>
         <v>Corbelli</v>
       </c>
       <c r="B44" t="str">
+        <f>[2]Personnes!B44</f>
         <v>Maya</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A45" t="str">
+        <f>[2]Personnes!A45</f>
         <v>Pasche</v>
       </c>
       <c r="B45" t="str">
+        <f>[2]Personnes!B45</f>
         <v>Mickaël</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A46" t="str">
+        <f>[2]Personnes!A46</f>
         <v>Fargues</v>
       </c>
       <c r="B46" t="str">
+        <f>[2]Personnes!B46</f>
         <v>Morgana</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A47" t="str">
+        <f>[2]Personnes!A47</f>
         <v>Scyboz (Lambelet)</v>
       </c>
       <c r="B47" t="str">
+        <f>[2]Personnes!B47</f>
         <v>Morgane</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A48" t="str">
+        <f>[2]Personnes!A48</f>
         <v>Koux</v>
       </c>
       <c r="B48" t="str">
+        <f>[2]Personnes!B48</f>
         <v>Nathalia</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A49" t="str">
+        <f>[2]Personnes!A49</f>
         <v>Cherpillod</v>
       </c>
       <c r="B49" t="str">
+        <f>[2]Personnes!B49</f>
         <v>Noah</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A50" t="str">
+        <f>[2]Personnes!A50</f>
         <v>Chambaz</v>
       </c>
       <c r="B50" t="str">
+        <f>[2]Personnes!B50</f>
         <v>Patrick</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A51" t="str">
+        <f>[2]Personnes!A51</f>
         <v>Assaoui</v>
       </c>
       <c r="B51" t="str">
+        <f>[2]Personnes!B51</f>
         <v>Rama</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A52" t="str">
+        <f>[2]Personnes!A52</f>
         <v>Lacroze</v>
       </c>
       <c r="B52" t="str">
+        <f>[2]Personnes!B52</f>
         <v>Raphaël</v>
       </c>
       <c r="C52" t="s">
@@ -3868,94 +4949,136 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A53" t="str">
+        <f>[2]Personnes!A53</f>
         <v>Neidhart</v>
       </c>
       <c r="B53" t="str">
+        <f>[2]Personnes!B53</f>
         <v>Raphaëlle</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A54" t="str">
+        <f>[2]Personnes!A54</f>
         <v xml:space="preserve">Lanni </v>
       </c>
       <c r="B54" t="str">
+        <f>[2]Personnes!B54</f>
         <v>Roxanne</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A55" t="str">
+        <f>[2]Personnes!A55</f>
         <v>Schiesser</v>
       </c>
       <c r="B55" t="str">
+        <f>[2]Personnes!B55</f>
         <v>Sébastien</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A56" t="str">
+        <f>[2]Personnes!A56</f>
         <v>Lambelet</v>
       </c>
       <c r="B56" t="str">
+        <f>[2]Personnes!B56</f>
         <v>Simon</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A57" t="str">
+        <f>[2]Personnes!A57</f>
         <v>Cyprien</v>
       </c>
       <c r="B57" t="str">
+        <f>[2]Personnes!B57</f>
         <v>Theo</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A58" t="str">
+        <f>[2]Personnes!A58</f>
         <v>Clerici</v>
       </c>
       <c r="B58" t="str">
+        <f>[2]Personnes!B58</f>
         <v>Thibault</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A59" t="str">
+        <f>[2]Personnes!A59</f>
         <v>Ménétrey</v>
       </c>
       <c r="B59" t="str">
+        <f>[2]Personnes!B59</f>
         <v>Titouan</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A60" t="str">
+        <f>[2]Personnes!A60</f>
         <v>Clerici</v>
       </c>
       <c r="B60" t="str">
+        <f>[2]Personnes!B60</f>
         <v>Tristan</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A61" t="str">
+        <f>[2]Personnes!A61</f>
         <v>Bally</v>
       </c>
       <c r="B61" t="str">
+        <f>[2]Personnes!B61</f>
         <v>Yann</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A62" t="str">
+        <f>[2]Personnes!A62</f>
         <v>Ménétrey</v>
       </c>
       <c r="B62" t="str">
+        <f>[2]Personnes!B62</f>
         <v>Ysatis</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A63" t="str">
+        <f>[2]Personnes!A63</f>
         <v>Ménard</v>
       </c>
       <c r="B63" t="str">
+        <f>[2]Personnes!B63</f>
         <v>Mireille</v>
       </c>
     </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A64" t="str">
+        <f>[2]Personnes!A64</f>
+        <v>Rieger</v>
+      </c>
+      <c r="B64" t="str">
+        <f>[2]Personnes!B64</f>
+        <v>Maya</v>
+      </c>
+    </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
+  <protectedRanges>
+    <protectedRange sqref="C1:E1048576" name="Shifts"/>
+  </protectedRanges>
+  <conditionalFormatting sqref="A2:XFD65">
+    <cfRule type="expression" dxfId="2" priority="1">
+      <formula>MOD(ROW(),2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -3973,332 +5096,410 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7E4AE93-50CA-4EB1-98E3-757ADDFDDBBD}">
-  <dimension ref="A1:E63"/>
+  <sheetPr codeName="Sheet5">
+    <tabColor theme="9" tint="0.59999389629810485"/>
+  </sheetPr>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="2" width="14.921875" customWidth="1"/>
     <col min="3" max="3" width="11.765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A2" t="str" cm="1">
-        <f t="array" ref="A2:B63">_xlfn._xlws.FILTER('[1]Bénévoles 2026 V2'!$E:$F,'[1]Bénévoles 2026 V2'!$B:$B=TRUE)</f>
+      <c r="A2" t="str">
+        <f>[2]Personnes!A2</f>
         <v>Bouvet</v>
       </c>
       <c r="B2" t="str">
+        <f>[2]Personnes!B2</f>
         <v>Agathe</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A3" t="str">
+        <f>[2]Personnes!A3</f>
         <v>Bulka</v>
       </c>
       <c r="B3" t="str">
+        <f>[2]Personnes!B3</f>
         <v>Alegria Lily</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A4" t="str">
+        <f>[2]Personnes!A4</f>
         <v>Bastian</v>
       </c>
       <c r="B4" t="str">
+        <f>[2]Personnes!B4</f>
         <v>Alexandra</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A5" t="str">
+        <f>[2]Personnes!A5</f>
         <v>L'Horset</v>
       </c>
       <c r="B5" t="str">
+        <f>[2]Personnes!B5</f>
         <v>Alice</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A6" t="str">
+        <f>[2]Personnes!A6</f>
         <v>Ledru</v>
       </c>
       <c r="B6" t="str">
+        <f>[2]Personnes!B6</f>
         <v>Analou</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A7" t="str">
+        <f>[2]Personnes!A7</f>
         <v>Mallet</v>
       </c>
       <c r="B7" t="str">
+        <f>[2]Personnes!B7</f>
         <v>Anna</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A8" t="str">
+        <f>[2]Personnes!A8</f>
         <v>Malric</v>
       </c>
       <c r="B8" t="str">
+        <f>[2]Personnes!B8</f>
         <v>Annouk</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A9" t="str">
+        <f>[2]Personnes!A9</f>
         <v>Noël</v>
       </c>
       <c r="B9" t="str">
+        <f>[2]Personnes!B9</f>
         <v>Antonin</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A10" t="str">
+        <f>[2]Personnes!A10</f>
         <v>Tessier</v>
       </c>
       <c r="B10" t="str">
+        <f>[2]Personnes!B10</f>
         <v>Arsène</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A11" t="str">
+        <f>[2]Personnes!A11</f>
         <v>Uldry</v>
       </c>
       <c r="B11" t="str">
+        <f>[2]Personnes!B11</f>
         <v>Arthur</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A12" t="str">
+        <f>[2]Personnes!A12</f>
         <v>Marchand</v>
       </c>
       <c r="B12" t="str">
+        <f>[2]Personnes!B12</f>
         <v>Athénaé</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A13" t="str">
+        <f>[2]Personnes!A13</f>
         <v>Magerand</v>
       </c>
       <c r="B13" t="str">
+        <f>[2]Personnes!B13</f>
         <v>Auxence</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A14" t="str">
+        <f>[2]Personnes!A14</f>
         <v>Baruch</v>
       </c>
       <c r="B14" t="str">
+        <f>[2]Personnes!B14</f>
         <v>Ava</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A15" t="str">
+        <f>[2]Personnes!A15</f>
         <v>Detrain</v>
       </c>
       <c r="B15" t="str">
+        <f>[2]Personnes!B15</f>
         <v>Benoît</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A16" t="str">
+        <f>[2]Personnes!A16</f>
         <v>Meige</v>
       </c>
       <c r="B16" t="str">
+        <f>[2]Personnes!B16</f>
         <v>Corentin</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17" t="str">
+        <f>[2]Personnes!A17</f>
         <v>De Filippo</v>
       </c>
       <c r="B17" t="str">
+        <f>[2]Personnes!B17</f>
         <v>Emma</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18" t="str">
+        <f>[2]Personnes!A18</f>
         <v>Maître</v>
       </c>
       <c r="B18" t="str">
+        <f>[2]Personnes!B18</f>
         <v>Enzo</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19" t="str">
+        <f>[2]Personnes!A19</f>
         <v>Prouvost</v>
       </c>
       <c r="B19" t="str">
+        <f>[2]Personnes!B19</f>
         <v>Eugénie</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20" t="str">
+        <f>[2]Personnes!A20</f>
         <v xml:space="preserve">Rakotonandrasana </v>
       </c>
       <c r="B20" t="str">
+        <f>[2]Personnes!B20</f>
         <v>Iris</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21" t="str">
+        <f>[2]Personnes!A21</f>
         <v>Bürgisser</v>
       </c>
       <c r="B21" t="str">
+        <f>[2]Personnes!B21</f>
         <v>Jamilah</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A22" t="str">
+        <f>[2]Personnes!A22</f>
         <v>Ruscio</v>
       </c>
       <c r="B22" t="str">
+        <f>[2]Personnes!B22</f>
         <v>Jolan</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A23" t="str">
+        <f>[2]Personnes!A23</f>
         <v>Wuilloud</v>
       </c>
       <c r="B23" t="str">
+        <f>[2]Personnes!B23</f>
         <v xml:space="preserve">Jonas </v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A24" t="str">
+        <f>[2]Personnes!A24</f>
         <v>Pirolley</v>
       </c>
       <c r="B24" t="str">
+        <f>[2]Personnes!B24</f>
         <v>Jules</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25" t="str">
+        <f>[2]Personnes!A25</f>
         <v>Chavaillaz</v>
       </c>
       <c r="B25" t="str">
+        <f>[2]Personnes!B25</f>
         <v>Julie</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A26" t="str">
+        <f>[2]Personnes!A26</f>
         <v>Oeschger</v>
       </c>
       <c r="B26" t="str">
+        <f>[2]Personnes!B26</f>
         <v>Kristel</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A27" t="str">
+        <f>[2]Personnes!A27</f>
         <v>Baltzinger</v>
       </c>
       <c r="B27" t="str">
+        <f>[2]Personnes!B27</f>
         <v>Léa</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A28" t="str">
+        <f>[2]Personnes!A28</f>
         <v>Chambaz</v>
       </c>
       <c r="B28" t="str">
+        <f>[2]Personnes!B28</f>
         <v>Léa</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A29" t="str">
+        <f>[2]Personnes!A29</f>
         <v>Ledru</v>
       </c>
       <c r="B29" t="str">
+        <f>[2]Personnes!B29</f>
         <v>Lina-Rosa</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A30" t="str">
+        <f>[2]Personnes!A30</f>
         <v>Jaquet</v>
       </c>
       <c r="B30" t="str">
+        <f>[2]Personnes!B30</f>
         <v>Lisa</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A31" t="str">
+        <f>[2]Personnes!A31</f>
         <v>Magnin</v>
       </c>
       <c r="B31" t="str">
+        <f>[2]Personnes!B31</f>
         <v>Lisa</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A32" t="str">
+        <f>[2]Personnes!A32</f>
         <v>Cardis</v>
       </c>
       <c r="B32" t="str">
+        <f>[2]Personnes!B32</f>
         <v>Louis</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A33" t="str">
+        <f>[2]Personnes!A33</f>
         <v>Post</v>
       </c>
       <c r="B33" t="str">
+        <f>[2]Personnes!B33</f>
         <v>Louis</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A34" t="str">
+        <f>[2]Personnes!A34</f>
         <v>Blanchard</v>
       </c>
       <c r="B34" t="str">
+        <f>[2]Personnes!B34</f>
         <v>Louise</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A35" t="str">
+        <f>[2]Personnes!A35</f>
         <v>Chastroux</v>
       </c>
       <c r="B35" t="str">
+        <f>[2]Personnes!B35</f>
         <v>Lucas</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A36" t="str">
+        <f>[2]Personnes!A36</f>
         <v>Meyer</v>
       </c>
       <c r="B36" t="str">
+        <f>[2]Personnes!B36</f>
         <v>Lucie</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A37" t="str">
+        <f>[2]Personnes!A37</f>
         <v>Ménétrey</v>
       </c>
       <c r="B37" t="str">
+        <f>[2]Personnes!B37</f>
         <v>Maëlan</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A38" t="str">
+        <f>[2]Personnes!A38</f>
         <v>Chambaz</v>
       </c>
       <c r="B38" t="str">
+        <f>[2]Personnes!B38</f>
         <v>Maëlle</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A39" t="str">
+        <f>[2]Personnes!A39</f>
         <v>Felix</v>
       </c>
       <c r="B39" t="str">
+        <f>[2]Personnes!B39</f>
         <v>Marius</v>
       </c>
       <c r="C39" t="s">
@@ -4313,33 +5514,41 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A40" t="str">
+        <f>[2]Personnes!A40</f>
         <v>Ledru</v>
       </c>
       <c r="B40" t="str">
+        <f>[2]Personnes!B40</f>
         <v>Marot</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A41" t="str">
+        <f>[2]Personnes!A41</f>
         <v>Cuinet</v>
       </c>
       <c r="B41" t="str">
+        <f>[2]Personnes!B41</f>
         <v>Mathis</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A42" t="str">
+        <f>[2]Personnes!A42</f>
         <v>Gavin</v>
       </c>
       <c r="B42" t="str">
+        <f>[2]Personnes!B42</f>
         <v>Matteo</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A43" t="str">
+        <f>[2]Personnes!A43</f>
         <v>Debray</v>
       </c>
       <c r="B43" t="str">
+        <f>[2]Personnes!B43</f>
         <v>Maxime</v>
       </c>
       <c r="C43" t="s">
@@ -4354,73 +5563,91 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A44" t="str">
+        <f>[2]Personnes!A44</f>
         <v>Corbelli</v>
       </c>
       <c r="B44" t="str">
+        <f>[2]Personnes!B44</f>
         <v>Maya</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A45" t="str">
+        <f>[2]Personnes!A45</f>
         <v>Pasche</v>
       </c>
       <c r="B45" t="str">
+        <f>[2]Personnes!B45</f>
         <v>Mickaël</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A46" t="str">
+        <f>[2]Personnes!A46</f>
         <v>Fargues</v>
       </c>
       <c r="B46" t="str">
+        <f>[2]Personnes!B46</f>
         <v>Morgana</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A47" t="str">
+        <f>[2]Personnes!A47</f>
         <v>Scyboz (Lambelet)</v>
       </c>
       <c r="B47" t="str">
+        <f>[2]Personnes!B47</f>
         <v>Morgane</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A48" t="str">
+        <f>[2]Personnes!A48</f>
         <v>Koux</v>
       </c>
       <c r="B48" t="str">
+        <f>[2]Personnes!B48</f>
         <v>Nathalia</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A49" t="str">
+        <f>[2]Personnes!A49</f>
         <v>Cherpillod</v>
       </c>
       <c r="B49" t="str">
+        <f>[2]Personnes!B49</f>
         <v>Noah</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A50" t="str">
+        <f>[2]Personnes!A50</f>
         <v>Chambaz</v>
       </c>
       <c r="B50" t="str">
+        <f>[2]Personnes!B50</f>
         <v>Patrick</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A51" t="str">
+        <f>[2]Personnes!A51</f>
         <v>Assaoui</v>
       </c>
       <c r="B51" t="str">
+        <f>[2]Personnes!B51</f>
         <v>Rama</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A52" t="str">
+        <f>[2]Personnes!A52</f>
         <v>Lacroze</v>
       </c>
       <c r="B52" t="str">
+        <f>[2]Personnes!B52</f>
         <v>Raphaël</v>
       </c>
       <c r="C52" t="s">
@@ -4435,94 +5662,136 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A53" t="str">
+        <f>[2]Personnes!A53</f>
         <v>Neidhart</v>
       </c>
       <c r="B53" t="str">
+        <f>[2]Personnes!B53</f>
         <v>Raphaëlle</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A54" t="str">
+        <f>[2]Personnes!A54</f>
         <v xml:space="preserve">Lanni </v>
       </c>
       <c r="B54" t="str">
+        <f>[2]Personnes!B54</f>
         <v>Roxanne</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A55" t="str">
+        <f>[2]Personnes!A55</f>
         <v>Schiesser</v>
       </c>
       <c r="B55" t="str">
+        <f>[2]Personnes!B55</f>
         <v>Sébastien</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A56" t="str">
+        <f>[2]Personnes!A56</f>
         <v>Lambelet</v>
       </c>
       <c r="B56" t="str">
+        <f>[2]Personnes!B56</f>
         <v>Simon</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A57" t="str">
+        <f>[2]Personnes!A57</f>
         <v>Cyprien</v>
       </c>
       <c r="B57" t="str">
+        <f>[2]Personnes!B57</f>
         <v>Theo</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A58" t="str">
+        <f>[2]Personnes!A58</f>
         <v>Clerici</v>
       </c>
       <c r="B58" t="str">
+        <f>[2]Personnes!B58</f>
         <v>Thibault</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A59" t="str">
+        <f>[2]Personnes!A59</f>
         <v>Ménétrey</v>
       </c>
       <c r="B59" t="str">
+        <f>[2]Personnes!B59</f>
         <v>Titouan</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A60" t="str">
+        <f>[2]Personnes!A60</f>
         <v>Clerici</v>
       </c>
       <c r="B60" t="str">
+        <f>[2]Personnes!B60</f>
         <v>Tristan</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A61" t="str">
+        <f>[2]Personnes!A61</f>
         <v>Bally</v>
       </c>
       <c r="B61" t="str">
+        <f>[2]Personnes!B61</f>
         <v>Yann</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A62" t="str">
+        <f>[2]Personnes!A62</f>
         <v>Ménétrey</v>
       </c>
       <c r="B62" t="str">
+        <f>[2]Personnes!B62</f>
         <v>Ysatis</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A63" t="str">
+        <f>[2]Personnes!A63</f>
         <v>Ménard</v>
       </c>
       <c r="B63" t="str">
+        <f>[2]Personnes!B63</f>
         <v>Mireille</v>
       </c>
     </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A64" t="str">
+        <f>[2]Personnes!A64</f>
+        <v>Rieger</v>
+      </c>
+      <c r="B64" t="str">
+        <f>[2]Personnes!B64</f>
+        <v>Maya</v>
+      </c>
+    </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
+  <protectedRanges>
+    <protectedRange sqref="C1:E1048576" name="Shifts"/>
+  </protectedRanges>
+  <conditionalFormatting sqref="A2:XFD65">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>MOD(ROW(),2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -4540,332 +5809,410 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B965F37E-7321-434E-8400-31D7FE0BF594}">
-  <dimension ref="A1:E63"/>
+  <sheetPr codeName="Sheet6">
+    <tabColor theme="2" tint="-0.249977111117893"/>
+  </sheetPr>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="2" width="14.921875" customWidth="1"/>
     <col min="3" max="3" width="11.765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="9" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A2" t="str" cm="1">
-        <f t="array" ref="A2:B63">_xlfn._xlws.FILTER('[1]Bénévoles 2026 V2'!$E:$F,'[1]Bénévoles 2026 V2'!$B:$B=TRUE)</f>
+      <c r="A2" t="str">
+        <f>[2]Personnes!A2</f>
         <v>Bouvet</v>
       </c>
       <c r="B2" t="str">
+        <f>[2]Personnes!B2</f>
         <v>Agathe</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A3" t="str">
+        <f>[2]Personnes!A3</f>
         <v>Bulka</v>
       </c>
       <c r="B3" t="str">
+        <f>[2]Personnes!B3</f>
         <v>Alegria Lily</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A4" t="str">
+        <f>[2]Personnes!A4</f>
         <v>Bastian</v>
       </c>
       <c r="B4" t="str">
+        <f>[2]Personnes!B4</f>
         <v>Alexandra</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A5" t="str">
+        <f>[2]Personnes!A5</f>
         <v>L'Horset</v>
       </c>
       <c r="B5" t="str">
+        <f>[2]Personnes!B5</f>
         <v>Alice</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A6" t="str">
+        <f>[2]Personnes!A6</f>
         <v>Ledru</v>
       </c>
       <c r="B6" t="str">
+        <f>[2]Personnes!B6</f>
         <v>Analou</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A7" t="str">
+        <f>[2]Personnes!A7</f>
         <v>Mallet</v>
       </c>
       <c r="B7" t="str">
+        <f>[2]Personnes!B7</f>
         <v>Anna</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A8" t="str">
+        <f>[2]Personnes!A8</f>
         <v>Malric</v>
       </c>
       <c r="B8" t="str">
+        <f>[2]Personnes!B8</f>
         <v>Annouk</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A9" t="str">
+        <f>[2]Personnes!A9</f>
         <v>Noël</v>
       </c>
       <c r="B9" t="str">
+        <f>[2]Personnes!B9</f>
         <v>Antonin</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A10" t="str">
+        <f>[2]Personnes!A10</f>
         <v>Tessier</v>
       </c>
       <c r="B10" t="str">
+        <f>[2]Personnes!B10</f>
         <v>Arsène</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A11" t="str">
+        <f>[2]Personnes!A11</f>
         <v>Uldry</v>
       </c>
       <c r="B11" t="str">
+        <f>[2]Personnes!B11</f>
         <v>Arthur</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A12" t="str">
+        <f>[2]Personnes!A12</f>
         <v>Marchand</v>
       </c>
       <c r="B12" t="str">
+        <f>[2]Personnes!B12</f>
         <v>Athénaé</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A13" t="str">
+        <f>[2]Personnes!A13</f>
         <v>Magerand</v>
       </c>
       <c r="B13" t="str">
+        <f>[2]Personnes!B13</f>
         <v>Auxence</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A14" t="str">
+        <f>[2]Personnes!A14</f>
         <v>Baruch</v>
       </c>
       <c r="B14" t="str">
+        <f>[2]Personnes!B14</f>
         <v>Ava</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A15" t="str">
+        <f>[2]Personnes!A15</f>
         <v>Detrain</v>
       </c>
       <c r="B15" t="str">
+        <f>[2]Personnes!B15</f>
         <v>Benoît</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A16" t="str">
+        <f>[2]Personnes!A16</f>
         <v>Meige</v>
       </c>
       <c r="B16" t="str">
+        <f>[2]Personnes!B16</f>
         <v>Corentin</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17" t="str">
+        <f>[2]Personnes!A17</f>
         <v>De Filippo</v>
       </c>
       <c r="B17" t="str">
+        <f>[2]Personnes!B17</f>
         <v>Emma</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18" t="str">
+        <f>[2]Personnes!A18</f>
         <v>Maître</v>
       </c>
       <c r="B18" t="str">
+        <f>[2]Personnes!B18</f>
         <v>Enzo</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19" t="str">
+        <f>[2]Personnes!A19</f>
         <v>Prouvost</v>
       </c>
       <c r="B19" t="str">
+        <f>[2]Personnes!B19</f>
         <v>Eugénie</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20" t="str">
+        <f>[2]Personnes!A20</f>
         <v xml:space="preserve">Rakotonandrasana </v>
       </c>
       <c r="B20" t="str">
+        <f>[2]Personnes!B20</f>
         <v>Iris</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21" t="str">
+        <f>[2]Personnes!A21</f>
         <v>Bürgisser</v>
       </c>
       <c r="B21" t="str">
+        <f>[2]Personnes!B21</f>
         <v>Jamilah</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A22" t="str">
+        <f>[2]Personnes!A22</f>
         <v>Ruscio</v>
       </c>
       <c r="B22" t="str">
+        <f>[2]Personnes!B22</f>
         <v>Jolan</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A23" t="str">
+        <f>[2]Personnes!A23</f>
         <v>Wuilloud</v>
       </c>
       <c r="B23" t="str">
+        <f>[2]Personnes!B23</f>
         <v xml:space="preserve">Jonas </v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A24" t="str">
+        <f>[2]Personnes!A24</f>
         <v>Pirolley</v>
       </c>
       <c r="B24" t="str">
+        <f>[2]Personnes!B24</f>
         <v>Jules</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25" t="str">
+        <f>[2]Personnes!A25</f>
         <v>Chavaillaz</v>
       </c>
       <c r="B25" t="str">
+        <f>[2]Personnes!B25</f>
         <v>Julie</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A26" t="str">
+        <f>[2]Personnes!A26</f>
         <v>Oeschger</v>
       </c>
       <c r="B26" t="str">
+        <f>[2]Personnes!B26</f>
         <v>Kristel</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A27" t="str">
+        <f>[2]Personnes!A27</f>
         <v>Baltzinger</v>
       </c>
       <c r="B27" t="str">
+        <f>[2]Personnes!B27</f>
         <v>Léa</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A28" t="str">
+        <f>[2]Personnes!A28</f>
         <v>Chambaz</v>
       </c>
       <c r="B28" t="str">
+        <f>[2]Personnes!B28</f>
         <v>Léa</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A29" t="str">
+        <f>[2]Personnes!A29</f>
         <v>Ledru</v>
       </c>
       <c r="B29" t="str">
+        <f>[2]Personnes!B29</f>
         <v>Lina-Rosa</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A30" t="str">
+        <f>[2]Personnes!A30</f>
         <v>Jaquet</v>
       </c>
       <c r="B30" t="str">
+        <f>[2]Personnes!B30</f>
         <v>Lisa</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A31" t="str">
+        <f>[2]Personnes!A31</f>
         <v>Magnin</v>
       </c>
       <c r="B31" t="str">
+        <f>[2]Personnes!B31</f>
         <v>Lisa</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A32" t="str">
+        <f>[2]Personnes!A32</f>
         <v>Cardis</v>
       </c>
       <c r="B32" t="str">
+        <f>[2]Personnes!B32</f>
         <v>Louis</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A33" t="str">
+        <f>[2]Personnes!A33</f>
         <v>Post</v>
       </c>
       <c r="B33" t="str">
+        <f>[2]Personnes!B33</f>
         <v>Louis</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A34" t="str">
+        <f>[2]Personnes!A34</f>
         <v>Blanchard</v>
       </c>
       <c r="B34" t="str">
+        <f>[2]Personnes!B34</f>
         <v>Louise</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A35" t="str">
+        <f>[2]Personnes!A35</f>
         <v>Chastroux</v>
       </c>
       <c r="B35" t="str">
+        <f>[2]Personnes!B35</f>
         <v>Lucas</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A36" t="str">
+        <f>[2]Personnes!A36</f>
         <v>Meyer</v>
       </c>
       <c r="B36" t="str">
+        <f>[2]Personnes!B36</f>
         <v>Lucie</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A37" t="str">
+        <f>[2]Personnes!A37</f>
         <v>Ménétrey</v>
       </c>
       <c r="B37" t="str">
+        <f>[2]Personnes!B37</f>
         <v>Maëlan</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A38" t="str">
+        <f>[2]Personnes!A38</f>
         <v>Chambaz</v>
       </c>
       <c r="B38" t="str">
+        <f>[2]Personnes!B38</f>
         <v>Maëlle</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A39" t="str">
+        <f>[2]Personnes!A39</f>
         <v>Felix</v>
       </c>
       <c r="B39" t="str">
+        <f>[2]Personnes!B39</f>
         <v>Marius</v>
       </c>
       <c r="C39" t="s">
@@ -4880,33 +6227,41 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A40" t="str">
+        <f>[2]Personnes!A40</f>
         <v>Ledru</v>
       </c>
       <c r="B40" t="str">
+        <f>[2]Personnes!B40</f>
         <v>Marot</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A41" t="str">
+        <f>[2]Personnes!A41</f>
         <v>Cuinet</v>
       </c>
       <c r="B41" t="str">
+        <f>[2]Personnes!B41</f>
         <v>Mathis</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A42" t="str">
+        <f>[2]Personnes!A42</f>
         <v>Gavin</v>
       </c>
       <c r="B42" t="str">
+        <f>[2]Personnes!B42</f>
         <v>Matteo</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A43" t="str">
+        <f>[2]Personnes!A43</f>
         <v>Debray</v>
       </c>
       <c r="B43" t="str">
+        <f>[2]Personnes!B43</f>
         <v>Maxime</v>
       </c>
       <c r="C43" t="s">
@@ -4921,73 +6276,91 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A44" t="str">
+        <f>[2]Personnes!A44</f>
         <v>Corbelli</v>
       </c>
       <c r="B44" t="str">
+        <f>[2]Personnes!B44</f>
         <v>Maya</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A45" t="str">
+        <f>[2]Personnes!A45</f>
         <v>Pasche</v>
       </c>
       <c r="B45" t="str">
+        <f>[2]Personnes!B45</f>
         <v>Mickaël</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A46" t="str">
+        <f>[2]Personnes!A46</f>
         <v>Fargues</v>
       </c>
       <c r="B46" t="str">
+        <f>[2]Personnes!B46</f>
         <v>Morgana</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A47" t="str">
+        <f>[2]Personnes!A47</f>
         <v>Scyboz (Lambelet)</v>
       </c>
       <c r="B47" t="str">
+        <f>[2]Personnes!B47</f>
         <v>Morgane</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A48" t="str">
+        <f>[2]Personnes!A48</f>
         <v>Koux</v>
       </c>
       <c r="B48" t="str">
+        <f>[2]Personnes!B48</f>
         <v>Nathalia</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A49" t="str">
+        <f>[2]Personnes!A49</f>
         <v>Cherpillod</v>
       </c>
       <c r="B49" t="str">
+        <f>[2]Personnes!B49</f>
         <v>Noah</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A50" t="str">
+        <f>[2]Personnes!A50</f>
         <v>Chambaz</v>
       </c>
       <c r="B50" t="str">
+        <f>[2]Personnes!B50</f>
         <v>Patrick</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A51" t="str">
+        <f>[2]Personnes!A51</f>
         <v>Assaoui</v>
       </c>
       <c r="B51" t="str">
+        <f>[2]Personnes!B51</f>
         <v>Rama</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A52" t="str">
+        <f>[2]Personnes!A52</f>
         <v>Lacroze</v>
       </c>
       <c r="B52" t="str">
+        <f>[2]Personnes!B52</f>
         <v>Raphaël</v>
       </c>
       <c r="C52" t="s">
@@ -5002,94 +6375,136 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A53" t="str">
+        <f>[2]Personnes!A53</f>
         <v>Neidhart</v>
       </c>
       <c r="B53" t="str">
+        <f>[2]Personnes!B53</f>
         <v>Raphaëlle</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A54" t="str">
+        <f>[2]Personnes!A54</f>
         <v xml:space="preserve">Lanni </v>
       </c>
       <c r="B54" t="str">
+        <f>[2]Personnes!B54</f>
         <v>Roxanne</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A55" t="str">
+        <f>[2]Personnes!A55</f>
         <v>Schiesser</v>
       </c>
       <c r="B55" t="str">
+        <f>[2]Personnes!B55</f>
         <v>Sébastien</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A56" t="str">
+        <f>[2]Personnes!A56</f>
         <v>Lambelet</v>
       </c>
       <c r="B56" t="str">
+        <f>[2]Personnes!B56</f>
         <v>Simon</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A57" t="str">
+        <f>[2]Personnes!A57</f>
         <v>Cyprien</v>
       </c>
       <c r="B57" t="str">
+        <f>[2]Personnes!B57</f>
         <v>Theo</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A58" t="str">
+        <f>[2]Personnes!A58</f>
         <v>Clerici</v>
       </c>
       <c r="B58" t="str">
+        <f>[2]Personnes!B58</f>
         <v>Thibault</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A59" t="str">
+        <f>[2]Personnes!A59</f>
         <v>Ménétrey</v>
       </c>
       <c r="B59" t="str">
+        <f>[2]Personnes!B59</f>
         <v>Titouan</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A60" t="str">
+        <f>[2]Personnes!A60</f>
         <v>Clerici</v>
       </c>
       <c r="B60" t="str">
+        <f>[2]Personnes!B60</f>
         <v>Tristan</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A61" t="str">
+        <f>[2]Personnes!A61</f>
         <v>Bally</v>
       </c>
       <c r="B61" t="str">
+        <f>[2]Personnes!B61</f>
         <v>Yann</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A62" t="str">
+        <f>[2]Personnes!A62</f>
         <v>Ménétrey</v>
       </c>
       <c r="B62" t="str">
+        <f>[2]Personnes!B62</f>
         <v>Ysatis</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A63" t="str">
+        <f>[2]Personnes!A63</f>
         <v>Ménard</v>
       </c>
       <c r="B63" t="str">
+        <f>[2]Personnes!B63</f>
         <v>Mireille</v>
       </c>
     </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A64" t="str">
+        <f>[2]Personnes!A64</f>
+        <v>Rieger</v>
+      </c>
+      <c r="B64" t="str">
+        <f>[2]Personnes!B64</f>
+        <v>Maya</v>
+      </c>
+    </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
+  <protectedRanges>
+    <protectedRange sqref="C1:E1048576" name="Shifts"/>
+  </protectedRanges>
+  <conditionalFormatting sqref="A2:XFD65">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>MOD(ROW(),2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -5107,6 +6522,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C8EFFCD-CA70-46B8-8E6B-FC87ED018E1A}">
+  <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:A20"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
@@ -5115,120 +6531,120 @@
   <sheetData>
     <row r="1" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="str">
-        <f>[2]Tâches!$A1</f>
+        <f>[1]Tâches!$A1</f>
         <v>Tâches</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="str">
-        <f>[2]Tâches!$A2</f>
+        <f>[1]Tâches!$A2</f>
         <v>Accueil</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="str">
-        <f>[2]Tâches!$A3</f>
+        <f>[1]Tâches!$A3</f>
         <v>Abeilles Ruche</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="str">
-        <f>[2]Tâches!$A4</f>
+        <f>[1]Tâches!$A4</f>
         <v>Ailes</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="str">
-        <f>[2]Tâches!$A5</f>
+        <f>[1]Tâches!$A5</f>
         <v>Bar loges</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="str">
-        <f>[2]Tâches!$A6</f>
+        <f>[1]Tâches!$A6</f>
         <v>Bar public</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="str">
-        <f>[2]Tâches!$A7</f>
+        <f>[1]Tâches!$A7</f>
         <v>Bourdon.ne</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="str">
-        <f>[2]Tâches!$A8</f>
+        <f>[1]Tâches!$A8</f>
         <v>Entrée backstage</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="str">
-        <f>[2]Tâches!$A9</f>
+        <f>[1]Tâches!$A9</f>
         <v>Horaires</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="str">
-        <f>[2]Tâches!$A10</f>
+        <f>[1]Tâches!$A10</f>
         <v>Déambule Gerry</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="str">
-        <f>[2]Tâches!$A11</f>
+        <f>[1]Tâches!$A11</f>
         <v>Déambule Colbok</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="str">
-        <f>[2]Tâches!$A12</f>
+        <f>[1]Tâches!$A12</f>
         <v>Déambule Goulus</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="str">
-        <f>[2]Tâches!$A13</f>
+        <f>[1]Tâches!$A13</f>
         <v>Déambule Ko-compagnie</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A15" t="str">
-        <f>[2]Tâches!$A14</f>
+        <f>[1]Tâches!$A14</f>
         <v>Déambule Spoutnik</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" t="str">
-        <f>[2]Tâches!$A15</f>
+        <f>[1]Tâches!$A15</f>
         <v>Déambule FBI</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17" t="str">
-        <f>[2]Tâches!$A16</f>
+        <f>[1]Tâches!$A16</f>
         <v>Tech PCGB</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A18" t="str">
-        <f>[2]Tâches!$A17</f>
+        <f>[1]Tâches!$A17</f>
         <v>Tech Jacquard</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19" t="str">
-        <f>[2]Tâches!$A18</f>
+        <f>[1]Tâches!$A18</f>
         <v>Tech Muchmuche</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A20" t="str">
-        <f>[2]Tâches!$A19</f>
+        <f>[1]Tâches!$A19</f>
         <v>Tech T'es rien…</v>
       </c>
     </row>

--- a/data/shifts_fixes.xlsx
+++ b/data/shifts_fixes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sschies1\_code\1.09_VScode\06_VoeuxConcerts\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EB75E46-24F0-4FDA-BBCA-7337DB391D55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B006F675-E766-468A-A0B9-70B5AB6295FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25490" yWindow="1480" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mardi" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
   <definedNames>
     <definedName name="FromArray_1">_xlfn.ANCHORARRAY(Mardi!$A$2)</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterate="1" iterateCount="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="11">
   <si>
     <t>Nom</t>
   </si>
@@ -84,6 +84,9 @@
   </si>
   <si>
     <t>Tech Jacquard</t>
+  </si>
+  <si>
+    <t>Tech Phusis</t>
   </si>
 </sst>
 </file>
@@ -1303,118 +1306,517 @@
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="Mardi"/>
-      <sheetName val="Mercredi"/>
-      <sheetName val="Jeudi"/>
-      <sheetName val="Vendredi"/>
-      <sheetName val="Samedi"/>
-      <sheetName val="Dimanche"/>
-      <sheetName val="Tâches"/>
+      <sheetName val="Personnes"/>
+      <sheetName val="LOOKUP"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6">
-        <row r="1">
-          <cell r="A1" t="str">
-            <v>Tâches</v>
-          </cell>
-        </row>
+      <sheetData sheetId="0">
         <row r="2">
           <cell r="A2" t="str">
-            <v>Accueil</v>
+            <v>Bouvet</v>
+          </cell>
+          <cell r="B2" t="str">
+            <v>Agathe</v>
           </cell>
         </row>
         <row r="3">
           <cell r="A3" t="str">
-            <v>Abeilles Ruche</v>
+            <v>Bulka</v>
+          </cell>
+          <cell r="B3" t="str">
+            <v>Alegria Lily</v>
           </cell>
         </row>
         <row r="4">
           <cell r="A4" t="str">
-            <v>Ailes</v>
+            <v>Bastian</v>
+          </cell>
+          <cell r="B4" t="str">
+            <v>Alexandra</v>
           </cell>
         </row>
         <row r="5">
           <cell r="A5" t="str">
-            <v>Bar loges</v>
+            <v>L'Horset</v>
+          </cell>
+          <cell r="B5" t="str">
+            <v>Alice</v>
           </cell>
         </row>
         <row r="6">
           <cell r="A6" t="str">
-            <v>Bar public</v>
+            <v>Ledru</v>
+          </cell>
+          <cell r="B6" t="str">
+            <v>Analou</v>
           </cell>
         </row>
         <row r="7">
           <cell r="A7" t="str">
-            <v>Bourdon.ne</v>
+            <v>Mallet</v>
+          </cell>
+          <cell r="B7" t="str">
+            <v>Anna</v>
           </cell>
         </row>
         <row r="8">
           <cell r="A8" t="str">
-            <v>Entrée backstage</v>
+            <v>Malric</v>
+          </cell>
+          <cell r="B8" t="str">
+            <v>Annouk</v>
           </cell>
         </row>
         <row r="9">
           <cell r="A9" t="str">
-            <v>Horaires</v>
+            <v>Noël</v>
+          </cell>
+          <cell r="B9" t="str">
+            <v>Antonin</v>
           </cell>
         </row>
         <row r="10">
           <cell r="A10" t="str">
-            <v>Déambule Gerry</v>
+            <v>Tessier</v>
+          </cell>
+          <cell r="B10" t="str">
+            <v>Arsène</v>
           </cell>
         </row>
         <row r="11">
           <cell r="A11" t="str">
-            <v>Déambule Colbok</v>
+            <v>Uldry</v>
+          </cell>
+          <cell r="B11" t="str">
+            <v>Arthur</v>
           </cell>
         </row>
         <row r="12">
           <cell r="A12" t="str">
-            <v>Déambule Goulus</v>
+            <v>Marchand</v>
+          </cell>
+          <cell r="B12" t="str">
+            <v>Athénaé</v>
           </cell>
         </row>
         <row r="13">
           <cell r="A13" t="str">
-            <v>Déambule Ko-compagnie</v>
+            <v>Magerand</v>
+          </cell>
+          <cell r="B13" t="str">
+            <v>Auxence</v>
           </cell>
         </row>
         <row r="14">
           <cell r="A14" t="str">
-            <v>Déambule Spoutnik</v>
+            <v>Baruch</v>
+          </cell>
+          <cell r="B14" t="str">
+            <v>Ava</v>
           </cell>
         </row>
         <row r="15">
           <cell r="A15" t="str">
-            <v>Déambule FBI</v>
+            <v>Detrain</v>
+          </cell>
+          <cell r="B15" t="str">
+            <v>Benoît</v>
           </cell>
         </row>
         <row r="16">
           <cell r="A16" t="str">
-            <v>Tech PCGB</v>
+            <v>Meige</v>
+          </cell>
+          <cell r="B16" t="str">
+            <v>Corentin</v>
           </cell>
         </row>
         <row r="17">
           <cell r="A17" t="str">
-            <v>Tech Jacquard</v>
+            <v>De Filippo</v>
+          </cell>
+          <cell r="B17" t="str">
+            <v>Emma</v>
           </cell>
         </row>
         <row r="18">
           <cell r="A18" t="str">
-            <v>Tech Muchmuche</v>
+            <v>Maître</v>
+          </cell>
+          <cell r="B18" t="str">
+            <v>Enzo</v>
           </cell>
         </row>
         <row r="19">
           <cell r="A19" t="str">
-            <v>Tech T'es rien…</v>
+            <v>Prouvost</v>
+          </cell>
+          <cell r="B19" t="str">
+            <v>Eugénie</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="A20" t="str">
+            <v xml:space="preserve">Rakotonandrasana </v>
+          </cell>
+          <cell r="B20" t="str">
+            <v>Iris</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="A21" t="str">
+            <v>Bürgisser</v>
+          </cell>
+          <cell r="B21" t="str">
+            <v>Jamilah</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="A22" t="str">
+            <v>Ruscio</v>
+          </cell>
+          <cell r="B22" t="str">
+            <v>Jolan</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="A23" t="str">
+            <v>Wuilloud</v>
+          </cell>
+          <cell r="B23" t="str">
+            <v xml:space="preserve">Jonas </v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="A24" t="str">
+            <v>Pirolley</v>
+          </cell>
+          <cell r="B24" t="str">
+            <v>Jules</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="A25" t="str">
+            <v>Chavaillaz</v>
+          </cell>
+          <cell r="B25" t="str">
+            <v>Julie</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="A26" t="str">
+            <v>Oeschger</v>
+          </cell>
+          <cell r="B26" t="str">
+            <v>Kristel</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="A27" t="str">
+            <v>Baltzinger</v>
+          </cell>
+          <cell r="B27" t="str">
+            <v>Léa</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="A28" t="str">
+            <v>Chambaz</v>
+          </cell>
+          <cell r="B28" t="str">
+            <v>Léa</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="A29" t="str">
+            <v>Ledru</v>
+          </cell>
+          <cell r="B29" t="str">
+            <v>Lina-Rosa</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="A30" t="str">
+            <v>Jaquet</v>
+          </cell>
+          <cell r="B30" t="str">
+            <v>Lisa</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="A31" t="str">
+            <v>Magnin</v>
+          </cell>
+          <cell r="B31" t="str">
+            <v>Lisa</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="A32" t="str">
+            <v>Cardis</v>
+          </cell>
+          <cell r="B32" t="str">
+            <v>Louis</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="A33" t="str">
+            <v>Post</v>
+          </cell>
+          <cell r="B33" t="str">
+            <v>Louis</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="A34" t="str">
+            <v>Blanchard</v>
+          </cell>
+          <cell r="B34" t="str">
+            <v>Louise</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="A35" t="str">
+            <v>Chastroux</v>
+          </cell>
+          <cell r="B35" t="str">
+            <v>Lucas</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="A36" t="str">
+            <v>Meyer</v>
+          </cell>
+          <cell r="B36" t="str">
+            <v>Lucie</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="A37" t="str">
+            <v>Ménétrey</v>
+          </cell>
+          <cell r="B37" t="str">
+            <v>Maëlan</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="A38" t="str">
+            <v>Chambaz</v>
+          </cell>
+          <cell r="B38" t="str">
+            <v>Maëlle</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="A39" t="str">
+            <v>Felix</v>
+          </cell>
+          <cell r="B39" t="str">
+            <v>Marius</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="A40" t="str">
+            <v>Ledru</v>
+          </cell>
+          <cell r="B40" t="str">
+            <v>Marot</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="A41" t="str">
+            <v>Cuinet</v>
+          </cell>
+          <cell r="B41" t="str">
+            <v>Mathis</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="A42" t="str">
+            <v>Gavin</v>
+          </cell>
+          <cell r="B42" t="str">
+            <v>Matteo</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="A43" t="str">
+            <v>Debray</v>
+          </cell>
+          <cell r="B43" t="str">
+            <v>Maxime</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="A44" t="str">
+            <v>Corbelli</v>
+          </cell>
+          <cell r="B44" t="str">
+            <v>Maya</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="A45" t="str">
+            <v>Pasche</v>
+          </cell>
+          <cell r="B45" t="str">
+            <v>Mickaël</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="A46" t="str">
+            <v>Fargues</v>
+          </cell>
+          <cell r="B46" t="str">
+            <v>Morgana</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="A47" t="str">
+            <v>Scyboz (Lambelet)</v>
+          </cell>
+          <cell r="B47" t="str">
+            <v>Morgane</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="A48" t="str">
+            <v>Koux</v>
+          </cell>
+          <cell r="B48" t="str">
+            <v>Nathalia</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="A49" t="str">
+            <v>Cherpillod</v>
+          </cell>
+          <cell r="B49" t="str">
+            <v>Noah</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="A50" t="str">
+            <v>Chambaz</v>
+          </cell>
+          <cell r="B50" t="str">
+            <v>Patrick</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="A51" t="str">
+            <v>Assaoui</v>
+          </cell>
+          <cell r="B51" t="str">
+            <v>Rama</v>
+          </cell>
+        </row>
+        <row r="52">
+          <cell r="A52" t="str">
+            <v>Lacroze</v>
+          </cell>
+          <cell r="B52" t="str">
+            <v>Raphaël</v>
+          </cell>
+        </row>
+        <row r="53">
+          <cell r="A53" t="str">
+            <v>Neidhart</v>
+          </cell>
+          <cell r="B53" t="str">
+            <v>Raphaëlle</v>
+          </cell>
+        </row>
+        <row r="54">
+          <cell r="A54" t="str">
+            <v xml:space="preserve">Lanni </v>
+          </cell>
+          <cell r="B54" t="str">
+            <v>Roxanne</v>
+          </cell>
+        </row>
+        <row r="55">
+          <cell r="A55" t="str">
+            <v>Schiesser</v>
+          </cell>
+          <cell r="B55" t="str">
+            <v>Sébastien</v>
+          </cell>
+        </row>
+        <row r="56">
+          <cell r="A56" t="str">
+            <v>Lambelet</v>
+          </cell>
+          <cell r="B56" t="str">
+            <v>Simon</v>
+          </cell>
+        </row>
+        <row r="57">
+          <cell r="A57" t="str">
+            <v>Cyprien</v>
+          </cell>
+          <cell r="B57" t="str">
+            <v>Theo</v>
+          </cell>
+        </row>
+        <row r="58">
+          <cell r="A58" t="str">
+            <v>Clerici</v>
+          </cell>
+          <cell r="B58" t="str">
+            <v>Thibault</v>
+          </cell>
+        </row>
+        <row r="59">
+          <cell r="A59" t="str">
+            <v>Ménétrey</v>
+          </cell>
+          <cell r="B59" t="str">
+            <v>Titouan</v>
+          </cell>
+        </row>
+        <row r="60">
+          <cell r="A60" t="str">
+            <v>Clerici</v>
+          </cell>
+          <cell r="B60" t="str">
+            <v>Tristan</v>
+          </cell>
+        </row>
+        <row r="61">
+          <cell r="A61" t="str">
+            <v>Bally</v>
+          </cell>
+          <cell r="B61" t="str">
+            <v>Yann</v>
+          </cell>
+        </row>
+        <row r="62">
+          <cell r="A62" t="str">
+            <v>Ménétrey</v>
+          </cell>
+          <cell r="B62" t="str">
+            <v>Ysatis</v>
+          </cell>
+        </row>
+        <row r="63">
+          <cell r="A63" t="str">
+            <v>Ménard</v>
+          </cell>
+          <cell r="B63" t="str">
+            <v>Mireille</v>
+          </cell>
+        </row>
+        <row r="64">
+          <cell r="A64" t="str">
+            <v>Rieger</v>
+          </cell>
+          <cell r="B64" t="str">
+            <v>Maya</v>
           </cell>
         </row>
       </sheetData>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1427,517 +1829,118 @@
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="Personnes"/>
-      <sheetName val="LOOKUP"/>
+      <sheetName val="Mardi"/>
+      <sheetName val="Mercredi"/>
+      <sheetName val="Jeudi"/>
+      <sheetName val="Vendredi"/>
+      <sheetName val="Samedi"/>
+      <sheetName val="Dimanche"/>
+      <sheetName val="Tâches"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0">
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6">
+        <row r="1">
+          <cell r="A1" t="str">
+            <v>Tâches</v>
+          </cell>
+        </row>
         <row r="2">
           <cell r="A2" t="str">
-            <v>Bouvet</v>
-          </cell>
-          <cell r="B2" t="str">
-            <v>Agathe</v>
+            <v>Accueil</v>
           </cell>
         </row>
         <row r="3">
           <cell r="A3" t="str">
-            <v>Bulka</v>
-          </cell>
-          <cell r="B3" t="str">
-            <v>Alegria Lily</v>
+            <v>Abeilles Ruche</v>
           </cell>
         </row>
         <row r="4">
           <cell r="A4" t="str">
-            <v>Bastian</v>
-          </cell>
-          <cell r="B4" t="str">
-            <v>Alexandra</v>
+            <v>Ailes</v>
           </cell>
         </row>
         <row r="5">
           <cell r="A5" t="str">
-            <v>L'Horset</v>
-          </cell>
-          <cell r="B5" t="str">
-            <v>Alice</v>
+            <v>Bar loges</v>
           </cell>
         </row>
         <row r="6">
           <cell r="A6" t="str">
-            <v>Ledru</v>
-          </cell>
-          <cell r="B6" t="str">
-            <v>Analou</v>
+            <v>Bar public</v>
           </cell>
         </row>
         <row r="7">
           <cell r="A7" t="str">
-            <v>Mallet</v>
-          </cell>
-          <cell r="B7" t="str">
-            <v>Anna</v>
+            <v>Bourdon.ne</v>
           </cell>
         </row>
         <row r="8">
           <cell r="A8" t="str">
-            <v>Malric</v>
-          </cell>
-          <cell r="B8" t="str">
-            <v>Annouk</v>
+            <v>Entrée backstage</v>
           </cell>
         </row>
         <row r="9">
           <cell r="A9" t="str">
-            <v>Noël</v>
-          </cell>
-          <cell r="B9" t="str">
-            <v>Antonin</v>
+            <v>Horaires</v>
           </cell>
         </row>
         <row r="10">
           <cell r="A10" t="str">
-            <v>Tessier</v>
-          </cell>
-          <cell r="B10" t="str">
-            <v>Arsène</v>
+            <v>Déambule Gerry</v>
           </cell>
         </row>
         <row r="11">
           <cell r="A11" t="str">
-            <v>Uldry</v>
-          </cell>
-          <cell r="B11" t="str">
-            <v>Arthur</v>
+            <v>Déambule Colbok</v>
           </cell>
         </row>
         <row r="12">
           <cell r="A12" t="str">
-            <v>Marchand</v>
-          </cell>
-          <cell r="B12" t="str">
-            <v>Athénaé</v>
+            <v>Déambule Goulus</v>
           </cell>
         </row>
         <row r="13">
           <cell r="A13" t="str">
-            <v>Magerand</v>
-          </cell>
-          <cell r="B13" t="str">
-            <v>Auxence</v>
+            <v>Déambule Volkanik</v>
           </cell>
         </row>
         <row r="14">
           <cell r="A14" t="str">
-            <v>Baruch</v>
-          </cell>
-          <cell r="B14" t="str">
-            <v>Ava</v>
+            <v>Déambule Spoutnik</v>
           </cell>
         </row>
         <row r="15">
           <cell r="A15" t="str">
-            <v>Detrain</v>
-          </cell>
-          <cell r="B15" t="str">
-            <v>Benoît</v>
+            <v>Déambule FBI</v>
           </cell>
         </row>
         <row r="16">
           <cell r="A16" t="str">
-            <v>Meige</v>
-          </cell>
-          <cell r="B16" t="str">
-            <v>Corentin</v>
+            <v>Tech PCGB</v>
           </cell>
         </row>
         <row r="17">
           <cell r="A17" t="str">
-            <v>De Filippo</v>
-          </cell>
-          <cell r="B17" t="str">
-            <v>Emma</v>
+            <v>Tech Jacquard</v>
           </cell>
         </row>
         <row r="18">
           <cell r="A18" t="str">
-            <v>Maître</v>
-          </cell>
-          <cell r="B18" t="str">
-            <v>Enzo</v>
+            <v>Tech Phusis</v>
           </cell>
         </row>
         <row r="19">
           <cell r="A19" t="str">
-            <v>Prouvost</v>
-          </cell>
-          <cell r="B19" t="str">
-            <v>Eugénie</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="A20" t="str">
-            <v xml:space="preserve">Rakotonandrasana </v>
-          </cell>
-          <cell r="B20" t="str">
-            <v>Iris</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="A21" t="str">
-            <v>Bürgisser</v>
-          </cell>
-          <cell r="B21" t="str">
-            <v>Jamilah</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="A22" t="str">
-            <v>Ruscio</v>
-          </cell>
-          <cell r="B22" t="str">
-            <v>Jolan</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="A23" t="str">
-            <v>Wuilloud</v>
-          </cell>
-          <cell r="B23" t="str">
-            <v xml:space="preserve">Jonas </v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="A24" t="str">
-            <v>Pirolley</v>
-          </cell>
-          <cell r="B24" t="str">
-            <v>Jules</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="A25" t="str">
-            <v>Chavaillaz</v>
-          </cell>
-          <cell r="B25" t="str">
-            <v>Julie</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="A26" t="str">
-            <v>Oeschger</v>
-          </cell>
-          <cell r="B26" t="str">
-            <v>Kristel</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="A27" t="str">
-            <v>Baltzinger</v>
-          </cell>
-          <cell r="B27" t="str">
-            <v>Léa</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="A28" t="str">
-            <v>Chambaz</v>
-          </cell>
-          <cell r="B28" t="str">
-            <v>Léa</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="A29" t="str">
-            <v>Ledru</v>
-          </cell>
-          <cell r="B29" t="str">
-            <v>Lina-Rosa</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="A30" t="str">
-            <v>Jaquet</v>
-          </cell>
-          <cell r="B30" t="str">
-            <v>Lisa</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="A31" t="str">
-            <v>Magnin</v>
-          </cell>
-          <cell r="B31" t="str">
-            <v>Lisa</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="A32" t="str">
-            <v>Cardis</v>
-          </cell>
-          <cell r="B32" t="str">
-            <v>Louis</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="A33" t="str">
-            <v>Post</v>
-          </cell>
-          <cell r="B33" t="str">
-            <v>Louis</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="A34" t="str">
-            <v>Blanchard</v>
-          </cell>
-          <cell r="B34" t="str">
-            <v>Louise</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="A35" t="str">
-            <v>Chastroux</v>
-          </cell>
-          <cell r="B35" t="str">
-            <v>Lucas</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="A36" t="str">
-            <v>Meyer</v>
-          </cell>
-          <cell r="B36" t="str">
-            <v>Lucie</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="A37" t="str">
-            <v>Ménétrey</v>
-          </cell>
-          <cell r="B37" t="str">
-            <v>Maëlan</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="A38" t="str">
-            <v>Chambaz</v>
-          </cell>
-          <cell r="B38" t="str">
-            <v>Maëlle</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="A39" t="str">
-            <v>Felix</v>
-          </cell>
-          <cell r="B39" t="str">
-            <v>Marius</v>
-          </cell>
-        </row>
-        <row r="40">
-          <cell r="A40" t="str">
-            <v>Ledru</v>
-          </cell>
-          <cell r="B40" t="str">
-            <v>Marot</v>
-          </cell>
-        </row>
-        <row r="41">
-          <cell r="A41" t="str">
-            <v>Cuinet</v>
-          </cell>
-          <cell r="B41" t="str">
-            <v>Mathis</v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="A42" t="str">
-            <v>Gavin</v>
-          </cell>
-          <cell r="B42" t="str">
-            <v>Matteo</v>
-          </cell>
-        </row>
-        <row r="43">
-          <cell r="A43" t="str">
-            <v>Debray</v>
-          </cell>
-          <cell r="B43" t="str">
-            <v>Maxime</v>
-          </cell>
-        </row>
-        <row r="44">
-          <cell r="A44" t="str">
-            <v>Corbelli</v>
-          </cell>
-          <cell r="B44" t="str">
-            <v>Maya</v>
-          </cell>
-        </row>
-        <row r="45">
-          <cell r="A45" t="str">
-            <v>Pasche</v>
-          </cell>
-          <cell r="B45" t="str">
-            <v>Mickaël</v>
-          </cell>
-        </row>
-        <row r="46">
-          <cell r="A46" t="str">
-            <v>Fargues</v>
-          </cell>
-          <cell r="B46" t="str">
-            <v>Morgana</v>
-          </cell>
-        </row>
-        <row r="47">
-          <cell r="A47" t="str">
-            <v>Scyboz (Lambelet)</v>
-          </cell>
-          <cell r="B47" t="str">
-            <v>Morgane</v>
-          </cell>
-        </row>
-        <row r="48">
-          <cell r="A48" t="str">
-            <v>Koux</v>
-          </cell>
-          <cell r="B48" t="str">
-            <v>Nathalia</v>
-          </cell>
-        </row>
-        <row r="49">
-          <cell r="A49" t="str">
-            <v>Cherpillod</v>
-          </cell>
-          <cell r="B49" t="str">
-            <v>Noah</v>
-          </cell>
-        </row>
-        <row r="50">
-          <cell r="A50" t="str">
-            <v>Chambaz</v>
-          </cell>
-          <cell r="B50" t="str">
-            <v>Patrick</v>
-          </cell>
-        </row>
-        <row r="51">
-          <cell r="A51" t="str">
-            <v>Assaoui</v>
-          </cell>
-          <cell r="B51" t="str">
-            <v>Rama</v>
-          </cell>
-        </row>
-        <row r="52">
-          <cell r="A52" t="str">
-            <v>Lacroze</v>
-          </cell>
-          <cell r="B52" t="str">
-            <v>Raphaël</v>
-          </cell>
-        </row>
-        <row r="53">
-          <cell r="A53" t="str">
-            <v>Neidhart</v>
-          </cell>
-          <cell r="B53" t="str">
-            <v>Raphaëlle</v>
-          </cell>
-        </row>
-        <row r="54">
-          <cell r="A54" t="str">
-            <v xml:space="preserve">Lanni </v>
-          </cell>
-          <cell r="B54" t="str">
-            <v>Roxanne</v>
-          </cell>
-        </row>
-        <row r="55">
-          <cell r="A55" t="str">
-            <v>Schiesser</v>
-          </cell>
-          <cell r="B55" t="str">
-            <v>Sébastien</v>
-          </cell>
-        </row>
-        <row r="56">
-          <cell r="A56" t="str">
-            <v>Lambelet</v>
-          </cell>
-          <cell r="B56" t="str">
-            <v>Simon</v>
-          </cell>
-        </row>
-        <row r="57">
-          <cell r="A57" t="str">
-            <v>Cyprien</v>
-          </cell>
-          <cell r="B57" t="str">
-            <v>Theo</v>
-          </cell>
-        </row>
-        <row r="58">
-          <cell r="A58" t="str">
-            <v>Clerici</v>
-          </cell>
-          <cell r="B58" t="str">
-            <v>Thibault</v>
-          </cell>
-        </row>
-        <row r="59">
-          <cell r="A59" t="str">
-            <v>Ménétrey</v>
-          </cell>
-          <cell r="B59" t="str">
-            <v>Titouan</v>
-          </cell>
-        </row>
-        <row r="60">
-          <cell r="A60" t="str">
-            <v>Clerici</v>
-          </cell>
-          <cell r="B60" t="str">
-            <v>Tristan</v>
-          </cell>
-        </row>
-        <row r="61">
-          <cell r="A61" t="str">
-            <v>Bally</v>
-          </cell>
-          <cell r="B61" t="str">
-            <v>Yann</v>
-          </cell>
-        </row>
-        <row r="62">
-          <cell r="A62" t="str">
-            <v>Ménétrey</v>
-          </cell>
-          <cell r="B62" t="str">
-            <v>Ysatis</v>
-          </cell>
-        </row>
-        <row r="63">
-          <cell r="A63" t="str">
-            <v>Ménard</v>
-          </cell>
-          <cell r="B63" t="str">
-            <v>Mireille</v>
-          </cell>
-        </row>
-        <row r="64">
-          <cell r="A64" t="str">
-            <v>Rieger</v>
-          </cell>
-          <cell r="B64" t="str">
-            <v>Maya</v>
+            <v>Tech T'es rien</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2258,401 +2261,401 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A2" t="str">
-        <f>[2]Personnes!A2</f>
+        <f>[1]Personnes!A2</f>
         <v>Bouvet</v>
       </c>
       <c r="B2" t="str">
-        <f>[2]Personnes!B2</f>
+        <f>[1]Personnes!B2</f>
         <v>Agathe</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A3" t="str">
-        <f>[2]Personnes!A3</f>
+        <f>[1]Personnes!A3</f>
         <v>Bulka</v>
       </c>
       <c r="B3" t="str">
-        <f>[2]Personnes!B3</f>
+        <f>[1]Personnes!B3</f>
         <v>Alegria Lily</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A4" t="str">
-        <f>[2]Personnes!A4</f>
+        <f>[1]Personnes!A4</f>
         <v>Bastian</v>
       </c>
       <c r="B4" t="str">
-        <f>[2]Personnes!B4</f>
+        <f>[1]Personnes!B4</f>
         <v>Alexandra</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A5" t="str">
-        <f>[2]Personnes!A5</f>
+        <f>[1]Personnes!A5</f>
         <v>L'Horset</v>
       </c>
       <c r="B5" t="str">
-        <f>[2]Personnes!B5</f>
+        <f>[1]Personnes!B5</f>
         <v>Alice</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A6" t="str">
-        <f>[2]Personnes!A6</f>
+        <f>[1]Personnes!A6</f>
         <v>Ledru</v>
       </c>
       <c r="B6" t="str">
-        <f>[2]Personnes!B6</f>
+        <f>[1]Personnes!B6</f>
         <v>Analou</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A7" t="str">
-        <f>[2]Personnes!A7</f>
+        <f>[1]Personnes!A7</f>
         <v>Mallet</v>
       </c>
       <c r="B7" t="str">
-        <f>[2]Personnes!B7</f>
+        <f>[1]Personnes!B7</f>
         <v>Anna</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A8" t="str">
-        <f>[2]Personnes!A8</f>
+        <f>[1]Personnes!A8</f>
         <v>Malric</v>
       </c>
       <c r="B8" t="str">
-        <f>[2]Personnes!B8</f>
+        <f>[1]Personnes!B8</f>
         <v>Annouk</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A9" t="str">
-        <f>[2]Personnes!A9</f>
+        <f>[1]Personnes!A9</f>
         <v>Noël</v>
       </c>
       <c r="B9" t="str">
-        <f>[2]Personnes!B9</f>
+        <f>[1]Personnes!B9</f>
         <v>Antonin</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A10" t="str">
-        <f>[2]Personnes!A10</f>
+        <f>[1]Personnes!A10</f>
         <v>Tessier</v>
       </c>
       <c r="B10" t="str">
-        <f>[2]Personnes!B10</f>
+        <f>[1]Personnes!B10</f>
         <v>Arsène</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A11" t="str">
-        <f>[2]Personnes!A11</f>
+        <f>[1]Personnes!A11</f>
         <v>Uldry</v>
       </c>
       <c r="B11" t="str">
-        <f>[2]Personnes!B11</f>
+        <f>[1]Personnes!B11</f>
         <v>Arthur</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A12" t="str">
-        <f>[2]Personnes!A12</f>
+        <f>[1]Personnes!A12</f>
         <v>Marchand</v>
       </c>
       <c r="B12" t="str">
-        <f>[2]Personnes!B12</f>
+        <f>[1]Personnes!B12</f>
         <v>Athénaé</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A13" t="str">
-        <f>[2]Personnes!A13</f>
+        <f>[1]Personnes!A13</f>
         <v>Magerand</v>
       </c>
       <c r="B13" t="str">
-        <f>[2]Personnes!B13</f>
+        <f>[1]Personnes!B13</f>
         <v>Auxence</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A14" t="str">
-        <f>[2]Personnes!A14</f>
+        <f>[1]Personnes!A14</f>
         <v>Baruch</v>
       </c>
       <c r="B14" t="str">
-        <f>[2]Personnes!B14</f>
+        <f>[1]Personnes!B14</f>
         <v>Ava</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A15" t="str">
-        <f>[2]Personnes!A15</f>
+        <f>[1]Personnes!A15</f>
         <v>Detrain</v>
       </c>
       <c r="B15" t="str">
-        <f>[2]Personnes!B15</f>
+        <f>[1]Personnes!B15</f>
         <v>Benoît</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A16" t="str">
-        <f>[2]Personnes!A16</f>
+        <f>[1]Personnes!A16</f>
         <v>Meige</v>
       </c>
       <c r="B16" t="str">
-        <f>[2]Personnes!B16</f>
+        <f>[1]Personnes!B16</f>
         <v>Corentin</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17" t="str">
-        <f>[2]Personnes!A17</f>
+        <f>[1]Personnes!A17</f>
         <v>De Filippo</v>
       </c>
       <c r="B17" t="str">
-        <f>[2]Personnes!B17</f>
+        <f>[1]Personnes!B17</f>
         <v>Emma</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18" t="str">
-        <f>[2]Personnes!A18</f>
+        <f>[1]Personnes!A18</f>
         <v>Maître</v>
       </c>
       <c r="B18" t="str">
-        <f>[2]Personnes!B18</f>
+        <f>[1]Personnes!B18</f>
         <v>Enzo</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19" t="str">
-        <f>[2]Personnes!A19</f>
+        <f>[1]Personnes!A19</f>
         <v>Prouvost</v>
       </c>
       <c r="B19" t="str">
-        <f>[2]Personnes!B19</f>
+        <f>[1]Personnes!B19</f>
         <v>Eugénie</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20" t="str">
-        <f>[2]Personnes!A20</f>
+        <f>[1]Personnes!A20</f>
         <v xml:space="preserve">Rakotonandrasana </v>
       </c>
       <c r="B20" t="str">
-        <f>[2]Personnes!B20</f>
+        <f>[1]Personnes!B20</f>
         <v>Iris</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21" t="str">
-        <f>[2]Personnes!A21</f>
+        <f>[1]Personnes!A21</f>
         <v>Bürgisser</v>
       </c>
       <c r="B21" t="str">
-        <f>[2]Personnes!B21</f>
+        <f>[1]Personnes!B21</f>
         <v>Jamilah</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A22" t="str">
-        <f>[2]Personnes!A22</f>
+        <f>[1]Personnes!A22</f>
         <v>Ruscio</v>
       </c>
       <c r="B22" t="str">
-        <f>[2]Personnes!B22</f>
+        <f>[1]Personnes!B22</f>
         <v>Jolan</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A23" t="str">
-        <f>[2]Personnes!A23</f>
+        <f>[1]Personnes!A23</f>
         <v>Wuilloud</v>
       </c>
       <c r="B23" t="str">
-        <f>[2]Personnes!B23</f>
+        <f>[1]Personnes!B23</f>
         <v xml:space="preserve">Jonas </v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A24" t="str">
-        <f>[2]Personnes!A24</f>
+        <f>[1]Personnes!A24</f>
         <v>Pirolley</v>
       </c>
       <c r="B24" t="str">
-        <f>[2]Personnes!B24</f>
+        <f>[1]Personnes!B24</f>
         <v>Jules</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25" t="str">
-        <f>[2]Personnes!A25</f>
+        <f>[1]Personnes!A25</f>
         <v>Chavaillaz</v>
       </c>
       <c r="B25" t="str">
-        <f>[2]Personnes!B25</f>
+        <f>[1]Personnes!B25</f>
         <v>Julie</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A26" t="str">
-        <f>[2]Personnes!A26</f>
+        <f>[1]Personnes!A26</f>
         <v>Oeschger</v>
       </c>
       <c r="B26" t="str">
-        <f>[2]Personnes!B26</f>
+        <f>[1]Personnes!B26</f>
         <v>Kristel</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A27" t="str">
-        <f>[2]Personnes!A27</f>
+        <f>[1]Personnes!A27</f>
         <v>Baltzinger</v>
       </c>
       <c r="B27" t="str">
-        <f>[2]Personnes!B27</f>
+        <f>[1]Personnes!B27</f>
         <v>Léa</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A28" t="str">
-        <f>[2]Personnes!A28</f>
+        <f>[1]Personnes!A28</f>
         <v>Chambaz</v>
       </c>
       <c r="B28" t="str">
-        <f>[2]Personnes!B28</f>
+        <f>[1]Personnes!B28</f>
         <v>Léa</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A29" t="str">
-        <f>[2]Personnes!A29</f>
+        <f>[1]Personnes!A29</f>
         <v>Ledru</v>
       </c>
       <c r="B29" t="str">
-        <f>[2]Personnes!B29</f>
+        <f>[1]Personnes!B29</f>
         <v>Lina-Rosa</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A30" t="str">
-        <f>[2]Personnes!A30</f>
+        <f>[1]Personnes!A30</f>
         <v>Jaquet</v>
       </c>
       <c r="B30" t="str">
-        <f>[2]Personnes!B30</f>
+        <f>[1]Personnes!B30</f>
         <v>Lisa</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A31" t="str">
-        <f>[2]Personnes!A31</f>
+        <f>[1]Personnes!A31</f>
         <v>Magnin</v>
       </c>
       <c r="B31" t="str">
-        <f>[2]Personnes!B31</f>
+        <f>[1]Personnes!B31</f>
         <v>Lisa</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A32" t="str">
-        <f>[2]Personnes!A32</f>
+        <f>[1]Personnes!A32</f>
         <v>Cardis</v>
       </c>
       <c r="B32" t="str">
-        <f>[2]Personnes!B32</f>
+        <f>[1]Personnes!B32</f>
         <v>Louis</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A33" t="str">
-        <f>[2]Personnes!A33</f>
+        <f>[1]Personnes!A33</f>
         <v>Post</v>
       </c>
       <c r="B33" t="str">
-        <f>[2]Personnes!B33</f>
+        <f>[1]Personnes!B33</f>
         <v>Louis</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A34" t="str">
-        <f>[2]Personnes!A34</f>
+        <f>[1]Personnes!A34</f>
         <v>Blanchard</v>
       </c>
       <c r="B34" t="str">
-        <f>[2]Personnes!B34</f>
+        <f>[1]Personnes!B34</f>
         <v>Louise</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A35" t="str">
-        <f>[2]Personnes!A35</f>
+        <f>[1]Personnes!A35</f>
         <v>Chastroux</v>
       </c>
       <c r="B35" t="str">
-        <f>[2]Personnes!B35</f>
+        <f>[1]Personnes!B35</f>
         <v>Lucas</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A36" t="str">
-        <f>[2]Personnes!A36</f>
+        <f>[1]Personnes!A36</f>
         <v>Meyer</v>
       </c>
       <c r="B36" t="str">
-        <f>[2]Personnes!B36</f>
+        <f>[1]Personnes!B36</f>
         <v>Lucie</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A37" t="str">
-        <f>[2]Personnes!A37</f>
+        <f>[1]Personnes!A37</f>
         <v>Ménétrey</v>
       </c>
       <c r="B37" t="str">
-        <f>[2]Personnes!B37</f>
+        <f>[1]Personnes!B37</f>
         <v>Maëlan</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A38" t="str">
-        <f>[2]Personnes!A38</f>
+        <f>[1]Personnes!A38</f>
         <v>Chambaz</v>
       </c>
       <c r="B38" t="str">
-        <f>[2]Personnes!B38</f>
+        <f>[1]Personnes!B38</f>
         <v>Maëlle</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A39" t="str">
-        <f>[2]Personnes!A39</f>
+        <f>[1]Personnes!A39</f>
         <v>Felix</v>
       </c>
       <c r="B39" t="str">
-        <f>[2]Personnes!B39</f>
+        <f>[1]Personnes!B39</f>
         <v>Marius</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A40" t="str">
-        <f>[2]Personnes!A40</f>
+        <f>[1]Personnes!A40</f>
         <v>Ledru</v>
       </c>
       <c r="B40" t="str">
-        <f>[2]Personnes!B40</f>
+        <f>[1]Personnes!B40</f>
         <v>Marot</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A41" t="str">
-        <f>[2]Personnes!A41</f>
+        <f>[1]Personnes!A41</f>
         <v>Cuinet</v>
       </c>
       <c r="B41" t="str">
-        <f>[2]Personnes!B41</f>
+        <f>[1]Personnes!B41</f>
         <v>Mathis</v>
       </c>
       <c r="C41" t="s">
@@ -2667,120 +2670,120 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A42" t="str">
-        <f>[2]Personnes!A42</f>
+        <f>[1]Personnes!A42</f>
         <v>Gavin</v>
       </c>
       <c r="B42" t="str">
-        <f>[2]Personnes!B42</f>
+        <f>[1]Personnes!B42</f>
         <v>Matteo</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A43" t="str">
-        <f>[2]Personnes!A43</f>
+        <f>[1]Personnes!A43</f>
         <v>Debray</v>
       </c>
       <c r="B43" t="str">
-        <f>[2]Personnes!B43</f>
+        <f>[1]Personnes!B43</f>
         <v>Maxime</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A44" t="str">
-        <f>[2]Personnes!A44</f>
+        <f>[1]Personnes!A44</f>
         <v>Corbelli</v>
       </c>
       <c r="B44" t="str">
-        <f>[2]Personnes!B44</f>
+        <f>[1]Personnes!B44</f>
         <v>Maya</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A45" t="str">
-        <f>[2]Personnes!A45</f>
+        <f>[1]Personnes!A45</f>
         <v>Pasche</v>
       </c>
       <c r="B45" t="str">
-        <f>[2]Personnes!B45</f>
+        <f>[1]Personnes!B45</f>
         <v>Mickaël</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A46" t="str">
-        <f>[2]Personnes!A46</f>
+        <f>[1]Personnes!A46</f>
         <v>Fargues</v>
       </c>
       <c r="B46" t="str">
-        <f>[2]Personnes!B46</f>
+        <f>[1]Personnes!B46</f>
         <v>Morgana</v>
       </c>
       <c r="C46" t="s">
         <v>5</v>
       </c>
       <c r="D46" s="2">
-        <v>0.66666666666666663</v>
+        <v>0.8125</v>
       </c>
       <c r="E46" s="2">
-        <v>0.75</v>
+        <v>0.85416666666666663</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A47" t="str">
-        <f>[2]Personnes!A47</f>
+        <f>[1]Personnes!A47</f>
         <v>Scyboz (Lambelet)</v>
       </c>
       <c r="B47" t="str">
-        <f>[2]Personnes!B47</f>
+        <f>[1]Personnes!B47</f>
         <v>Morgane</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A48" t="str">
-        <f>[2]Personnes!A48</f>
+        <f>[1]Personnes!A48</f>
         <v>Koux</v>
       </c>
       <c r="B48" t="str">
-        <f>[2]Personnes!B48</f>
+        <f>[1]Personnes!B48</f>
         <v>Nathalia</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A49" t="str">
-        <f>[2]Personnes!A49</f>
+        <f>[1]Personnes!A49</f>
         <v>Cherpillod</v>
       </c>
       <c r="B49" t="str">
-        <f>[2]Personnes!B49</f>
+        <f>[1]Personnes!B49</f>
         <v>Noah</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A50" t="str">
-        <f>[2]Personnes!A50</f>
+        <f>[1]Personnes!A50</f>
         <v>Chambaz</v>
       </c>
       <c r="B50" t="str">
-        <f>[2]Personnes!B50</f>
+        <f>[1]Personnes!B50</f>
         <v>Patrick</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A51" t="str">
-        <f>[2]Personnes!A51</f>
+        <f>[1]Personnes!A51</f>
         <v>Assaoui</v>
       </c>
       <c r="B51" t="str">
-        <f>[2]Personnes!B51</f>
+        <f>[1]Personnes!B51</f>
         <v>Rama</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A52" t="str">
-        <f>[2]Personnes!A52</f>
+        <f>[1]Personnes!A52</f>
         <v>Lacroze</v>
       </c>
       <c r="B52" t="str">
-        <f>[2]Personnes!B52</f>
+        <f>[1]Personnes!B52</f>
         <v>Raphaël</v>
       </c>
       <c r="C52" t="s">
@@ -2790,135 +2793,135 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="E52" s="2">
-        <v>0.79166666666666663</v>
+        <v>0.77083333333333337</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A53" t="str">
-        <f>[2]Personnes!A53</f>
+        <f>[1]Personnes!A53</f>
         <v>Neidhart</v>
       </c>
       <c r="B53" t="str">
-        <f>[2]Personnes!B53</f>
+        <f>[1]Personnes!B53</f>
         <v>Raphaëlle</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A54" t="str">
-        <f>[2]Personnes!A54</f>
+        <f>[1]Personnes!A54</f>
         <v xml:space="preserve">Lanni </v>
       </c>
       <c r="B54" t="str">
-        <f>[2]Personnes!B54</f>
+        <f>[1]Personnes!B54</f>
         <v>Roxanne</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A55" t="str">
-        <f>[2]Personnes!A55</f>
+        <f>[1]Personnes!A55</f>
         <v>Schiesser</v>
       </c>
       <c r="B55" t="str">
-        <f>[2]Personnes!B55</f>
+        <f>[1]Personnes!B55</f>
         <v>Sébastien</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A56" t="str">
-        <f>[2]Personnes!A56</f>
+        <f>[1]Personnes!A56</f>
         <v>Lambelet</v>
       </c>
       <c r="B56" t="str">
-        <f>[2]Personnes!B56</f>
+        <f>[1]Personnes!B56</f>
         <v>Simon</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A57" t="str">
-        <f>[2]Personnes!A57</f>
+        <f>[1]Personnes!A57</f>
         <v>Cyprien</v>
       </c>
       <c r="B57" t="str">
-        <f>[2]Personnes!B57</f>
+        <f>[1]Personnes!B57</f>
         <v>Theo</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A58" t="str">
-        <f>[2]Personnes!A58</f>
+        <f>[1]Personnes!A58</f>
         <v>Clerici</v>
       </c>
       <c r="B58" t="str">
-        <f>[2]Personnes!B58</f>
+        <f>[1]Personnes!B58</f>
         <v>Thibault</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A59" t="str">
-        <f>[2]Personnes!A59</f>
+        <f>[1]Personnes!A59</f>
         <v>Ménétrey</v>
       </c>
       <c r="B59" t="str">
-        <f>[2]Personnes!B59</f>
+        <f>[1]Personnes!B59</f>
         <v>Titouan</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A60" t="str">
-        <f>[2]Personnes!A60</f>
+        <f>[1]Personnes!A60</f>
         <v>Clerici</v>
       </c>
       <c r="B60" t="str">
-        <f>[2]Personnes!B60</f>
+        <f>[1]Personnes!B60</f>
         <v>Tristan</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A61" t="str">
-        <f>[2]Personnes!A61</f>
+        <f>[1]Personnes!A61</f>
         <v>Bally</v>
       </c>
       <c r="B61" t="str">
-        <f>[2]Personnes!B61</f>
+        <f>[1]Personnes!B61</f>
         <v>Yann</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A62" t="str">
-        <f>[2]Personnes!A62</f>
+        <f>[1]Personnes!A62</f>
         <v>Ménétrey</v>
       </c>
       <c r="B62" t="str">
-        <f>[2]Personnes!B62</f>
+        <f>[1]Personnes!B62</f>
         <v>Ysatis</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A63" t="str">
-        <f>[2]Personnes!A63</f>
+        <f>[1]Personnes!A63</f>
         <v>Ménard</v>
       </c>
       <c r="B63" t="str">
-        <f>[2]Personnes!B63</f>
+        <f>[1]Personnes!B63</f>
         <v>Mireille</v>
       </c>
       <c r="C63" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D63" s="2">
-        <v>0.79166666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="E63" s="2">
-        <v>0.875</v>
+        <v>0.8125</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A64" t="str">
-        <f>[2]Personnes!A64</f>
+        <f>[1]Personnes!A64</f>
         <v>Rieger</v>
       </c>
       <c r="B64" t="str">
-        <f>[2]Personnes!B64</f>
+        <f>[1]Personnes!B64</f>
         <v>Maya</v>
       </c>
     </row>
@@ -2980,381 +2983,381 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A2" t="str">
-        <f>[2]Personnes!A2</f>
+        <f>[1]Personnes!A2</f>
         <v>Bouvet</v>
       </c>
       <c r="B2" t="str">
-        <f>[2]Personnes!B2</f>
+        <f>[1]Personnes!B2</f>
         <v>Agathe</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A3" t="str">
-        <f>[2]Personnes!A3</f>
+        <f>[1]Personnes!A3</f>
         <v>Bulka</v>
       </c>
       <c r="B3" t="str">
-        <f>[2]Personnes!B3</f>
+        <f>[1]Personnes!B3</f>
         <v>Alegria Lily</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A4" t="str">
-        <f>[2]Personnes!A4</f>
+        <f>[1]Personnes!A4</f>
         <v>Bastian</v>
       </c>
       <c r="B4" t="str">
-        <f>[2]Personnes!B4</f>
+        <f>[1]Personnes!B4</f>
         <v>Alexandra</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A5" t="str">
-        <f>[2]Personnes!A5</f>
+        <f>[1]Personnes!A5</f>
         <v>L'Horset</v>
       </c>
       <c r="B5" t="str">
-        <f>[2]Personnes!B5</f>
+        <f>[1]Personnes!B5</f>
         <v>Alice</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A6" t="str">
-        <f>[2]Personnes!A6</f>
+        <f>[1]Personnes!A6</f>
         <v>Ledru</v>
       </c>
       <c r="B6" t="str">
-        <f>[2]Personnes!B6</f>
+        <f>[1]Personnes!B6</f>
         <v>Analou</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A7" t="str">
-        <f>[2]Personnes!A7</f>
+        <f>[1]Personnes!A7</f>
         <v>Mallet</v>
       </c>
       <c r="B7" t="str">
-        <f>[2]Personnes!B7</f>
+        <f>[1]Personnes!B7</f>
         <v>Anna</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A8" t="str">
-        <f>[2]Personnes!A8</f>
+        <f>[1]Personnes!A8</f>
         <v>Malric</v>
       </c>
       <c r="B8" t="str">
-        <f>[2]Personnes!B8</f>
+        <f>[1]Personnes!B8</f>
         <v>Annouk</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A9" t="str">
-        <f>[2]Personnes!A9</f>
+        <f>[1]Personnes!A9</f>
         <v>Noël</v>
       </c>
       <c r="B9" t="str">
-        <f>[2]Personnes!B9</f>
+        <f>[1]Personnes!B9</f>
         <v>Antonin</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A10" t="str">
-        <f>[2]Personnes!A10</f>
+        <f>[1]Personnes!A10</f>
         <v>Tessier</v>
       </c>
       <c r="B10" t="str">
-        <f>[2]Personnes!B10</f>
+        <f>[1]Personnes!B10</f>
         <v>Arsène</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A11" t="str">
-        <f>[2]Personnes!A11</f>
+        <f>[1]Personnes!A11</f>
         <v>Uldry</v>
       </c>
       <c r="B11" t="str">
-        <f>[2]Personnes!B11</f>
+        <f>[1]Personnes!B11</f>
         <v>Arthur</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A12" t="str">
-        <f>[2]Personnes!A12</f>
+        <f>[1]Personnes!A12</f>
         <v>Marchand</v>
       </c>
       <c r="B12" t="str">
-        <f>[2]Personnes!B12</f>
+        <f>[1]Personnes!B12</f>
         <v>Athénaé</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A13" t="str">
-        <f>[2]Personnes!A13</f>
+        <f>[1]Personnes!A13</f>
         <v>Magerand</v>
       </c>
       <c r="B13" t="str">
-        <f>[2]Personnes!B13</f>
+        <f>[1]Personnes!B13</f>
         <v>Auxence</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A14" t="str">
-        <f>[2]Personnes!A14</f>
+        <f>[1]Personnes!A14</f>
         <v>Baruch</v>
       </c>
       <c r="B14" t="str">
-        <f>[2]Personnes!B14</f>
+        <f>[1]Personnes!B14</f>
         <v>Ava</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A15" t="str">
-        <f>[2]Personnes!A15</f>
+        <f>[1]Personnes!A15</f>
         <v>Detrain</v>
       </c>
       <c r="B15" t="str">
-        <f>[2]Personnes!B15</f>
+        <f>[1]Personnes!B15</f>
         <v>Benoît</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A16" t="str">
-        <f>[2]Personnes!A16</f>
+        <f>[1]Personnes!A16</f>
         <v>Meige</v>
       </c>
       <c r="B16" t="str">
-        <f>[2]Personnes!B16</f>
+        <f>[1]Personnes!B16</f>
         <v>Corentin</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17" t="str">
-        <f>[2]Personnes!A17</f>
+        <f>[1]Personnes!A17</f>
         <v>De Filippo</v>
       </c>
       <c r="B17" t="str">
-        <f>[2]Personnes!B17</f>
+        <f>[1]Personnes!B17</f>
         <v>Emma</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18" t="str">
-        <f>[2]Personnes!A18</f>
+        <f>[1]Personnes!A18</f>
         <v>Maître</v>
       </c>
       <c r="B18" t="str">
-        <f>[2]Personnes!B18</f>
+        <f>[1]Personnes!B18</f>
         <v>Enzo</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19" t="str">
-        <f>[2]Personnes!A19</f>
+        <f>[1]Personnes!A19</f>
         <v>Prouvost</v>
       </c>
       <c r="B19" t="str">
-        <f>[2]Personnes!B19</f>
+        <f>[1]Personnes!B19</f>
         <v>Eugénie</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20" t="str">
-        <f>[2]Personnes!A20</f>
+        <f>[1]Personnes!A20</f>
         <v xml:space="preserve">Rakotonandrasana </v>
       </c>
       <c r="B20" t="str">
-        <f>[2]Personnes!B20</f>
+        <f>[1]Personnes!B20</f>
         <v>Iris</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21" t="str">
-        <f>[2]Personnes!A21</f>
+        <f>[1]Personnes!A21</f>
         <v>Bürgisser</v>
       </c>
       <c r="B21" t="str">
-        <f>[2]Personnes!B21</f>
+        <f>[1]Personnes!B21</f>
         <v>Jamilah</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A22" t="str">
-        <f>[2]Personnes!A22</f>
+        <f>[1]Personnes!A22</f>
         <v>Ruscio</v>
       </c>
       <c r="B22" t="str">
-        <f>[2]Personnes!B22</f>
+        <f>[1]Personnes!B22</f>
         <v>Jolan</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A23" t="str">
-        <f>[2]Personnes!A23</f>
+        <f>[1]Personnes!A23</f>
         <v>Wuilloud</v>
       </c>
       <c r="B23" t="str">
-        <f>[2]Personnes!B23</f>
+        <f>[1]Personnes!B23</f>
         <v xml:space="preserve">Jonas </v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A24" t="str">
-        <f>[2]Personnes!A24</f>
+        <f>[1]Personnes!A24</f>
         <v>Pirolley</v>
       </c>
       <c r="B24" t="str">
-        <f>[2]Personnes!B24</f>
+        <f>[1]Personnes!B24</f>
         <v>Jules</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25" t="str">
-        <f>[2]Personnes!A25</f>
+        <f>[1]Personnes!A25</f>
         <v>Chavaillaz</v>
       </c>
       <c r="B25" t="str">
-        <f>[2]Personnes!B25</f>
+        <f>[1]Personnes!B25</f>
         <v>Julie</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A26" t="str">
-        <f>[2]Personnes!A26</f>
+        <f>[1]Personnes!A26</f>
         <v>Oeschger</v>
       </c>
       <c r="B26" t="str">
-        <f>[2]Personnes!B26</f>
+        <f>[1]Personnes!B26</f>
         <v>Kristel</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A27" t="str">
-        <f>[2]Personnes!A27</f>
+        <f>[1]Personnes!A27</f>
         <v>Baltzinger</v>
       </c>
       <c r="B27" t="str">
-        <f>[2]Personnes!B27</f>
+        <f>[1]Personnes!B27</f>
         <v>Léa</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A28" t="str">
-        <f>[2]Personnes!A28</f>
+        <f>[1]Personnes!A28</f>
         <v>Chambaz</v>
       </c>
       <c r="B28" t="str">
-        <f>[2]Personnes!B28</f>
+        <f>[1]Personnes!B28</f>
         <v>Léa</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A29" t="str">
-        <f>[2]Personnes!A29</f>
+        <f>[1]Personnes!A29</f>
         <v>Ledru</v>
       </c>
       <c r="B29" t="str">
-        <f>[2]Personnes!B29</f>
+        <f>[1]Personnes!B29</f>
         <v>Lina-Rosa</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A30" t="str">
-        <f>[2]Personnes!A30</f>
+        <f>[1]Personnes!A30</f>
         <v>Jaquet</v>
       </c>
       <c r="B30" t="str">
-        <f>[2]Personnes!B30</f>
+        <f>[1]Personnes!B30</f>
         <v>Lisa</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A31" t="str">
-        <f>[2]Personnes!A31</f>
+        <f>[1]Personnes!A31</f>
         <v>Magnin</v>
       </c>
       <c r="B31" t="str">
-        <f>[2]Personnes!B31</f>
+        <f>[1]Personnes!B31</f>
         <v>Lisa</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A32" t="str">
-        <f>[2]Personnes!A32</f>
+        <f>[1]Personnes!A32</f>
         <v>Cardis</v>
       </c>
       <c r="B32" t="str">
-        <f>[2]Personnes!B32</f>
+        <f>[1]Personnes!B32</f>
         <v>Louis</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A33" t="str">
-        <f>[2]Personnes!A33</f>
+        <f>[1]Personnes!A33</f>
         <v>Post</v>
       </c>
       <c r="B33" t="str">
-        <f>[2]Personnes!B33</f>
+        <f>[1]Personnes!B33</f>
         <v>Louis</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A34" t="str">
-        <f>[2]Personnes!A34</f>
+        <f>[1]Personnes!A34</f>
         <v>Blanchard</v>
       </c>
       <c r="B34" t="str">
-        <f>[2]Personnes!B34</f>
+        <f>[1]Personnes!B34</f>
         <v>Louise</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A35" t="str">
-        <f>[2]Personnes!A35</f>
+        <f>[1]Personnes!A35</f>
         <v>Chastroux</v>
       </c>
       <c r="B35" t="str">
-        <f>[2]Personnes!B35</f>
+        <f>[1]Personnes!B35</f>
         <v>Lucas</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A36" t="str">
-        <f>[2]Personnes!A36</f>
+        <f>[1]Personnes!A36</f>
         <v>Meyer</v>
       </c>
       <c r="B36" t="str">
-        <f>[2]Personnes!B36</f>
+        <f>[1]Personnes!B36</f>
         <v>Lucie</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A37" t="str">
-        <f>[2]Personnes!A37</f>
+        <f>[1]Personnes!A37</f>
         <v>Ménétrey</v>
       </c>
       <c r="B37" t="str">
-        <f>[2]Personnes!B37</f>
+        <f>[1]Personnes!B37</f>
         <v>Maëlan</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A38" t="str">
-        <f>[2]Personnes!A38</f>
+        <f>[1]Personnes!A38</f>
         <v>Chambaz</v>
       </c>
       <c r="B38" t="str">
-        <f>[2]Personnes!B38</f>
+        <f>[1]Personnes!B38</f>
         <v>Maëlle</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A39" t="str">
-        <f>[2]Personnes!A39</f>
+        <f>[1]Personnes!A39</f>
         <v>Felix</v>
       </c>
       <c r="B39" t="str">
-        <f>[2]Personnes!B39</f>
+        <f>[1]Personnes!B39</f>
         <v>Marius</v>
       </c>
       <c r="C39" t="s">
@@ -3369,41 +3372,41 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A40" t="str">
-        <f>[2]Personnes!A40</f>
+        <f>[1]Personnes!A40</f>
         <v>Ledru</v>
       </c>
       <c r="B40" t="str">
-        <f>[2]Personnes!B40</f>
+        <f>[1]Personnes!B40</f>
         <v>Marot</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A41" t="str">
-        <f>[2]Personnes!A41</f>
+        <f>[1]Personnes!A41</f>
         <v>Cuinet</v>
       </c>
       <c r="B41" t="str">
-        <f>[2]Personnes!B41</f>
+        <f>[1]Personnes!B41</f>
         <v>Mathis</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A42" t="str">
-        <f>[2]Personnes!A42</f>
+        <f>[1]Personnes!A42</f>
         <v>Gavin</v>
       </c>
       <c r="B42" t="str">
-        <f>[2]Personnes!B42</f>
+        <f>[1]Personnes!B42</f>
         <v>Matteo</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A43" t="str">
-        <f>[2]Personnes!A43</f>
+        <f>[1]Personnes!A43</f>
         <v>Debray</v>
       </c>
       <c r="B43" t="str">
-        <f>[2]Personnes!B43</f>
+        <f>[1]Personnes!B43</f>
         <v>Maxime</v>
       </c>
       <c r="C43" t="s">
@@ -3418,91 +3421,91 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A44" t="str">
-        <f>[2]Personnes!A44</f>
+        <f>[1]Personnes!A44</f>
         <v>Corbelli</v>
       </c>
       <c r="B44" t="str">
-        <f>[2]Personnes!B44</f>
+        <f>[1]Personnes!B44</f>
         <v>Maya</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A45" t="str">
-        <f>[2]Personnes!A45</f>
+        <f>[1]Personnes!A45</f>
         <v>Pasche</v>
       </c>
       <c r="B45" t="str">
-        <f>[2]Personnes!B45</f>
+        <f>[1]Personnes!B45</f>
         <v>Mickaël</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A46" t="str">
-        <f>[2]Personnes!A46</f>
+        <f>[1]Personnes!A46</f>
         <v>Fargues</v>
       </c>
       <c r="B46" t="str">
-        <f>[2]Personnes!B46</f>
+        <f>[1]Personnes!B46</f>
         <v>Morgana</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A47" t="str">
-        <f>[2]Personnes!A47</f>
+        <f>[1]Personnes!A47</f>
         <v>Scyboz (Lambelet)</v>
       </c>
       <c r="B47" t="str">
-        <f>[2]Personnes!B47</f>
+        <f>[1]Personnes!B47</f>
         <v>Morgane</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A48" t="str">
-        <f>[2]Personnes!A48</f>
+        <f>[1]Personnes!A48</f>
         <v>Koux</v>
       </c>
       <c r="B48" t="str">
-        <f>[2]Personnes!B48</f>
+        <f>[1]Personnes!B48</f>
         <v>Nathalia</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A49" t="str">
-        <f>[2]Personnes!A49</f>
+        <f>[1]Personnes!A49</f>
         <v>Cherpillod</v>
       </c>
       <c r="B49" t="str">
-        <f>[2]Personnes!B49</f>
+        <f>[1]Personnes!B49</f>
         <v>Noah</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A50" t="str">
-        <f>[2]Personnes!A50</f>
+        <f>[1]Personnes!A50</f>
         <v>Chambaz</v>
       </c>
       <c r="B50" t="str">
-        <f>[2]Personnes!B50</f>
+        <f>[1]Personnes!B50</f>
         <v>Patrick</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A51" t="str">
-        <f>[2]Personnes!A51</f>
+        <f>[1]Personnes!A51</f>
         <v>Assaoui</v>
       </c>
       <c r="B51" t="str">
-        <f>[2]Personnes!B51</f>
+        <f>[1]Personnes!B51</f>
         <v>Rama</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A52" t="str">
-        <f>[2]Personnes!A52</f>
+        <f>[1]Personnes!A52</f>
         <v>Lacroze</v>
       </c>
       <c r="B52" t="str">
-        <f>[2]Personnes!B52</f>
+        <f>[1]Personnes!B52</f>
         <v>Raphaël</v>
       </c>
       <c r="C52" t="s">
@@ -3517,127 +3520,127 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A53" t="str">
-        <f>[2]Personnes!A53</f>
+        <f>[1]Personnes!A53</f>
         <v>Neidhart</v>
       </c>
       <c r="B53" t="str">
-        <f>[2]Personnes!B53</f>
+        <f>[1]Personnes!B53</f>
         <v>Raphaëlle</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A54" t="str">
-        <f>[2]Personnes!A54</f>
+        <f>[1]Personnes!A54</f>
         <v xml:space="preserve">Lanni </v>
       </c>
       <c r="B54" t="str">
-        <f>[2]Personnes!B54</f>
+        <f>[1]Personnes!B54</f>
         <v>Roxanne</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A55" t="str">
-        <f>[2]Personnes!A55</f>
+        <f>[1]Personnes!A55</f>
         <v>Schiesser</v>
       </c>
       <c r="B55" t="str">
-        <f>[2]Personnes!B55</f>
+        <f>[1]Personnes!B55</f>
         <v>Sébastien</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A56" t="str">
-        <f>[2]Personnes!A56</f>
+        <f>[1]Personnes!A56</f>
         <v>Lambelet</v>
       </c>
       <c r="B56" t="str">
-        <f>[2]Personnes!B56</f>
+        <f>[1]Personnes!B56</f>
         <v>Simon</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A57" t="str">
-        <f>[2]Personnes!A57</f>
+        <f>[1]Personnes!A57</f>
         <v>Cyprien</v>
       </c>
       <c r="B57" t="str">
-        <f>[2]Personnes!B57</f>
+        <f>[1]Personnes!B57</f>
         <v>Theo</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A58" t="str">
-        <f>[2]Personnes!A58</f>
+        <f>[1]Personnes!A58</f>
         <v>Clerici</v>
       </c>
       <c r="B58" t="str">
-        <f>[2]Personnes!B58</f>
+        <f>[1]Personnes!B58</f>
         <v>Thibault</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A59" t="str">
-        <f>[2]Personnes!A59</f>
+        <f>[1]Personnes!A59</f>
         <v>Ménétrey</v>
       </c>
       <c r="B59" t="str">
-        <f>[2]Personnes!B59</f>
+        <f>[1]Personnes!B59</f>
         <v>Titouan</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A60" t="str">
-        <f>[2]Personnes!A60</f>
+        <f>[1]Personnes!A60</f>
         <v>Clerici</v>
       </c>
       <c r="B60" t="str">
-        <f>[2]Personnes!B60</f>
+        <f>[1]Personnes!B60</f>
         <v>Tristan</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A61" t="str">
-        <f>[2]Personnes!A61</f>
+        <f>[1]Personnes!A61</f>
         <v>Bally</v>
       </c>
       <c r="B61" t="str">
-        <f>[2]Personnes!B61</f>
+        <f>[1]Personnes!B61</f>
         <v>Yann</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A62" t="str">
-        <f>[2]Personnes!A62</f>
+        <f>[1]Personnes!A62</f>
         <v>Ménétrey</v>
       </c>
       <c r="B62" t="str">
-        <f>[2]Personnes!B62</f>
+        <f>[1]Personnes!B62</f>
         <v>Ysatis</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A63" t="str">
-        <f>[2]Personnes!A63</f>
+        <f>[1]Personnes!A63</f>
         <v>Ménard</v>
       </c>
       <c r="B63" t="str">
-        <f>[2]Personnes!B63</f>
+        <f>[1]Personnes!B63</f>
         <v>Mireille</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A64" t="str">
-        <f>[2]Personnes!A64</f>
+        <f>[1]Personnes!A64</f>
         <v>Rieger</v>
       </c>
       <c r="B64" t="str">
-        <f>[2]Personnes!B64</f>
+        <f>[1]Personnes!B64</f>
         <v>Maya</v>
       </c>
     </row>
     <row r="65" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B65">
-        <f>[2]Personnes!B65</f>
+        <f>[1]Personnes!B65</f>
         <v>0</v>
       </c>
     </row>
@@ -3699,381 +3702,381 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A2" t="str">
-        <f>[2]Personnes!A2</f>
+        <f>[1]Personnes!A2</f>
         <v>Bouvet</v>
       </c>
       <c r="B2" t="str">
-        <f>[2]Personnes!B2</f>
+        <f>[1]Personnes!B2</f>
         <v>Agathe</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A3" t="str">
-        <f>[2]Personnes!A3</f>
+        <f>[1]Personnes!A3</f>
         <v>Bulka</v>
       </c>
       <c r="B3" t="str">
-        <f>[2]Personnes!B3</f>
+        <f>[1]Personnes!B3</f>
         <v>Alegria Lily</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A4" t="str">
-        <f>[2]Personnes!A4</f>
+        <f>[1]Personnes!A4</f>
         <v>Bastian</v>
       </c>
       <c r="B4" t="str">
-        <f>[2]Personnes!B4</f>
+        <f>[1]Personnes!B4</f>
         <v>Alexandra</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A5" t="str">
-        <f>[2]Personnes!A5</f>
+        <f>[1]Personnes!A5</f>
         <v>L'Horset</v>
       </c>
       <c r="B5" t="str">
-        <f>[2]Personnes!B5</f>
+        <f>[1]Personnes!B5</f>
         <v>Alice</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A6" t="str">
-        <f>[2]Personnes!A6</f>
+        <f>[1]Personnes!A6</f>
         <v>Ledru</v>
       </c>
       <c r="B6" t="str">
-        <f>[2]Personnes!B6</f>
+        <f>[1]Personnes!B6</f>
         <v>Analou</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A7" t="str">
-        <f>[2]Personnes!A7</f>
+        <f>[1]Personnes!A7</f>
         <v>Mallet</v>
       </c>
       <c r="B7" t="str">
-        <f>[2]Personnes!B7</f>
+        <f>[1]Personnes!B7</f>
         <v>Anna</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A8" t="str">
-        <f>[2]Personnes!A8</f>
+        <f>[1]Personnes!A8</f>
         <v>Malric</v>
       </c>
       <c r="B8" t="str">
-        <f>[2]Personnes!B8</f>
+        <f>[1]Personnes!B8</f>
         <v>Annouk</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A9" t="str">
-        <f>[2]Personnes!A9</f>
+        <f>[1]Personnes!A9</f>
         <v>Noël</v>
       </c>
       <c r="B9" t="str">
-        <f>[2]Personnes!B9</f>
+        <f>[1]Personnes!B9</f>
         <v>Antonin</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A10" t="str">
-        <f>[2]Personnes!A10</f>
+        <f>[1]Personnes!A10</f>
         <v>Tessier</v>
       </c>
       <c r="B10" t="str">
-        <f>[2]Personnes!B10</f>
+        <f>[1]Personnes!B10</f>
         <v>Arsène</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A11" t="str">
-        <f>[2]Personnes!A11</f>
+        <f>[1]Personnes!A11</f>
         <v>Uldry</v>
       </c>
       <c r="B11" t="str">
-        <f>[2]Personnes!B11</f>
+        <f>[1]Personnes!B11</f>
         <v>Arthur</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A12" t="str">
-        <f>[2]Personnes!A12</f>
+        <f>[1]Personnes!A12</f>
         <v>Marchand</v>
       </c>
       <c r="B12" t="str">
-        <f>[2]Personnes!B12</f>
+        <f>[1]Personnes!B12</f>
         <v>Athénaé</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A13" t="str">
-        <f>[2]Personnes!A13</f>
+        <f>[1]Personnes!A13</f>
         <v>Magerand</v>
       </c>
       <c r="B13" t="str">
-        <f>[2]Personnes!B13</f>
+        <f>[1]Personnes!B13</f>
         <v>Auxence</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A14" t="str">
-        <f>[2]Personnes!A14</f>
+        <f>[1]Personnes!A14</f>
         <v>Baruch</v>
       </c>
       <c r="B14" t="str">
-        <f>[2]Personnes!B14</f>
+        <f>[1]Personnes!B14</f>
         <v>Ava</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A15" t="str">
-        <f>[2]Personnes!A15</f>
+        <f>[1]Personnes!A15</f>
         <v>Detrain</v>
       </c>
       <c r="B15" t="str">
-        <f>[2]Personnes!B15</f>
+        <f>[1]Personnes!B15</f>
         <v>Benoît</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A16" t="str">
-        <f>[2]Personnes!A16</f>
+        <f>[1]Personnes!A16</f>
         <v>Meige</v>
       </c>
       <c r="B16" t="str">
-        <f>[2]Personnes!B16</f>
+        <f>[1]Personnes!B16</f>
         <v>Corentin</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17" t="str">
-        <f>[2]Personnes!A17</f>
+        <f>[1]Personnes!A17</f>
         <v>De Filippo</v>
       </c>
       <c r="B17" t="str">
-        <f>[2]Personnes!B17</f>
+        <f>[1]Personnes!B17</f>
         <v>Emma</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18" t="str">
-        <f>[2]Personnes!A18</f>
+        <f>[1]Personnes!A18</f>
         <v>Maître</v>
       </c>
       <c r="B18" t="str">
-        <f>[2]Personnes!B18</f>
+        <f>[1]Personnes!B18</f>
         <v>Enzo</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19" t="str">
-        <f>[2]Personnes!A19</f>
+        <f>[1]Personnes!A19</f>
         <v>Prouvost</v>
       </c>
       <c r="B19" t="str">
-        <f>[2]Personnes!B19</f>
+        <f>[1]Personnes!B19</f>
         <v>Eugénie</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20" t="str">
-        <f>[2]Personnes!A20</f>
+        <f>[1]Personnes!A20</f>
         <v xml:space="preserve">Rakotonandrasana </v>
       </c>
       <c r="B20" t="str">
-        <f>[2]Personnes!B20</f>
+        <f>[1]Personnes!B20</f>
         <v>Iris</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21" t="str">
-        <f>[2]Personnes!A21</f>
+        <f>[1]Personnes!A21</f>
         <v>Bürgisser</v>
       </c>
       <c r="B21" t="str">
-        <f>[2]Personnes!B21</f>
+        <f>[1]Personnes!B21</f>
         <v>Jamilah</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A22" t="str">
-        <f>[2]Personnes!A22</f>
+        <f>[1]Personnes!A22</f>
         <v>Ruscio</v>
       </c>
       <c r="B22" t="str">
-        <f>[2]Personnes!B22</f>
+        <f>[1]Personnes!B22</f>
         <v>Jolan</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A23" t="str">
-        <f>[2]Personnes!A23</f>
+        <f>[1]Personnes!A23</f>
         <v>Wuilloud</v>
       </c>
       <c r="B23" t="str">
-        <f>[2]Personnes!B23</f>
+        <f>[1]Personnes!B23</f>
         <v xml:space="preserve">Jonas </v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A24" t="str">
-        <f>[2]Personnes!A24</f>
+        <f>[1]Personnes!A24</f>
         <v>Pirolley</v>
       </c>
       <c r="B24" t="str">
-        <f>[2]Personnes!B24</f>
+        <f>[1]Personnes!B24</f>
         <v>Jules</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25" t="str">
-        <f>[2]Personnes!A25</f>
+        <f>[1]Personnes!A25</f>
         <v>Chavaillaz</v>
       </c>
       <c r="B25" t="str">
-        <f>[2]Personnes!B25</f>
+        <f>[1]Personnes!B25</f>
         <v>Julie</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A26" t="str">
-        <f>[2]Personnes!A26</f>
+        <f>[1]Personnes!A26</f>
         <v>Oeschger</v>
       </c>
       <c r="B26" t="str">
-        <f>[2]Personnes!B26</f>
+        <f>[1]Personnes!B26</f>
         <v>Kristel</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A27" t="str">
-        <f>[2]Personnes!A27</f>
+        <f>[1]Personnes!A27</f>
         <v>Baltzinger</v>
       </c>
       <c r="B27" t="str">
-        <f>[2]Personnes!B27</f>
+        <f>[1]Personnes!B27</f>
         <v>Léa</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A28" t="str">
-        <f>[2]Personnes!A28</f>
+        <f>[1]Personnes!A28</f>
         <v>Chambaz</v>
       </c>
       <c r="B28" t="str">
-        <f>[2]Personnes!B28</f>
+        <f>[1]Personnes!B28</f>
         <v>Léa</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A29" t="str">
-        <f>[2]Personnes!A29</f>
+        <f>[1]Personnes!A29</f>
         <v>Ledru</v>
       </c>
       <c r="B29" t="str">
-        <f>[2]Personnes!B29</f>
+        <f>[1]Personnes!B29</f>
         <v>Lina-Rosa</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A30" t="str">
-        <f>[2]Personnes!A30</f>
+        <f>[1]Personnes!A30</f>
         <v>Jaquet</v>
       </c>
       <c r="B30" t="str">
-        <f>[2]Personnes!B30</f>
+        <f>[1]Personnes!B30</f>
         <v>Lisa</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A31" t="str">
-        <f>[2]Personnes!A31</f>
+        <f>[1]Personnes!A31</f>
         <v>Magnin</v>
       </c>
       <c r="B31" t="str">
-        <f>[2]Personnes!B31</f>
+        <f>[1]Personnes!B31</f>
         <v>Lisa</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A32" t="str">
-        <f>[2]Personnes!A32</f>
+        <f>[1]Personnes!A32</f>
         <v>Cardis</v>
       </c>
       <c r="B32" t="str">
-        <f>[2]Personnes!B32</f>
+        <f>[1]Personnes!B32</f>
         <v>Louis</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A33" t="str">
-        <f>[2]Personnes!A33</f>
+        <f>[1]Personnes!A33</f>
         <v>Post</v>
       </c>
       <c r="B33" t="str">
-        <f>[2]Personnes!B33</f>
+        <f>[1]Personnes!B33</f>
         <v>Louis</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A34" t="str">
-        <f>[2]Personnes!A34</f>
+        <f>[1]Personnes!A34</f>
         <v>Blanchard</v>
       </c>
       <c r="B34" t="str">
-        <f>[2]Personnes!B34</f>
+        <f>[1]Personnes!B34</f>
         <v>Louise</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A35" t="str">
-        <f>[2]Personnes!A35</f>
+        <f>[1]Personnes!A35</f>
         <v>Chastroux</v>
       </c>
       <c r="B35" t="str">
-        <f>[2]Personnes!B35</f>
+        <f>[1]Personnes!B35</f>
         <v>Lucas</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A36" t="str">
-        <f>[2]Personnes!A36</f>
+        <f>[1]Personnes!A36</f>
         <v>Meyer</v>
       </c>
       <c r="B36" t="str">
-        <f>[2]Personnes!B36</f>
+        <f>[1]Personnes!B36</f>
         <v>Lucie</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A37" t="str">
-        <f>[2]Personnes!A37</f>
+        <f>[1]Personnes!A37</f>
         <v>Ménétrey</v>
       </c>
       <c r="B37" t="str">
-        <f>[2]Personnes!B37</f>
+        <f>[1]Personnes!B37</f>
         <v>Maëlan</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A38" t="str">
-        <f>[2]Personnes!A38</f>
+        <f>[1]Personnes!A38</f>
         <v>Chambaz</v>
       </c>
       <c r="B38" t="str">
-        <f>[2]Personnes!B38</f>
+        <f>[1]Personnes!B38</f>
         <v>Maëlle</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A39" t="str">
-        <f>[2]Personnes!A39</f>
+        <f>[1]Personnes!A39</f>
         <v>Felix</v>
       </c>
       <c r="B39" t="str">
-        <f>[2]Personnes!B39</f>
+        <f>[1]Personnes!B39</f>
         <v>Marius</v>
       </c>
       <c r="C39" t="s">
@@ -4088,41 +4091,41 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A40" t="str">
-        <f>[2]Personnes!A40</f>
+        <f>[1]Personnes!A40</f>
         <v>Ledru</v>
       </c>
       <c r="B40" t="str">
-        <f>[2]Personnes!B40</f>
+        <f>[1]Personnes!B40</f>
         <v>Marot</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A41" t="str">
-        <f>[2]Personnes!A41</f>
+        <f>[1]Personnes!A41</f>
         <v>Cuinet</v>
       </c>
       <c r="B41" t="str">
-        <f>[2]Personnes!B41</f>
+        <f>[1]Personnes!B41</f>
         <v>Mathis</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A42" t="str">
-        <f>[2]Personnes!A42</f>
+        <f>[1]Personnes!A42</f>
         <v>Gavin</v>
       </c>
       <c r="B42" t="str">
-        <f>[2]Personnes!B42</f>
+        <f>[1]Personnes!B42</f>
         <v>Matteo</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A43" t="str">
-        <f>[2]Personnes!A43</f>
+        <f>[1]Personnes!A43</f>
         <v>Debray</v>
       </c>
       <c r="B43" t="str">
-        <f>[2]Personnes!B43</f>
+        <f>[1]Personnes!B43</f>
         <v>Maxime</v>
       </c>
       <c r="C43" t="s">
@@ -4137,91 +4140,91 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A44" t="str">
-        <f>[2]Personnes!A44</f>
+        <f>[1]Personnes!A44</f>
         <v>Corbelli</v>
       </c>
       <c r="B44" t="str">
-        <f>[2]Personnes!B44</f>
+        <f>[1]Personnes!B44</f>
         <v>Maya</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A45" t="str">
-        <f>[2]Personnes!A45</f>
+        <f>[1]Personnes!A45</f>
         <v>Pasche</v>
       </c>
       <c r="B45" t="str">
-        <f>[2]Personnes!B45</f>
+        <f>[1]Personnes!B45</f>
         <v>Mickaël</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A46" t="str">
-        <f>[2]Personnes!A46</f>
+        <f>[1]Personnes!A46</f>
         <v>Fargues</v>
       </c>
       <c r="B46" t="str">
-        <f>[2]Personnes!B46</f>
+        <f>[1]Personnes!B46</f>
         <v>Morgana</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A47" t="str">
-        <f>[2]Personnes!A47</f>
+        <f>[1]Personnes!A47</f>
         <v>Scyboz (Lambelet)</v>
       </c>
       <c r="B47" t="str">
-        <f>[2]Personnes!B47</f>
+        <f>[1]Personnes!B47</f>
         <v>Morgane</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A48" t="str">
-        <f>[2]Personnes!A48</f>
+        <f>[1]Personnes!A48</f>
         <v>Koux</v>
       </c>
       <c r="B48" t="str">
-        <f>[2]Personnes!B48</f>
+        <f>[1]Personnes!B48</f>
         <v>Nathalia</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A49" t="str">
-        <f>[2]Personnes!A49</f>
+        <f>[1]Personnes!A49</f>
         <v>Cherpillod</v>
       </c>
       <c r="B49" t="str">
-        <f>[2]Personnes!B49</f>
+        <f>[1]Personnes!B49</f>
         <v>Noah</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A50" t="str">
-        <f>[2]Personnes!A50</f>
+        <f>[1]Personnes!A50</f>
         <v>Chambaz</v>
       </c>
       <c r="B50" t="str">
-        <f>[2]Personnes!B50</f>
+        <f>[1]Personnes!B50</f>
         <v>Patrick</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A51" t="str">
-        <f>[2]Personnes!A51</f>
+        <f>[1]Personnes!A51</f>
         <v>Assaoui</v>
       </c>
       <c r="B51" t="str">
-        <f>[2]Personnes!B51</f>
+        <f>[1]Personnes!B51</f>
         <v>Rama</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A52" t="str">
-        <f>[2]Personnes!A52</f>
+        <f>[1]Personnes!A52</f>
         <v>Lacroze</v>
       </c>
       <c r="B52" t="str">
-        <f>[2]Personnes!B52</f>
+        <f>[1]Personnes!B52</f>
         <v>Raphaël</v>
       </c>
       <c r="C52" t="s">
@@ -4236,121 +4239,121 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A53" t="str">
-        <f>[2]Personnes!A53</f>
+        <f>[1]Personnes!A53</f>
         <v>Neidhart</v>
       </c>
       <c r="B53" t="str">
-        <f>[2]Personnes!B53</f>
+        <f>[1]Personnes!B53</f>
         <v>Raphaëlle</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A54" t="str">
-        <f>[2]Personnes!A54</f>
+        <f>[1]Personnes!A54</f>
         <v xml:space="preserve">Lanni </v>
       </c>
       <c r="B54" t="str">
-        <f>[2]Personnes!B54</f>
+        <f>[1]Personnes!B54</f>
         <v>Roxanne</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A55" t="str">
-        <f>[2]Personnes!A55</f>
+        <f>[1]Personnes!A55</f>
         <v>Schiesser</v>
       </c>
       <c r="B55" t="str">
-        <f>[2]Personnes!B55</f>
+        <f>[1]Personnes!B55</f>
         <v>Sébastien</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A56" t="str">
-        <f>[2]Personnes!A56</f>
+        <f>[1]Personnes!A56</f>
         <v>Lambelet</v>
       </c>
       <c r="B56" t="str">
-        <f>[2]Personnes!B56</f>
+        <f>[1]Personnes!B56</f>
         <v>Simon</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A57" t="str">
-        <f>[2]Personnes!A57</f>
+        <f>[1]Personnes!A57</f>
         <v>Cyprien</v>
       </c>
       <c r="B57" t="str">
-        <f>[2]Personnes!B57</f>
+        <f>[1]Personnes!B57</f>
         <v>Theo</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A58" t="str">
-        <f>[2]Personnes!A58</f>
+        <f>[1]Personnes!A58</f>
         <v>Clerici</v>
       </c>
       <c r="B58" t="str">
-        <f>[2]Personnes!B58</f>
+        <f>[1]Personnes!B58</f>
         <v>Thibault</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A59" t="str">
-        <f>[2]Personnes!A59</f>
+        <f>[1]Personnes!A59</f>
         <v>Ménétrey</v>
       </c>
       <c r="B59" t="str">
-        <f>[2]Personnes!B59</f>
+        <f>[1]Personnes!B59</f>
         <v>Titouan</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A60" t="str">
-        <f>[2]Personnes!A60</f>
+        <f>[1]Personnes!A60</f>
         <v>Clerici</v>
       </c>
       <c r="B60" t="str">
-        <f>[2]Personnes!B60</f>
+        <f>[1]Personnes!B60</f>
         <v>Tristan</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A61" t="str">
-        <f>[2]Personnes!A61</f>
+        <f>[1]Personnes!A61</f>
         <v>Bally</v>
       </c>
       <c r="B61" t="str">
-        <f>[2]Personnes!B61</f>
+        <f>[1]Personnes!B61</f>
         <v>Yann</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A62" t="str">
-        <f>[2]Personnes!A62</f>
+        <f>[1]Personnes!A62</f>
         <v>Ménétrey</v>
       </c>
       <c r="B62" t="str">
-        <f>[2]Personnes!B62</f>
+        <f>[1]Personnes!B62</f>
         <v>Ysatis</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A63" t="str">
-        <f>[2]Personnes!A63</f>
+        <f>[1]Personnes!A63</f>
         <v>Ménard</v>
       </c>
       <c r="B63" t="str">
-        <f>[2]Personnes!B63</f>
+        <f>[1]Personnes!B63</f>
         <v>Mireille</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A64" t="str">
-        <f>[2]Personnes!A64</f>
+        <f>[1]Personnes!A64</f>
         <v>Rieger</v>
       </c>
       <c r="B64" t="str">
-        <f>[2]Personnes!B64</f>
+        <f>[1]Personnes!B64</f>
         <v>Maya</v>
       </c>
     </row>
@@ -4412,381 +4415,381 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A2" t="str">
-        <f>[2]Personnes!A2</f>
+        <f>[1]Personnes!A2</f>
         <v>Bouvet</v>
       </c>
       <c r="B2" t="str">
-        <f>[2]Personnes!B2</f>
+        <f>[1]Personnes!B2</f>
         <v>Agathe</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A3" t="str">
-        <f>[2]Personnes!A3</f>
+        <f>[1]Personnes!A3</f>
         <v>Bulka</v>
       </c>
       <c r="B3" t="str">
-        <f>[2]Personnes!B3</f>
+        <f>[1]Personnes!B3</f>
         <v>Alegria Lily</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A4" t="str">
-        <f>[2]Personnes!A4</f>
+        <f>[1]Personnes!A4</f>
         <v>Bastian</v>
       </c>
       <c r="B4" t="str">
-        <f>[2]Personnes!B4</f>
+        <f>[1]Personnes!B4</f>
         <v>Alexandra</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A5" t="str">
-        <f>[2]Personnes!A5</f>
+        <f>[1]Personnes!A5</f>
         <v>L'Horset</v>
       </c>
       <c r="B5" t="str">
-        <f>[2]Personnes!B5</f>
+        <f>[1]Personnes!B5</f>
         <v>Alice</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A6" t="str">
-        <f>[2]Personnes!A6</f>
+        <f>[1]Personnes!A6</f>
         <v>Ledru</v>
       </c>
       <c r="B6" t="str">
-        <f>[2]Personnes!B6</f>
+        <f>[1]Personnes!B6</f>
         <v>Analou</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A7" t="str">
-        <f>[2]Personnes!A7</f>
+        <f>[1]Personnes!A7</f>
         <v>Mallet</v>
       </c>
       <c r="B7" t="str">
-        <f>[2]Personnes!B7</f>
+        <f>[1]Personnes!B7</f>
         <v>Anna</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A8" t="str">
-        <f>[2]Personnes!A8</f>
+        <f>[1]Personnes!A8</f>
         <v>Malric</v>
       </c>
       <c r="B8" t="str">
-        <f>[2]Personnes!B8</f>
+        <f>[1]Personnes!B8</f>
         <v>Annouk</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A9" t="str">
-        <f>[2]Personnes!A9</f>
+        <f>[1]Personnes!A9</f>
         <v>Noël</v>
       </c>
       <c r="B9" t="str">
-        <f>[2]Personnes!B9</f>
+        <f>[1]Personnes!B9</f>
         <v>Antonin</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A10" t="str">
-        <f>[2]Personnes!A10</f>
+        <f>[1]Personnes!A10</f>
         <v>Tessier</v>
       </c>
       <c r="B10" t="str">
-        <f>[2]Personnes!B10</f>
+        <f>[1]Personnes!B10</f>
         <v>Arsène</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A11" t="str">
-        <f>[2]Personnes!A11</f>
+        <f>[1]Personnes!A11</f>
         <v>Uldry</v>
       </c>
       <c r="B11" t="str">
-        <f>[2]Personnes!B11</f>
+        <f>[1]Personnes!B11</f>
         <v>Arthur</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A12" t="str">
-        <f>[2]Personnes!A12</f>
+        <f>[1]Personnes!A12</f>
         <v>Marchand</v>
       </c>
       <c r="B12" t="str">
-        <f>[2]Personnes!B12</f>
+        <f>[1]Personnes!B12</f>
         <v>Athénaé</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A13" t="str">
-        <f>[2]Personnes!A13</f>
+        <f>[1]Personnes!A13</f>
         <v>Magerand</v>
       </c>
       <c r="B13" t="str">
-        <f>[2]Personnes!B13</f>
+        <f>[1]Personnes!B13</f>
         <v>Auxence</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A14" t="str">
-        <f>[2]Personnes!A14</f>
+        <f>[1]Personnes!A14</f>
         <v>Baruch</v>
       </c>
       <c r="B14" t="str">
-        <f>[2]Personnes!B14</f>
+        <f>[1]Personnes!B14</f>
         <v>Ava</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A15" t="str">
-        <f>[2]Personnes!A15</f>
+        <f>[1]Personnes!A15</f>
         <v>Detrain</v>
       </c>
       <c r="B15" t="str">
-        <f>[2]Personnes!B15</f>
+        <f>[1]Personnes!B15</f>
         <v>Benoît</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A16" t="str">
-        <f>[2]Personnes!A16</f>
+        <f>[1]Personnes!A16</f>
         <v>Meige</v>
       </c>
       <c r="B16" t="str">
-        <f>[2]Personnes!B16</f>
+        <f>[1]Personnes!B16</f>
         <v>Corentin</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17" t="str">
-        <f>[2]Personnes!A17</f>
+        <f>[1]Personnes!A17</f>
         <v>De Filippo</v>
       </c>
       <c r="B17" t="str">
-        <f>[2]Personnes!B17</f>
+        <f>[1]Personnes!B17</f>
         <v>Emma</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18" t="str">
-        <f>[2]Personnes!A18</f>
+        <f>[1]Personnes!A18</f>
         <v>Maître</v>
       </c>
       <c r="B18" t="str">
-        <f>[2]Personnes!B18</f>
+        <f>[1]Personnes!B18</f>
         <v>Enzo</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19" t="str">
-        <f>[2]Personnes!A19</f>
+        <f>[1]Personnes!A19</f>
         <v>Prouvost</v>
       </c>
       <c r="B19" t="str">
-        <f>[2]Personnes!B19</f>
+        <f>[1]Personnes!B19</f>
         <v>Eugénie</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20" t="str">
-        <f>[2]Personnes!A20</f>
+        <f>[1]Personnes!A20</f>
         <v xml:space="preserve">Rakotonandrasana </v>
       </c>
       <c r="B20" t="str">
-        <f>[2]Personnes!B20</f>
+        <f>[1]Personnes!B20</f>
         <v>Iris</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21" t="str">
-        <f>[2]Personnes!A21</f>
+        <f>[1]Personnes!A21</f>
         <v>Bürgisser</v>
       </c>
       <c r="B21" t="str">
-        <f>[2]Personnes!B21</f>
+        <f>[1]Personnes!B21</f>
         <v>Jamilah</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A22" t="str">
-        <f>[2]Personnes!A22</f>
+        <f>[1]Personnes!A22</f>
         <v>Ruscio</v>
       </c>
       <c r="B22" t="str">
-        <f>[2]Personnes!B22</f>
+        <f>[1]Personnes!B22</f>
         <v>Jolan</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A23" t="str">
-        <f>[2]Personnes!A23</f>
+        <f>[1]Personnes!A23</f>
         <v>Wuilloud</v>
       </c>
       <c r="B23" t="str">
-        <f>[2]Personnes!B23</f>
+        <f>[1]Personnes!B23</f>
         <v xml:space="preserve">Jonas </v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A24" t="str">
-        <f>[2]Personnes!A24</f>
+        <f>[1]Personnes!A24</f>
         <v>Pirolley</v>
       </c>
       <c r="B24" t="str">
-        <f>[2]Personnes!B24</f>
+        <f>[1]Personnes!B24</f>
         <v>Jules</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25" t="str">
-        <f>[2]Personnes!A25</f>
+        <f>[1]Personnes!A25</f>
         <v>Chavaillaz</v>
       </c>
       <c r="B25" t="str">
-        <f>[2]Personnes!B25</f>
+        <f>[1]Personnes!B25</f>
         <v>Julie</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A26" t="str">
-        <f>[2]Personnes!A26</f>
+        <f>[1]Personnes!A26</f>
         <v>Oeschger</v>
       </c>
       <c r="B26" t="str">
-        <f>[2]Personnes!B26</f>
+        <f>[1]Personnes!B26</f>
         <v>Kristel</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A27" t="str">
-        <f>[2]Personnes!A27</f>
+        <f>[1]Personnes!A27</f>
         <v>Baltzinger</v>
       </c>
       <c r="B27" t="str">
-        <f>[2]Personnes!B27</f>
+        <f>[1]Personnes!B27</f>
         <v>Léa</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A28" t="str">
-        <f>[2]Personnes!A28</f>
+        <f>[1]Personnes!A28</f>
         <v>Chambaz</v>
       </c>
       <c r="B28" t="str">
-        <f>[2]Personnes!B28</f>
+        <f>[1]Personnes!B28</f>
         <v>Léa</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A29" t="str">
-        <f>[2]Personnes!A29</f>
+        <f>[1]Personnes!A29</f>
         <v>Ledru</v>
       </c>
       <c r="B29" t="str">
-        <f>[2]Personnes!B29</f>
+        <f>[1]Personnes!B29</f>
         <v>Lina-Rosa</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A30" t="str">
-        <f>[2]Personnes!A30</f>
+        <f>[1]Personnes!A30</f>
         <v>Jaquet</v>
       </c>
       <c r="B30" t="str">
-        <f>[2]Personnes!B30</f>
+        <f>[1]Personnes!B30</f>
         <v>Lisa</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A31" t="str">
-        <f>[2]Personnes!A31</f>
+        <f>[1]Personnes!A31</f>
         <v>Magnin</v>
       </c>
       <c r="B31" t="str">
-        <f>[2]Personnes!B31</f>
+        <f>[1]Personnes!B31</f>
         <v>Lisa</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A32" t="str">
-        <f>[2]Personnes!A32</f>
+        <f>[1]Personnes!A32</f>
         <v>Cardis</v>
       </c>
       <c r="B32" t="str">
-        <f>[2]Personnes!B32</f>
+        <f>[1]Personnes!B32</f>
         <v>Louis</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A33" t="str">
-        <f>[2]Personnes!A33</f>
+        <f>[1]Personnes!A33</f>
         <v>Post</v>
       </c>
       <c r="B33" t="str">
-        <f>[2]Personnes!B33</f>
+        <f>[1]Personnes!B33</f>
         <v>Louis</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A34" t="str">
-        <f>[2]Personnes!A34</f>
+        <f>[1]Personnes!A34</f>
         <v>Blanchard</v>
       </c>
       <c r="B34" t="str">
-        <f>[2]Personnes!B34</f>
+        <f>[1]Personnes!B34</f>
         <v>Louise</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A35" t="str">
-        <f>[2]Personnes!A35</f>
+        <f>[1]Personnes!A35</f>
         <v>Chastroux</v>
       </c>
       <c r="B35" t="str">
-        <f>[2]Personnes!B35</f>
+        <f>[1]Personnes!B35</f>
         <v>Lucas</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A36" t="str">
-        <f>[2]Personnes!A36</f>
+        <f>[1]Personnes!A36</f>
         <v>Meyer</v>
       </c>
       <c r="B36" t="str">
-        <f>[2]Personnes!B36</f>
+        <f>[1]Personnes!B36</f>
         <v>Lucie</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A37" t="str">
-        <f>[2]Personnes!A37</f>
+        <f>[1]Personnes!A37</f>
         <v>Ménétrey</v>
       </c>
       <c r="B37" t="str">
-        <f>[2]Personnes!B37</f>
+        <f>[1]Personnes!B37</f>
         <v>Maëlan</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A38" t="str">
-        <f>[2]Personnes!A38</f>
+        <f>[1]Personnes!A38</f>
         <v>Chambaz</v>
       </c>
       <c r="B38" t="str">
-        <f>[2]Personnes!B38</f>
+        <f>[1]Personnes!B38</f>
         <v>Maëlle</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A39" t="str">
-        <f>[2]Personnes!A39</f>
+        <f>[1]Personnes!A39</f>
         <v>Felix</v>
       </c>
       <c r="B39" t="str">
-        <f>[2]Personnes!B39</f>
+        <f>[1]Personnes!B39</f>
         <v>Marius</v>
       </c>
       <c r="C39" t="s">
@@ -4801,41 +4804,41 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A40" t="str">
-        <f>[2]Personnes!A40</f>
+        <f>[1]Personnes!A40</f>
         <v>Ledru</v>
       </c>
       <c r="B40" t="str">
-        <f>[2]Personnes!B40</f>
+        <f>[1]Personnes!B40</f>
         <v>Marot</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A41" t="str">
-        <f>[2]Personnes!A41</f>
+        <f>[1]Personnes!A41</f>
         <v>Cuinet</v>
       </c>
       <c r="B41" t="str">
-        <f>[2]Personnes!B41</f>
+        <f>[1]Personnes!B41</f>
         <v>Mathis</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A42" t="str">
-        <f>[2]Personnes!A42</f>
+        <f>[1]Personnes!A42</f>
         <v>Gavin</v>
       </c>
       <c r="B42" t="str">
-        <f>[2]Personnes!B42</f>
+        <f>[1]Personnes!B42</f>
         <v>Matteo</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A43" t="str">
-        <f>[2]Personnes!A43</f>
+        <f>[1]Personnes!A43</f>
         <v>Debray</v>
       </c>
       <c r="B43" t="str">
-        <f>[2]Personnes!B43</f>
+        <f>[1]Personnes!B43</f>
         <v>Maxime</v>
       </c>
       <c r="C43" t="s">
@@ -4850,91 +4853,91 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A44" t="str">
-        <f>[2]Personnes!A44</f>
+        <f>[1]Personnes!A44</f>
         <v>Corbelli</v>
       </c>
       <c r="B44" t="str">
-        <f>[2]Personnes!B44</f>
+        <f>[1]Personnes!B44</f>
         <v>Maya</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A45" t="str">
-        <f>[2]Personnes!A45</f>
+        <f>[1]Personnes!A45</f>
         <v>Pasche</v>
       </c>
       <c r="B45" t="str">
-        <f>[2]Personnes!B45</f>
+        <f>[1]Personnes!B45</f>
         <v>Mickaël</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A46" t="str">
-        <f>[2]Personnes!A46</f>
+        <f>[1]Personnes!A46</f>
         <v>Fargues</v>
       </c>
       <c r="B46" t="str">
-        <f>[2]Personnes!B46</f>
+        <f>[1]Personnes!B46</f>
         <v>Morgana</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A47" t="str">
-        <f>[2]Personnes!A47</f>
+        <f>[1]Personnes!A47</f>
         <v>Scyboz (Lambelet)</v>
       </c>
       <c r="B47" t="str">
-        <f>[2]Personnes!B47</f>
+        <f>[1]Personnes!B47</f>
         <v>Morgane</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A48" t="str">
-        <f>[2]Personnes!A48</f>
+        <f>[1]Personnes!A48</f>
         <v>Koux</v>
       </c>
       <c r="B48" t="str">
-        <f>[2]Personnes!B48</f>
+        <f>[1]Personnes!B48</f>
         <v>Nathalia</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A49" t="str">
-        <f>[2]Personnes!A49</f>
+        <f>[1]Personnes!A49</f>
         <v>Cherpillod</v>
       </c>
       <c r="B49" t="str">
-        <f>[2]Personnes!B49</f>
+        <f>[1]Personnes!B49</f>
         <v>Noah</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A50" t="str">
-        <f>[2]Personnes!A50</f>
+        <f>[1]Personnes!A50</f>
         <v>Chambaz</v>
       </c>
       <c r="B50" t="str">
-        <f>[2]Personnes!B50</f>
+        <f>[1]Personnes!B50</f>
         <v>Patrick</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A51" t="str">
-        <f>[2]Personnes!A51</f>
+        <f>[1]Personnes!A51</f>
         <v>Assaoui</v>
       </c>
       <c r="B51" t="str">
-        <f>[2]Personnes!B51</f>
+        <f>[1]Personnes!B51</f>
         <v>Rama</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A52" t="str">
-        <f>[2]Personnes!A52</f>
+        <f>[1]Personnes!A52</f>
         <v>Lacroze</v>
       </c>
       <c r="B52" t="str">
-        <f>[2]Personnes!B52</f>
+        <f>[1]Personnes!B52</f>
         <v>Raphaël</v>
       </c>
       <c r="C52" t="s">
@@ -4949,121 +4952,121 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A53" t="str">
-        <f>[2]Personnes!A53</f>
+        <f>[1]Personnes!A53</f>
         <v>Neidhart</v>
       </c>
       <c r="B53" t="str">
-        <f>[2]Personnes!B53</f>
+        <f>[1]Personnes!B53</f>
         <v>Raphaëlle</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A54" t="str">
-        <f>[2]Personnes!A54</f>
+        <f>[1]Personnes!A54</f>
         <v xml:space="preserve">Lanni </v>
       </c>
       <c r="B54" t="str">
-        <f>[2]Personnes!B54</f>
+        <f>[1]Personnes!B54</f>
         <v>Roxanne</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A55" t="str">
-        <f>[2]Personnes!A55</f>
+        <f>[1]Personnes!A55</f>
         <v>Schiesser</v>
       </c>
       <c r="B55" t="str">
-        <f>[2]Personnes!B55</f>
+        <f>[1]Personnes!B55</f>
         <v>Sébastien</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A56" t="str">
-        <f>[2]Personnes!A56</f>
+        <f>[1]Personnes!A56</f>
         <v>Lambelet</v>
       </c>
       <c r="B56" t="str">
-        <f>[2]Personnes!B56</f>
+        <f>[1]Personnes!B56</f>
         <v>Simon</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A57" t="str">
-        <f>[2]Personnes!A57</f>
+        <f>[1]Personnes!A57</f>
         <v>Cyprien</v>
       </c>
       <c r="B57" t="str">
-        <f>[2]Personnes!B57</f>
+        <f>[1]Personnes!B57</f>
         <v>Theo</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A58" t="str">
-        <f>[2]Personnes!A58</f>
+        <f>[1]Personnes!A58</f>
         <v>Clerici</v>
       </c>
       <c r="B58" t="str">
-        <f>[2]Personnes!B58</f>
+        <f>[1]Personnes!B58</f>
         <v>Thibault</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A59" t="str">
-        <f>[2]Personnes!A59</f>
+        <f>[1]Personnes!A59</f>
         <v>Ménétrey</v>
       </c>
       <c r="B59" t="str">
-        <f>[2]Personnes!B59</f>
+        <f>[1]Personnes!B59</f>
         <v>Titouan</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A60" t="str">
-        <f>[2]Personnes!A60</f>
+        <f>[1]Personnes!A60</f>
         <v>Clerici</v>
       </c>
       <c r="B60" t="str">
-        <f>[2]Personnes!B60</f>
+        <f>[1]Personnes!B60</f>
         <v>Tristan</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A61" t="str">
-        <f>[2]Personnes!A61</f>
+        <f>[1]Personnes!A61</f>
         <v>Bally</v>
       </c>
       <c r="B61" t="str">
-        <f>[2]Personnes!B61</f>
+        <f>[1]Personnes!B61</f>
         <v>Yann</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A62" t="str">
-        <f>[2]Personnes!A62</f>
+        <f>[1]Personnes!A62</f>
         <v>Ménétrey</v>
       </c>
       <c r="B62" t="str">
-        <f>[2]Personnes!B62</f>
+        <f>[1]Personnes!B62</f>
         <v>Ysatis</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A63" t="str">
-        <f>[2]Personnes!A63</f>
+        <f>[1]Personnes!A63</f>
         <v>Ménard</v>
       </c>
       <c r="B63" t="str">
-        <f>[2]Personnes!B63</f>
+        <f>[1]Personnes!B63</f>
         <v>Mireille</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A64" t="str">
-        <f>[2]Personnes!A64</f>
+        <f>[1]Personnes!A64</f>
         <v>Rieger</v>
       </c>
       <c r="B64" t="str">
-        <f>[2]Personnes!B64</f>
+        <f>[1]Personnes!B64</f>
         <v>Maya</v>
       </c>
     </row>
@@ -5125,381 +5128,381 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A2" t="str">
-        <f>[2]Personnes!A2</f>
+        <f>[1]Personnes!A2</f>
         <v>Bouvet</v>
       </c>
       <c r="B2" t="str">
-        <f>[2]Personnes!B2</f>
+        <f>[1]Personnes!B2</f>
         <v>Agathe</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A3" t="str">
-        <f>[2]Personnes!A3</f>
+        <f>[1]Personnes!A3</f>
         <v>Bulka</v>
       </c>
       <c r="B3" t="str">
-        <f>[2]Personnes!B3</f>
+        <f>[1]Personnes!B3</f>
         <v>Alegria Lily</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A4" t="str">
-        <f>[2]Personnes!A4</f>
+        <f>[1]Personnes!A4</f>
         <v>Bastian</v>
       </c>
       <c r="B4" t="str">
-        <f>[2]Personnes!B4</f>
+        <f>[1]Personnes!B4</f>
         <v>Alexandra</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A5" t="str">
-        <f>[2]Personnes!A5</f>
+        <f>[1]Personnes!A5</f>
         <v>L'Horset</v>
       </c>
       <c r="B5" t="str">
-        <f>[2]Personnes!B5</f>
+        <f>[1]Personnes!B5</f>
         <v>Alice</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A6" t="str">
-        <f>[2]Personnes!A6</f>
+        <f>[1]Personnes!A6</f>
         <v>Ledru</v>
       </c>
       <c r="B6" t="str">
-        <f>[2]Personnes!B6</f>
+        <f>[1]Personnes!B6</f>
         <v>Analou</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A7" t="str">
-        <f>[2]Personnes!A7</f>
+        <f>[1]Personnes!A7</f>
         <v>Mallet</v>
       </c>
       <c r="B7" t="str">
-        <f>[2]Personnes!B7</f>
+        <f>[1]Personnes!B7</f>
         <v>Anna</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A8" t="str">
-        <f>[2]Personnes!A8</f>
+        <f>[1]Personnes!A8</f>
         <v>Malric</v>
       </c>
       <c r="B8" t="str">
-        <f>[2]Personnes!B8</f>
+        <f>[1]Personnes!B8</f>
         <v>Annouk</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A9" t="str">
-        <f>[2]Personnes!A9</f>
+        <f>[1]Personnes!A9</f>
         <v>Noël</v>
       </c>
       <c r="B9" t="str">
-        <f>[2]Personnes!B9</f>
+        <f>[1]Personnes!B9</f>
         <v>Antonin</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A10" t="str">
-        <f>[2]Personnes!A10</f>
+        <f>[1]Personnes!A10</f>
         <v>Tessier</v>
       </c>
       <c r="B10" t="str">
-        <f>[2]Personnes!B10</f>
+        <f>[1]Personnes!B10</f>
         <v>Arsène</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A11" t="str">
-        <f>[2]Personnes!A11</f>
+        <f>[1]Personnes!A11</f>
         <v>Uldry</v>
       </c>
       <c r="B11" t="str">
-        <f>[2]Personnes!B11</f>
+        <f>[1]Personnes!B11</f>
         <v>Arthur</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A12" t="str">
-        <f>[2]Personnes!A12</f>
+        <f>[1]Personnes!A12</f>
         <v>Marchand</v>
       </c>
       <c r="B12" t="str">
-        <f>[2]Personnes!B12</f>
+        <f>[1]Personnes!B12</f>
         <v>Athénaé</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A13" t="str">
-        <f>[2]Personnes!A13</f>
+        <f>[1]Personnes!A13</f>
         <v>Magerand</v>
       </c>
       <c r="B13" t="str">
-        <f>[2]Personnes!B13</f>
+        <f>[1]Personnes!B13</f>
         <v>Auxence</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A14" t="str">
-        <f>[2]Personnes!A14</f>
+        <f>[1]Personnes!A14</f>
         <v>Baruch</v>
       </c>
       <c r="B14" t="str">
-        <f>[2]Personnes!B14</f>
+        <f>[1]Personnes!B14</f>
         <v>Ava</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A15" t="str">
-        <f>[2]Personnes!A15</f>
+        <f>[1]Personnes!A15</f>
         <v>Detrain</v>
       </c>
       <c r="B15" t="str">
-        <f>[2]Personnes!B15</f>
+        <f>[1]Personnes!B15</f>
         <v>Benoît</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A16" t="str">
-        <f>[2]Personnes!A16</f>
+        <f>[1]Personnes!A16</f>
         <v>Meige</v>
       </c>
       <c r="B16" t="str">
-        <f>[2]Personnes!B16</f>
+        <f>[1]Personnes!B16</f>
         <v>Corentin</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17" t="str">
-        <f>[2]Personnes!A17</f>
+        <f>[1]Personnes!A17</f>
         <v>De Filippo</v>
       </c>
       <c r="B17" t="str">
-        <f>[2]Personnes!B17</f>
+        <f>[1]Personnes!B17</f>
         <v>Emma</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18" t="str">
-        <f>[2]Personnes!A18</f>
+        <f>[1]Personnes!A18</f>
         <v>Maître</v>
       </c>
       <c r="B18" t="str">
-        <f>[2]Personnes!B18</f>
+        <f>[1]Personnes!B18</f>
         <v>Enzo</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19" t="str">
-        <f>[2]Personnes!A19</f>
+        <f>[1]Personnes!A19</f>
         <v>Prouvost</v>
       </c>
       <c r="B19" t="str">
-        <f>[2]Personnes!B19</f>
+        <f>[1]Personnes!B19</f>
         <v>Eugénie</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20" t="str">
-        <f>[2]Personnes!A20</f>
+        <f>[1]Personnes!A20</f>
         <v xml:space="preserve">Rakotonandrasana </v>
       </c>
       <c r="B20" t="str">
-        <f>[2]Personnes!B20</f>
+        <f>[1]Personnes!B20</f>
         <v>Iris</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21" t="str">
-        <f>[2]Personnes!A21</f>
+        <f>[1]Personnes!A21</f>
         <v>Bürgisser</v>
       </c>
       <c r="B21" t="str">
-        <f>[2]Personnes!B21</f>
+        <f>[1]Personnes!B21</f>
         <v>Jamilah</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A22" t="str">
-        <f>[2]Personnes!A22</f>
+        <f>[1]Personnes!A22</f>
         <v>Ruscio</v>
       </c>
       <c r="B22" t="str">
-        <f>[2]Personnes!B22</f>
+        <f>[1]Personnes!B22</f>
         <v>Jolan</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A23" t="str">
-        <f>[2]Personnes!A23</f>
+        <f>[1]Personnes!A23</f>
         <v>Wuilloud</v>
       </c>
       <c r="B23" t="str">
-        <f>[2]Personnes!B23</f>
+        <f>[1]Personnes!B23</f>
         <v xml:space="preserve">Jonas </v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A24" t="str">
-        <f>[2]Personnes!A24</f>
+        <f>[1]Personnes!A24</f>
         <v>Pirolley</v>
       </c>
       <c r="B24" t="str">
-        <f>[2]Personnes!B24</f>
+        <f>[1]Personnes!B24</f>
         <v>Jules</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25" t="str">
-        <f>[2]Personnes!A25</f>
+        <f>[1]Personnes!A25</f>
         <v>Chavaillaz</v>
       </c>
       <c r="B25" t="str">
-        <f>[2]Personnes!B25</f>
+        <f>[1]Personnes!B25</f>
         <v>Julie</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A26" t="str">
-        <f>[2]Personnes!A26</f>
+        <f>[1]Personnes!A26</f>
         <v>Oeschger</v>
       </c>
       <c r="B26" t="str">
-        <f>[2]Personnes!B26</f>
+        <f>[1]Personnes!B26</f>
         <v>Kristel</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A27" t="str">
-        <f>[2]Personnes!A27</f>
+        <f>[1]Personnes!A27</f>
         <v>Baltzinger</v>
       </c>
       <c r="B27" t="str">
-        <f>[2]Personnes!B27</f>
+        <f>[1]Personnes!B27</f>
         <v>Léa</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A28" t="str">
-        <f>[2]Personnes!A28</f>
+        <f>[1]Personnes!A28</f>
         <v>Chambaz</v>
       </c>
       <c r="B28" t="str">
-        <f>[2]Personnes!B28</f>
+        <f>[1]Personnes!B28</f>
         <v>Léa</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A29" t="str">
-        <f>[2]Personnes!A29</f>
+        <f>[1]Personnes!A29</f>
         <v>Ledru</v>
       </c>
       <c r="B29" t="str">
-        <f>[2]Personnes!B29</f>
+        <f>[1]Personnes!B29</f>
         <v>Lina-Rosa</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A30" t="str">
-        <f>[2]Personnes!A30</f>
+        <f>[1]Personnes!A30</f>
         <v>Jaquet</v>
       </c>
       <c r="B30" t="str">
-        <f>[2]Personnes!B30</f>
+        <f>[1]Personnes!B30</f>
         <v>Lisa</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A31" t="str">
-        <f>[2]Personnes!A31</f>
+        <f>[1]Personnes!A31</f>
         <v>Magnin</v>
       </c>
       <c r="B31" t="str">
-        <f>[2]Personnes!B31</f>
+        <f>[1]Personnes!B31</f>
         <v>Lisa</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A32" t="str">
-        <f>[2]Personnes!A32</f>
+        <f>[1]Personnes!A32</f>
         <v>Cardis</v>
       </c>
       <c r="B32" t="str">
-        <f>[2]Personnes!B32</f>
+        <f>[1]Personnes!B32</f>
         <v>Louis</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A33" t="str">
-        <f>[2]Personnes!A33</f>
+        <f>[1]Personnes!A33</f>
         <v>Post</v>
       </c>
       <c r="B33" t="str">
-        <f>[2]Personnes!B33</f>
+        <f>[1]Personnes!B33</f>
         <v>Louis</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A34" t="str">
-        <f>[2]Personnes!A34</f>
+        <f>[1]Personnes!A34</f>
         <v>Blanchard</v>
       </c>
       <c r="B34" t="str">
-        <f>[2]Personnes!B34</f>
+        <f>[1]Personnes!B34</f>
         <v>Louise</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A35" t="str">
-        <f>[2]Personnes!A35</f>
+        <f>[1]Personnes!A35</f>
         <v>Chastroux</v>
       </c>
       <c r="B35" t="str">
-        <f>[2]Personnes!B35</f>
+        <f>[1]Personnes!B35</f>
         <v>Lucas</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A36" t="str">
-        <f>[2]Personnes!A36</f>
+        <f>[1]Personnes!A36</f>
         <v>Meyer</v>
       </c>
       <c r="B36" t="str">
-        <f>[2]Personnes!B36</f>
+        <f>[1]Personnes!B36</f>
         <v>Lucie</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A37" t="str">
-        <f>[2]Personnes!A37</f>
+        <f>[1]Personnes!A37</f>
         <v>Ménétrey</v>
       </c>
       <c r="B37" t="str">
-        <f>[2]Personnes!B37</f>
+        <f>[1]Personnes!B37</f>
         <v>Maëlan</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A38" t="str">
-        <f>[2]Personnes!A38</f>
+        <f>[1]Personnes!A38</f>
         <v>Chambaz</v>
       </c>
       <c r="B38" t="str">
-        <f>[2]Personnes!B38</f>
+        <f>[1]Personnes!B38</f>
         <v>Maëlle</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A39" t="str">
-        <f>[2]Personnes!A39</f>
+        <f>[1]Personnes!A39</f>
         <v>Felix</v>
       </c>
       <c r="B39" t="str">
-        <f>[2]Personnes!B39</f>
+        <f>[1]Personnes!B39</f>
         <v>Marius</v>
       </c>
       <c r="C39" t="s">
@@ -5514,41 +5517,41 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A40" t="str">
-        <f>[2]Personnes!A40</f>
+        <f>[1]Personnes!A40</f>
         <v>Ledru</v>
       </c>
       <c r="B40" t="str">
-        <f>[2]Personnes!B40</f>
+        <f>[1]Personnes!B40</f>
         <v>Marot</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A41" t="str">
-        <f>[2]Personnes!A41</f>
+        <f>[1]Personnes!A41</f>
         <v>Cuinet</v>
       </c>
       <c r="B41" t="str">
-        <f>[2]Personnes!B41</f>
+        <f>[1]Personnes!B41</f>
         <v>Mathis</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A42" t="str">
-        <f>[2]Personnes!A42</f>
+        <f>[1]Personnes!A42</f>
         <v>Gavin</v>
       </c>
       <c r="B42" t="str">
-        <f>[2]Personnes!B42</f>
+        <f>[1]Personnes!B42</f>
         <v>Matteo</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A43" t="str">
-        <f>[2]Personnes!A43</f>
+        <f>[1]Personnes!A43</f>
         <v>Debray</v>
       </c>
       <c r="B43" t="str">
-        <f>[2]Personnes!B43</f>
+        <f>[1]Personnes!B43</f>
         <v>Maxime</v>
       </c>
       <c r="C43" t="s">
@@ -5563,91 +5566,91 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A44" t="str">
-        <f>[2]Personnes!A44</f>
+        <f>[1]Personnes!A44</f>
         <v>Corbelli</v>
       </c>
       <c r="B44" t="str">
-        <f>[2]Personnes!B44</f>
+        <f>[1]Personnes!B44</f>
         <v>Maya</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A45" t="str">
-        <f>[2]Personnes!A45</f>
+        <f>[1]Personnes!A45</f>
         <v>Pasche</v>
       </c>
       <c r="B45" t="str">
-        <f>[2]Personnes!B45</f>
+        <f>[1]Personnes!B45</f>
         <v>Mickaël</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A46" t="str">
-        <f>[2]Personnes!A46</f>
+        <f>[1]Personnes!A46</f>
         <v>Fargues</v>
       </c>
       <c r="B46" t="str">
-        <f>[2]Personnes!B46</f>
+        <f>[1]Personnes!B46</f>
         <v>Morgana</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A47" t="str">
-        <f>[2]Personnes!A47</f>
+        <f>[1]Personnes!A47</f>
         <v>Scyboz (Lambelet)</v>
       </c>
       <c r="B47" t="str">
-        <f>[2]Personnes!B47</f>
+        <f>[1]Personnes!B47</f>
         <v>Morgane</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A48" t="str">
-        <f>[2]Personnes!A48</f>
+        <f>[1]Personnes!A48</f>
         <v>Koux</v>
       </c>
       <c r="B48" t="str">
-        <f>[2]Personnes!B48</f>
+        <f>[1]Personnes!B48</f>
         <v>Nathalia</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A49" t="str">
-        <f>[2]Personnes!A49</f>
+        <f>[1]Personnes!A49</f>
         <v>Cherpillod</v>
       </c>
       <c r="B49" t="str">
-        <f>[2]Personnes!B49</f>
+        <f>[1]Personnes!B49</f>
         <v>Noah</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A50" t="str">
-        <f>[2]Personnes!A50</f>
+        <f>[1]Personnes!A50</f>
         <v>Chambaz</v>
       </c>
       <c r="B50" t="str">
-        <f>[2]Personnes!B50</f>
+        <f>[1]Personnes!B50</f>
         <v>Patrick</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A51" t="str">
-        <f>[2]Personnes!A51</f>
+        <f>[1]Personnes!A51</f>
         <v>Assaoui</v>
       </c>
       <c r="B51" t="str">
-        <f>[2]Personnes!B51</f>
+        <f>[1]Personnes!B51</f>
         <v>Rama</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A52" t="str">
-        <f>[2]Personnes!A52</f>
+        <f>[1]Personnes!A52</f>
         <v>Lacroze</v>
       </c>
       <c r="B52" t="str">
-        <f>[2]Personnes!B52</f>
+        <f>[1]Personnes!B52</f>
         <v>Raphaël</v>
       </c>
       <c r="C52" t="s">
@@ -5662,121 +5665,121 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A53" t="str">
-        <f>[2]Personnes!A53</f>
+        <f>[1]Personnes!A53</f>
         <v>Neidhart</v>
       </c>
       <c r="B53" t="str">
-        <f>[2]Personnes!B53</f>
+        <f>[1]Personnes!B53</f>
         <v>Raphaëlle</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A54" t="str">
-        <f>[2]Personnes!A54</f>
+        <f>[1]Personnes!A54</f>
         <v xml:space="preserve">Lanni </v>
       </c>
       <c r="B54" t="str">
-        <f>[2]Personnes!B54</f>
+        <f>[1]Personnes!B54</f>
         <v>Roxanne</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A55" t="str">
-        <f>[2]Personnes!A55</f>
+        <f>[1]Personnes!A55</f>
         <v>Schiesser</v>
       </c>
       <c r="B55" t="str">
-        <f>[2]Personnes!B55</f>
+        <f>[1]Personnes!B55</f>
         <v>Sébastien</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A56" t="str">
-        <f>[2]Personnes!A56</f>
+        <f>[1]Personnes!A56</f>
         <v>Lambelet</v>
       </c>
       <c r="B56" t="str">
-        <f>[2]Personnes!B56</f>
+        <f>[1]Personnes!B56</f>
         <v>Simon</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A57" t="str">
-        <f>[2]Personnes!A57</f>
+        <f>[1]Personnes!A57</f>
         <v>Cyprien</v>
       </c>
       <c r="B57" t="str">
-        <f>[2]Personnes!B57</f>
+        <f>[1]Personnes!B57</f>
         <v>Theo</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A58" t="str">
-        <f>[2]Personnes!A58</f>
+        <f>[1]Personnes!A58</f>
         <v>Clerici</v>
       </c>
       <c r="B58" t="str">
-        <f>[2]Personnes!B58</f>
+        <f>[1]Personnes!B58</f>
         <v>Thibault</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A59" t="str">
-        <f>[2]Personnes!A59</f>
+        <f>[1]Personnes!A59</f>
         <v>Ménétrey</v>
       </c>
       <c r="B59" t="str">
-        <f>[2]Personnes!B59</f>
+        <f>[1]Personnes!B59</f>
         <v>Titouan</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A60" t="str">
-        <f>[2]Personnes!A60</f>
+        <f>[1]Personnes!A60</f>
         <v>Clerici</v>
       </c>
       <c r="B60" t="str">
-        <f>[2]Personnes!B60</f>
+        <f>[1]Personnes!B60</f>
         <v>Tristan</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A61" t="str">
-        <f>[2]Personnes!A61</f>
+        <f>[1]Personnes!A61</f>
         <v>Bally</v>
       </c>
       <c r="B61" t="str">
-        <f>[2]Personnes!B61</f>
+        <f>[1]Personnes!B61</f>
         <v>Yann</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A62" t="str">
-        <f>[2]Personnes!A62</f>
+        <f>[1]Personnes!A62</f>
         <v>Ménétrey</v>
       </c>
       <c r="B62" t="str">
-        <f>[2]Personnes!B62</f>
+        <f>[1]Personnes!B62</f>
         <v>Ysatis</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A63" t="str">
-        <f>[2]Personnes!A63</f>
+        <f>[1]Personnes!A63</f>
         <v>Ménard</v>
       </c>
       <c r="B63" t="str">
-        <f>[2]Personnes!B63</f>
+        <f>[1]Personnes!B63</f>
         <v>Mireille</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A64" t="str">
-        <f>[2]Personnes!A64</f>
+        <f>[1]Personnes!A64</f>
         <v>Rieger</v>
       </c>
       <c r="B64" t="str">
-        <f>[2]Personnes!B64</f>
+        <f>[1]Personnes!B64</f>
         <v>Maya</v>
       </c>
     </row>
@@ -5838,381 +5841,381 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A2" t="str">
-        <f>[2]Personnes!A2</f>
+        <f>[1]Personnes!A2</f>
         <v>Bouvet</v>
       </c>
       <c r="B2" t="str">
-        <f>[2]Personnes!B2</f>
+        <f>[1]Personnes!B2</f>
         <v>Agathe</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A3" t="str">
-        <f>[2]Personnes!A3</f>
+        <f>[1]Personnes!A3</f>
         <v>Bulka</v>
       </c>
       <c r="B3" t="str">
-        <f>[2]Personnes!B3</f>
+        <f>[1]Personnes!B3</f>
         <v>Alegria Lily</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A4" t="str">
-        <f>[2]Personnes!A4</f>
+        <f>[1]Personnes!A4</f>
         <v>Bastian</v>
       </c>
       <c r="B4" t="str">
-        <f>[2]Personnes!B4</f>
+        <f>[1]Personnes!B4</f>
         <v>Alexandra</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A5" t="str">
-        <f>[2]Personnes!A5</f>
+        <f>[1]Personnes!A5</f>
         <v>L'Horset</v>
       </c>
       <c r="B5" t="str">
-        <f>[2]Personnes!B5</f>
+        <f>[1]Personnes!B5</f>
         <v>Alice</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A6" t="str">
-        <f>[2]Personnes!A6</f>
+        <f>[1]Personnes!A6</f>
         <v>Ledru</v>
       </c>
       <c r="B6" t="str">
-        <f>[2]Personnes!B6</f>
+        <f>[1]Personnes!B6</f>
         <v>Analou</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A7" t="str">
-        <f>[2]Personnes!A7</f>
+        <f>[1]Personnes!A7</f>
         <v>Mallet</v>
       </c>
       <c r="B7" t="str">
-        <f>[2]Personnes!B7</f>
+        <f>[1]Personnes!B7</f>
         <v>Anna</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A8" t="str">
-        <f>[2]Personnes!A8</f>
+        <f>[1]Personnes!A8</f>
         <v>Malric</v>
       </c>
       <c r="B8" t="str">
-        <f>[2]Personnes!B8</f>
+        <f>[1]Personnes!B8</f>
         <v>Annouk</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A9" t="str">
-        <f>[2]Personnes!A9</f>
+        <f>[1]Personnes!A9</f>
         <v>Noël</v>
       </c>
       <c r="B9" t="str">
-        <f>[2]Personnes!B9</f>
+        <f>[1]Personnes!B9</f>
         <v>Antonin</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A10" t="str">
-        <f>[2]Personnes!A10</f>
+        <f>[1]Personnes!A10</f>
         <v>Tessier</v>
       </c>
       <c r="B10" t="str">
-        <f>[2]Personnes!B10</f>
+        <f>[1]Personnes!B10</f>
         <v>Arsène</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A11" t="str">
-        <f>[2]Personnes!A11</f>
+        <f>[1]Personnes!A11</f>
         <v>Uldry</v>
       </c>
       <c r="B11" t="str">
-        <f>[2]Personnes!B11</f>
+        <f>[1]Personnes!B11</f>
         <v>Arthur</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A12" t="str">
-        <f>[2]Personnes!A12</f>
+        <f>[1]Personnes!A12</f>
         <v>Marchand</v>
       </c>
       <c r="B12" t="str">
-        <f>[2]Personnes!B12</f>
+        <f>[1]Personnes!B12</f>
         <v>Athénaé</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A13" t="str">
-        <f>[2]Personnes!A13</f>
+        <f>[1]Personnes!A13</f>
         <v>Magerand</v>
       </c>
       <c r="B13" t="str">
-        <f>[2]Personnes!B13</f>
+        <f>[1]Personnes!B13</f>
         <v>Auxence</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A14" t="str">
-        <f>[2]Personnes!A14</f>
+        <f>[1]Personnes!A14</f>
         <v>Baruch</v>
       </c>
       <c r="B14" t="str">
-        <f>[2]Personnes!B14</f>
+        <f>[1]Personnes!B14</f>
         <v>Ava</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A15" t="str">
-        <f>[2]Personnes!A15</f>
+        <f>[1]Personnes!A15</f>
         <v>Detrain</v>
       </c>
       <c r="B15" t="str">
-        <f>[2]Personnes!B15</f>
+        <f>[1]Personnes!B15</f>
         <v>Benoît</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A16" t="str">
-        <f>[2]Personnes!A16</f>
+        <f>[1]Personnes!A16</f>
         <v>Meige</v>
       </c>
       <c r="B16" t="str">
-        <f>[2]Personnes!B16</f>
+        <f>[1]Personnes!B16</f>
         <v>Corentin</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17" t="str">
-        <f>[2]Personnes!A17</f>
+        <f>[1]Personnes!A17</f>
         <v>De Filippo</v>
       </c>
       <c r="B17" t="str">
-        <f>[2]Personnes!B17</f>
+        <f>[1]Personnes!B17</f>
         <v>Emma</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18" t="str">
-        <f>[2]Personnes!A18</f>
+        <f>[1]Personnes!A18</f>
         <v>Maître</v>
       </c>
       <c r="B18" t="str">
-        <f>[2]Personnes!B18</f>
+        <f>[1]Personnes!B18</f>
         <v>Enzo</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19" t="str">
-        <f>[2]Personnes!A19</f>
+        <f>[1]Personnes!A19</f>
         <v>Prouvost</v>
       </c>
       <c r="B19" t="str">
-        <f>[2]Personnes!B19</f>
+        <f>[1]Personnes!B19</f>
         <v>Eugénie</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20" t="str">
-        <f>[2]Personnes!A20</f>
+        <f>[1]Personnes!A20</f>
         <v xml:space="preserve">Rakotonandrasana </v>
       </c>
       <c r="B20" t="str">
-        <f>[2]Personnes!B20</f>
+        <f>[1]Personnes!B20</f>
         <v>Iris</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21" t="str">
-        <f>[2]Personnes!A21</f>
+        <f>[1]Personnes!A21</f>
         <v>Bürgisser</v>
       </c>
       <c r="B21" t="str">
-        <f>[2]Personnes!B21</f>
+        <f>[1]Personnes!B21</f>
         <v>Jamilah</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A22" t="str">
-        <f>[2]Personnes!A22</f>
+        <f>[1]Personnes!A22</f>
         <v>Ruscio</v>
       </c>
       <c r="B22" t="str">
-        <f>[2]Personnes!B22</f>
+        <f>[1]Personnes!B22</f>
         <v>Jolan</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A23" t="str">
-        <f>[2]Personnes!A23</f>
+        <f>[1]Personnes!A23</f>
         <v>Wuilloud</v>
       </c>
       <c r="B23" t="str">
-        <f>[2]Personnes!B23</f>
+        <f>[1]Personnes!B23</f>
         <v xml:space="preserve">Jonas </v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A24" t="str">
-        <f>[2]Personnes!A24</f>
+        <f>[1]Personnes!A24</f>
         <v>Pirolley</v>
       </c>
       <c r="B24" t="str">
-        <f>[2]Personnes!B24</f>
+        <f>[1]Personnes!B24</f>
         <v>Jules</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25" t="str">
-        <f>[2]Personnes!A25</f>
+        <f>[1]Personnes!A25</f>
         <v>Chavaillaz</v>
       </c>
       <c r="B25" t="str">
-        <f>[2]Personnes!B25</f>
+        <f>[1]Personnes!B25</f>
         <v>Julie</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A26" t="str">
-        <f>[2]Personnes!A26</f>
+        <f>[1]Personnes!A26</f>
         <v>Oeschger</v>
       </c>
       <c r="B26" t="str">
-        <f>[2]Personnes!B26</f>
+        <f>[1]Personnes!B26</f>
         <v>Kristel</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A27" t="str">
-        <f>[2]Personnes!A27</f>
+        <f>[1]Personnes!A27</f>
         <v>Baltzinger</v>
       </c>
       <c r="B27" t="str">
-        <f>[2]Personnes!B27</f>
+        <f>[1]Personnes!B27</f>
         <v>Léa</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A28" t="str">
-        <f>[2]Personnes!A28</f>
+        <f>[1]Personnes!A28</f>
         <v>Chambaz</v>
       </c>
       <c r="B28" t="str">
-        <f>[2]Personnes!B28</f>
+        <f>[1]Personnes!B28</f>
         <v>Léa</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A29" t="str">
-        <f>[2]Personnes!A29</f>
+        <f>[1]Personnes!A29</f>
         <v>Ledru</v>
       </c>
       <c r="B29" t="str">
-        <f>[2]Personnes!B29</f>
+        <f>[1]Personnes!B29</f>
         <v>Lina-Rosa</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A30" t="str">
-        <f>[2]Personnes!A30</f>
+        <f>[1]Personnes!A30</f>
         <v>Jaquet</v>
       </c>
       <c r="B30" t="str">
-        <f>[2]Personnes!B30</f>
+        <f>[1]Personnes!B30</f>
         <v>Lisa</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A31" t="str">
-        <f>[2]Personnes!A31</f>
+        <f>[1]Personnes!A31</f>
         <v>Magnin</v>
       </c>
       <c r="B31" t="str">
-        <f>[2]Personnes!B31</f>
+        <f>[1]Personnes!B31</f>
         <v>Lisa</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A32" t="str">
-        <f>[2]Personnes!A32</f>
+        <f>[1]Personnes!A32</f>
         <v>Cardis</v>
       </c>
       <c r="B32" t="str">
-        <f>[2]Personnes!B32</f>
+        <f>[1]Personnes!B32</f>
         <v>Louis</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A33" t="str">
-        <f>[2]Personnes!A33</f>
+        <f>[1]Personnes!A33</f>
         <v>Post</v>
       </c>
       <c r="B33" t="str">
-        <f>[2]Personnes!B33</f>
+        <f>[1]Personnes!B33</f>
         <v>Louis</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A34" t="str">
-        <f>[2]Personnes!A34</f>
+        <f>[1]Personnes!A34</f>
         <v>Blanchard</v>
       </c>
       <c r="B34" t="str">
-        <f>[2]Personnes!B34</f>
+        <f>[1]Personnes!B34</f>
         <v>Louise</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A35" t="str">
-        <f>[2]Personnes!A35</f>
+        <f>[1]Personnes!A35</f>
         <v>Chastroux</v>
       </c>
       <c r="B35" t="str">
-        <f>[2]Personnes!B35</f>
+        <f>[1]Personnes!B35</f>
         <v>Lucas</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A36" t="str">
-        <f>[2]Personnes!A36</f>
+        <f>[1]Personnes!A36</f>
         <v>Meyer</v>
       </c>
       <c r="B36" t="str">
-        <f>[2]Personnes!B36</f>
+        <f>[1]Personnes!B36</f>
         <v>Lucie</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A37" t="str">
-        <f>[2]Personnes!A37</f>
+        <f>[1]Personnes!A37</f>
         <v>Ménétrey</v>
       </c>
       <c r="B37" t="str">
-        <f>[2]Personnes!B37</f>
+        <f>[1]Personnes!B37</f>
         <v>Maëlan</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A38" t="str">
-        <f>[2]Personnes!A38</f>
+        <f>[1]Personnes!A38</f>
         <v>Chambaz</v>
       </c>
       <c r="B38" t="str">
-        <f>[2]Personnes!B38</f>
+        <f>[1]Personnes!B38</f>
         <v>Maëlle</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A39" t="str">
-        <f>[2]Personnes!A39</f>
+        <f>[1]Personnes!A39</f>
         <v>Felix</v>
       </c>
       <c r="B39" t="str">
-        <f>[2]Personnes!B39</f>
+        <f>[1]Personnes!B39</f>
         <v>Marius</v>
       </c>
       <c r="C39" t="s">
@@ -6227,41 +6230,41 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A40" t="str">
-        <f>[2]Personnes!A40</f>
+        <f>[1]Personnes!A40</f>
         <v>Ledru</v>
       </c>
       <c r="B40" t="str">
-        <f>[2]Personnes!B40</f>
+        <f>[1]Personnes!B40</f>
         <v>Marot</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A41" t="str">
-        <f>[2]Personnes!A41</f>
+        <f>[1]Personnes!A41</f>
         <v>Cuinet</v>
       </c>
       <c r="B41" t="str">
-        <f>[2]Personnes!B41</f>
+        <f>[1]Personnes!B41</f>
         <v>Mathis</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A42" t="str">
-        <f>[2]Personnes!A42</f>
+        <f>[1]Personnes!A42</f>
         <v>Gavin</v>
       </c>
       <c r="B42" t="str">
-        <f>[2]Personnes!B42</f>
+        <f>[1]Personnes!B42</f>
         <v>Matteo</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A43" t="str">
-        <f>[2]Personnes!A43</f>
+        <f>[1]Personnes!A43</f>
         <v>Debray</v>
       </c>
       <c r="B43" t="str">
-        <f>[2]Personnes!B43</f>
+        <f>[1]Personnes!B43</f>
         <v>Maxime</v>
       </c>
       <c r="C43" t="s">
@@ -6276,91 +6279,91 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A44" t="str">
-        <f>[2]Personnes!A44</f>
+        <f>[1]Personnes!A44</f>
         <v>Corbelli</v>
       </c>
       <c r="B44" t="str">
-        <f>[2]Personnes!B44</f>
+        <f>[1]Personnes!B44</f>
         <v>Maya</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A45" t="str">
-        <f>[2]Personnes!A45</f>
+        <f>[1]Personnes!A45</f>
         <v>Pasche</v>
       </c>
       <c r="B45" t="str">
-        <f>[2]Personnes!B45</f>
+        <f>[1]Personnes!B45</f>
         <v>Mickaël</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A46" t="str">
-        <f>[2]Personnes!A46</f>
+        <f>[1]Personnes!A46</f>
         <v>Fargues</v>
       </c>
       <c r="B46" t="str">
-        <f>[2]Personnes!B46</f>
+        <f>[1]Personnes!B46</f>
         <v>Morgana</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A47" t="str">
-        <f>[2]Personnes!A47</f>
+        <f>[1]Personnes!A47</f>
         <v>Scyboz (Lambelet)</v>
       </c>
       <c r="B47" t="str">
-        <f>[2]Personnes!B47</f>
+        <f>[1]Personnes!B47</f>
         <v>Morgane</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A48" t="str">
-        <f>[2]Personnes!A48</f>
+        <f>[1]Personnes!A48</f>
         <v>Koux</v>
       </c>
       <c r="B48" t="str">
-        <f>[2]Personnes!B48</f>
+        <f>[1]Personnes!B48</f>
         <v>Nathalia</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A49" t="str">
-        <f>[2]Personnes!A49</f>
+        <f>[1]Personnes!A49</f>
         <v>Cherpillod</v>
       </c>
       <c r="B49" t="str">
-        <f>[2]Personnes!B49</f>
+        <f>[1]Personnes!B49</f>
         <v>Noah</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A50" t="str">
-        <f>[2]Personnes!A50</f>
+        <f>[1]Personnes!A50</f>
         <v>Chambaz</v>
       </c>
       <c r="B50" t="str">
-        <f>[2]Personnes!B50</f>
+        <f>[1]Personnes!B50</f>
         <v>Patrick</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A51" t="str">
-        <f>[2]Personnes!A51</f>
+        <f>[1]Personnes!A51</f>
         <v>Assaoui</v>
       </c>
       <c r="B51" t="str">
-        <f>[2]Personnes!B51</f>
+        <f>[1]Personnes!B51</f>
         <v>Rama</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A52" t="str">
-        <f>[2]Personnes!A52</f>
+        <f>[1]Personnes!A52</f>
         <v>Lacroze</v>
       </c>
       <c r="B52" t="str">
-        <f>[2]Personnes!B52</f>
+        <f>[1]Personnes!B52</f>
         <v>Raphaël</v>
       </c>
       <c r="C52" t="s">
@@ -6375,121 +6378,121 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A53" t="str">
-        <f>[2]Personnes!A53</f>
+        <f>[1]Personnes!A53</f>
         <v>Neidhart</v>
       </c>
       <c r="B53" t="str">
-        <f>[2]Personnes!B53</f>
+        <f>[1]Personnes!B53</f>
         <v>Raphaëlle</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A54" t="str">
-        <f>[2]Personnes!A54</f>
+        <f>[1]Personnes!A54</f>
         <v xml:space="preserve">Lanni </v>
       </c>
       <c r="B54" t="str">
-        <f>[2]Personnes!B54</f>
+        <f>[1]Personnes!B54</f>
         <v>Roxanne</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A55" t="str">
-        <f>[2]Personnes!A55</f>
+        <f>[1]Personnes!A55</f>
         <v>Schiesser</v>
       </c>
       <c r="B55" t="str">
-        <f>[2]Personnes!B55</f>
+        <f>[1]Personnes!B55</f>
         <v>Sébastien</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A56" t="str">
-        <f>[2]Personnes!A56</f>
+        <f>[1]Personnes!A56</f>
         <v>Lambelet</v>
       </c>
       <c r="B56" t="str">
-        <f>[2]Personnes!B56</f>
+        <f>[1]Personnes!B56</f>
         <v>Simon</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A57" t="str">
-        <f>[2]Personnes!A57</f>
+        <f>[1]Personnes!A57</f>
         <v>Cyprien</v>
       </c>
       <c r="B57" t="str">
-        <f>[2]Personnes!B57</f>
+        <f>[1]Personnes!B57</f>
         <v>Theo</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A58" t="str">
-        <f>[2]Personnes!A58</f>
+        <f>[1]Personnes!A58</f>
         <v>Clerici</v>
       </c>
       <c r="B58" t="str">
-        <f>[2]Personnes!B58</f>
+        <f>[1]Personnes!B58</f>
         <v>Thibault</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A59" t="str">
-        <f>[2]Personnes!A59</f>
+        <f>[1]Personnes!A59</f>
         <v>Ménétrey</v>
       </c>
       <c r="B59" t="str">
-        <f>[2]Personnes!B59</f>
+        <f>[1]Personnes!B59</f>
         <v>Titouan</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A60" t="str">
-        <f>[2]Personnes!A60</f>
+        <f>[1]Personnes!A60</f>
         <v>Clerici</v>
       </c>
       <c r="B60" t="str">
-        <f>[2]Personnes!B60</f>
+        <f>[1]Personnes!B60</f>
         <v>Tristan</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A61" t="str">
-        <f>[2]Personnes!A61</f>
+        <f>[1]Personnes!A61</f>
         <v>Bally</v>
       </c>
       <c r="B61" t="str">
-        <f>[2]Personnes!B61</f>
+        <f>[1]Personnes!B61</f>
         <v>Yann</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A62" t="str">
-        <f>[2]Personnes!A62</f>
+        <f>[1]Personnes!A62</f>
         <v>Ménétrey</v>
       </c>
       <c r="B62" t="str">
-        <f>[2]Personnes!B62</f>
+        <f>[1]Personnes!B62</f>
         <v>Ysatis</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A63" t="str">
-        <f>[2]Personnes!A63</f>
+        <f>[1]Personnes!A63</f>
         <v>Ménard</v>
       </c>
       <c r="B63" t="str">
-        <f>[2]Personnes!B63</f>
+        <f>[1]Personnes!B63</f>
         <v>Mireille</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A64" t="str">
-        <f>[2]Personnes!A64</f>
+        <f>[1]Personnes!A64</f>
         <v>Rieger</v>
       </c>
       <c r="B64" t="str">
-        <f>[2]Personnes!B64</f>
+        <f>[1]Personnes!B64</f>
         <v>Maya</v>
       </c>
     </row>
@@ -6531,55 +6534,55 @@
   <sheetData>
     <row r="1" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="str">
-        <f>[1]Tâches!$A1</f>
+        <f>[2]Tâches!$A1</f>
         <v>Tâches</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="str">
-        <f>[1]Tâches!$A2</f>
+        <f>[2]Tâches!$A2</f>
         <v>Accueil</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="str">
-        <f>[1]Tâches!$A3</f>
+        <f>[2]Tâches!$A3</f>
         <v>Abeilles Ruche</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="str">
-        <f>[1]Tâches!$A4</f>
+        <f>[2]Tâches!$A4</f>
         <v>Ailes</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="str">
-        <f>[1]Tâches!$A5</f>
+        <f>[2]Tâches!$A5</f>
         <v>Bar loges</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="str">
-        <f>[1]Tâches!$A6</f>
+        <f>[2]Tâches!$A6</f>
         <v>Bar public</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="str">
-        <f>[1]Tâches!$A7</f>
+        <f>[2]Tâches!$A7</f>
         <v>Bourdon.ne</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="str">
-        <f>[1]Tâches!$A8</f>
+        <f>[2]Tâches!$A8</f>
         <v>Entrée backstage</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="str">
-        <f>[1]Tâches!$A9</f>
+        <f>[2]Tâches!$A9</f>
         <v>Horaires</v>
       </c>
     </row>
@@ -6590,62 +6593,62 @@
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="str">
-        <f>[1]Tâches!$A10</f>
+        <f>[2]Tâches!$A10</f>
         <v>Déambule Gerry</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="str">
-        <f>[1]Tâches!$A11</f>
+        <f>[2]Tâches!$A11</f>
         <v>Déambule Colbok</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="str">
-        <f>[1]Tâches!$A12</f>
+        <f>[2]Tâches!$A12</f>
         <v>Déambule Goulus</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="str">
-        <f>[1]Tâches!$A13</f>
-        <v>Déambule Ko-compagnie</v>
+        <f>[2]Tâches!$A13</f>
+        <v>Déambule Volkanik</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A15" t="str">
-        <f>[1]Tâches!$A14</f>
+        <f>[2]Tâches!$A14</f>
         <v>Déambule Spoutnik</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" t="str">
-        <f>[1]Tâches!$A15</f>
+        <f>[2]Tâches!$A15</f>
         <v>Déambule FBI</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17" t="str">
-        <f>[1]Tâches!$A16</f>
+        <f>[2]Tâches!$A16</f>
         <v>Tech PCGB</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A18" t="str">
-        <f>[1]Tâches!$A17</f>
+        <f>[2]Tâches!$A17</f>
         <v>Tech Jacquard</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19" t="str">
-        <f>[1]Tâches!$A18</f>
-        <v>Tech Muchmuche</v>
+        <f>[2]Tâches!$A18</f>
+        <v>Tech Phusis</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A20" t="str">
-        <f>[1]Tâches!$A19</f>
-        <v>Tech T'es rien…</v>
+        <f>[2]Tâches!$A19</f>
+        <v>Tech T'es rien</v>
       </c>
     </row>
   </sheetData>
